--- a/datas/mastersheet/Honda_6SAY_Container_MasterSheet_r00.xlsx
+++ b/datas/mastersheet/Honda_6SAY_Container_MasterSheet_r00.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Workspace\Tools\AutoHub\datas\mastersheet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12DE3D13-CF56-4849-86D9-C0FFFF98A39F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B302ED7-9675-48F6-B321-2DE3AFBFF6B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{287B7087-B8C3-483B-8615-16E7FDDFEF13}"/>
+    <workbookView xWindow="1170" yWindow="1170" windowWidth="21600" windowHeight="13185" activeTab="1" xr2:uid="{287B7087-B8C3-483B-8615-16E7FDDFEF13}"/>
   </bookViews>
   <sheets>
     <sheet name="WorkFlow_Detail" sheetId="4" r:id="rId1"/>
@@ -84,7 +84,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2333" uniqueCount="621">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1629" uniqueCount="579">
   <si>
     <t>General info</t>
   </si>
@@ -3117,200 +3117,73 @@
 Kurata-san</t>
   </si>
   <si>
-    <t>37820-6SA-TD10-M6</t>
-  </si>
-  <si>
-    <t>6SAW/X for DAN
-Dummy/MP1 event</t>
-  </si>
-  <si>
-    <t>MY28</t>
-  </si>
-  <si>
-    <t>BHARAT STAGE6 + RDE</t>
-  </si>
-  <si>
-    <t>ID</t>
-  </si>
-  <si>
-    <t>0261S10C0G</t>
-  </si>
-  <si>
-    <t>0261B00E34-00</t>
-  </si>
-  <si>
-    <t>6SAX</t>
+    <t>37820-6WZ-M610-M6</t>
+  </si>
+  <si>
+    <t>6WZX for CERT/MP0 event</t>
+  </si>
+  <si>
+    <t>MG1CS022</t>
+  </si>
+  <si>
+    <t>6WZX</t>
+  </si>
+  <si>
+    <t>AP2 FFV</t>
+  </si>
+  <si>
+    <t>Brazil</t>
+  </si>
+  <si>
+    <t>0261S10BN8</t>
+  </si>
+  <si>
+    <t>0261B00E0B</t>
+  </si>
+  <si>
+    <t>Honda_MG1CS022_CS_IndiSpec_01</t>
+  </si>
+  <si>
+    <t>V037</t>
+  </si>
+  <si>
+    <t>TP3</t>
   </si>
   <si>
     <t>FFFFEFFFFFEE00000000</t>
   </si>
   <si>
-    <t>37805-6SA-TD10</t>
-  </si>
-  <si>
-    <t>0A-28-31-00-00</t>
-  </si>
-  <si>
-    <t>61Y</t>
-  </si>
-  <si>
-    <t>37820-6SA-TE10-M6</t>
-  </si>
-  <si>
-    <t>0261S10C0H</t>
-  </si>
-  <si>
-    <t>0261B00E35-00</t>
-  </si>
-  <si>
-    <t>37805-6SA-TE10</t>
-  </si>
-  <si>
-    <t>0A-28-31-01-00</t>
-  </si>
-  <si>
-    <t>R2Z</t>
-  </si>
-  <si>
-    <t>37820-6SA-TF10-M6</t>
-  </si>
-  <si>
-    <t>0261S10C0J</t>
-  </si>
-  <si>
-    <t>0261B00E36-00</t>
-  </si>
-  <si>
-    <t>37805-6SA-TF10</t>
-  </si>
-  <si>
-    <t>0A-28-31-02-00</t>
-  </si>
-  <si>
-    <t>1RH</t>
-  </si>
-  <si>
-    <t>37820-6SA-TG10-M6</t>
-  </si>
-  <si>
-    <t>0261S10C0K</t>
-  </si>
-  <si>
-    <t>0261B00E37-00</t>
-  </si>
-  <si>
-    <t>37805-6SA-TG10</t>
-  </si>
-  <si>
-    <t>0A-28-31-03-01</t>
-  </si>
-  <si>
-    <t>HEL</t>
-  </si>
-  <si>
-    <t>37820-6SA-TJ10-M6</t>
-  </si>
-  <si>
-    <t>0261S10C0L</t>
-  </si>
-  <si>
-    <t>0261B00E38-00</t>
-  </si>
-  <si>
-    <t>37805-6SA-TJ10</t>
-  </si>
-  <si>
-    <t>0A-28-31-05-01</t>
-  </si>
-  <si>
-    <t>DQH</t>
-  </si>
-  <si>
-    <t>37820-6SA-TC10-M6</t>
-  </si>
-  <si>
-    <t>0261S10C0M</t>
-  </si>
-  <si>
-    <t>0261B00E39-00</t>
-  </si>
-  <si>
-    <t>6SAW</t>
-  </si>
-  <si>
-    <t>37805-6SA-TC10</t>
-  </si>
-  <si>
-    <t>0A-28-31-06-01</t>
-  </si>
-  <si>
-    <t>C2J</t>
-  </si>
-  <si>
-    <t>37820-6SA-N210-M6</t>
-  </si>
-  <si>
-    <t>EURO 5</t>
-  </si>
-  <si>
-    <t>N</t>
-  </si>
-  <si>
-    <t>0261S10C0N</t>
-  </si>
-  <si>
-    <t>0261B00E3A-00</t>
-  </si>
-  <si>
-    <t>37805-6SA-N210</t>
-  </si>
-  <si>
-    <t>0A-28-31-07-00</t>
-  </si>
-  <si>
-    <t>NCV</t>
-  </si>
-  <si>
-    <t>T52</t>
-  </si>
-  <si>
-    <t>37820-6SA-N710-M6</t>
-  </si>
-  <si>
-    <t>0261S10C0P</t>
-  </si>
-  <si>
-    <t>0261B00E3B-00</t>
-  </si>
-  <si>
-    <t>37805-6SA-N710</t>
-  </si>
-  <si>
-    <t>0A-28-31-08-01</t>
-  </si>
-  <si>
-    <t>BKC</t>
-  </si>
-  <si>
-    <t>NT5</t>
-  </si>
-  <si>
-    <t>37820-6SA-TK10-M6</t>
-  </si>
-  <si>
-    <t>0261S10C0R</t>
-  </si>
-  <si>
-    <t>0261B00E3C-00</t>
-  </si>
-  <si>
-    <t>37805-6SA-TK10</t>
-  </si>
-  <si>
-    <t>0A-28-31-09-01</t>
-  </si>
-  <si>
-    <t>YD7</t>
+    <t>37805-6WZ-M610</t>
+  </si>
+  <si>
+    <t>---</t>
+  </si>
+  <si>
+    <t>01</t>
+  </si>
+  <si>
+    <t>01-28-41-00-01</t>
+  </si>
+  <si>
+    <t>C7C</t>
+  </si>
+  <si>
+    <t>37820-6WZ-M710-M6</t>
+  </si>
+  <si>
+    <t>0261S10BN9</t>
+  </si>
+  <si>
+    <t>0261B00E0C</t>
+  </si>
+  <si>
+    <t>37805-6WZ-M710</t>
+  </si>
+  <si>
+    <t>01-28-41-01-01</t>
+  </si>
+  <si>
+    <t>DTW</t>
   </si>
 </sst>
 </file>
@@ -3857,7 +3730,7 @@
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="34" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="122">
+  <cellXfs count="121">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -4124,9 +3997,6 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="34" fillId="20" borderId="1" xfId="4" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="11" fontId="19" fillId="20" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="11" fontId="19" fillId="17" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -11984,7 +11854,7 @@
     <tabColor rgb="FFFFC000"/>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:CZ55"/>
+  <dimension ref="A1:CZ34"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="8.7109375" style="40" customWidth="1"/>
@@ -12049,35 +11919,35 @@
     </row>
     <row r="2" spans="1:104">
       <c r="A2" s="39"/>
-      <c r="B2" s="118" t="s">
+      <c r="B2" s="117" t="s">
         <v>489</v>
       </c>
-      <c r="C2" s="118"/>
-      <c r="D2" s="118"/>
-      <c r="E2" s="118"/>
-      <c r="F2" s="118"/>
-      <c r="G2" s="118"/>
-      <c r="H2" s="118"/>
+      <c r="C2" s="117"/>
+      <c r="D2" s="117"/>
+      <c r="E2" s="117"/>
+      <c r="F2" s="117"/>
+      <c r="G2" s="117"/>
+      <c r="H2" s="117"/>
     </row>
     <row r="3" spans="1:104" ht="4.5" customHeight="1">
       <c r="A3" s="39"/>
-      <c r="B3" s="118"/>
-      <c r="C3" s="118"/>
-      <c r="D3" s="118"/>
-      <c r="E3" s="118"/>
-      <c r="F3" s="118"/>
-      <c r="G3" s="118"/>
-      <c r="H3" s="118"/>
+      <c r="B3" s="117"/>
+      <c r="C3" s="117"/>
+      <c r="D3" s="117"/>
+      <c r="E3" s="117"/>
+      <c r="F3" s="117"/>
+      <c r="G3" s="117"/>
+      <c r="H3" s="117"/>
     </row>
     <row r="4" spans="1:104" ht="4.5" customHeight="1">
       <c r="A4" s="39"/>
-      <c r="B4" s="118"/>
-      <c r="C4" s="118"/>
-      <c r="D4" s="118"/>
-      <c r="E4" s="118"/>
-      <c r="F4" s="118"/>
-      <c r="G4" s="118"/>
-      <c r="H4" s="118"/>
+      <c r="B4" s="117"/>
+      <c r="C4" s="117"/>
+      <c r="D4" s="117"/>
+      <c r="E4" s="117"/>
+      <c r="F4" s="117"/>
+      <c r="G4" s="117"/>
+      <c r="H4" s="117"/>
     </row>
     <row r="5" spans="1:104" s="41" customFormat="1" ht="18.75" customHeight="1">
       <c r="C5" s="68"/>
@@ -12127,75 +11997,75 @@
       <c r="CZ5" s="68"/>
     </row>
     <row r="6" spans="1:104" ht="18" customHeight="1">
-      <c r="B6" s="121" t="s">
+      <c r="B6" s="120" t="s">
         <v>0</v>
       </c>
-      <c r="C6" s="121"/>
-      <c r="D6" s="121"/>
-      <c r="E6" s="121"/>
-      <c r="F6" s="121"/>
-      <c r="G6" s="121"/>
-      <c r="H6" s="121"/>
-      <c r="I6" s="121"/>
-      <c r="J6" s="121"/>
-      <c r="K6" s="121"/>
-      <c r="L6" s="121"/>
-      <c r="M6" s="120" t="s">
+      <c r="C6" s="120"/>
+      <c r="D6" s="120"/>
+      <c r="E6" s="120"/>
+      <c r="F6" s="120"/>
+      <c r="G6" s="120"/>
+      <c r="H6" s="120"/>
+      <c r="I6" s="120"/>
+      <c r="J6" s="120"/>
+      <c r="K6" s="120"/>
+      <c r="L6" s="120"/>
+      <c r="M6" s="119" t="s">
         <v>311</v>
       </c>
-      <c r="N6" s="120"/>
-      <c r="O6" s="120" t="s">
+      <c r="N6" s="119"/>
+      <c r="O6" s="119" t="s">
         <v>312</v>
       </c>
-      <c r="P6" s="120"/>
+      <c r="P6" s="119"/>
       <c r="Q6" s="61" t="s">
         <v>356</v>
       </c>
       <c r="R6" s="61"/>
       <c r="S6" s="61"/>
-      <c r="T6" s="119" t="s">
+      <c r="T6" s="118" t="s">
         <v>100</v>
       </c>
-      <c r="U6" s="119"/>
-      <c r="V6" s="119"/>
-      <c r="W6" s="119"/>
-      <c r="X6" s="119"/>
-      <c r="Y6" s="119"/>
-      <c r="Z6" s="119"/>
-      <c r="AA6" s="119"/>
-      <c r="AB6" s="115" t="s">
+      <c r="U6" s="118"/>
+      <c r="V6" s="118"/>
+      <c r="W6" s="118"/>
+      <c r="X6" s="118"/>
+      <c r="Y6" s="118"/>
+      <c r="Z6" s="118"/>
+      <c r="AA6" s="118"/>
+      <c r="AB6" s="114" t="s">
         <v>124</v>
       </c>
-      <c r="AC6" s="115"/>
-      <c r="AD6" s="115"/>
-      <c r="AE6" s="115"/>
-      <c r="AF6" s="115"/>
-      <c r="AG6" s="115"/>
-      <c r="AH6" s="115"/>
-      <c r="AI6" s="115"/>
-      <c r="AJ6" s="115"/>
-      <c r="AK6" s="115"/>
-      <c r="AL6" s="116" t="s">
+      <c r="AC6" s="114"/>
+      <c r="AD6" s="114"/>
+      <c r="AE6" s="114"/>
+      <c r="AF6" s="114"/>
+      <c r="AG6" s="114"/>
+      <c r="AH6" s="114"/>
+      <c r="AI6" s="114"/>
+      <c r="AJ6" s="114"/>
+      <c r="AK6" s="114"/>
+      <c r="AL6" s="115" t="s">
         <v>125</v>
       </c>
-      <c r="AM6" s="116"/>
-      <c r="AN6" s="116"/>
-      <c r="AO6" s="116"/>
-      <c r="AP6" s="116"/>
-      <c r="AQ6" s="115" t="s">
+      <c r="AM6" s="115"/>
+      <c r="AN6" s="115"/>
+      <c r="AO6" s="115"/>
+      <c r="AP6" s="115"/>
+      <c r="AQ6" s="114" t="s">
         <v>140</v>
       </c>
-      <c r="AR6" s="115"/>
-      <c r="AS6" s="115"/>
-      <c r="AT6" s="115"/>
-      <c r="AU6" s="115"/>
-      <c r="AV6" s="116" t="s">
+      <c r="AR6" s="114"/>
+      <c r="AS6" s="114"/>
+      <c r="AT6" s="114"/>
+      <c r="AU6" s="114"/>
+      <c r="AV6" s="115" t="s">
         <v>165</v>
       </c>
-      <c r="AW6" s="116"/>
-      <c r="AX6" s="116"/>
-      <c r="AY6" s="116"/>
-      <c r="AZ6" s="116"/>
+      <c r="AW6" s="115"/>
+      <c r="AX6" s="115"/>
+      <c r="AY6" s="115"/>
+      <c r="AZ6" s="115"/>
       <c r="BA6" s="48"/>
       <c r="BB6" s="48"/>
       <c r="BC6" s="61" t="s">
@@ -12293,25 +12163,25 @@
       <c r="CK6" s="65">
         <v>14</v>
       </c>
-      <c r="CL6" s="112" t="s">
+      <c r="CL6" s="111" t="s">
         <v>193</v>
       </c>
-      <c r="CM6" s="113"/>
-      <c r="CN6" s="113"/>
-      <c r="CO6" s="113"/>
-      <c r="CP6" s="113"/>
-      <c r="CQ6" s="113"/>
-      <c r="CR6" s="114"/>
-      <c r="CS6" s="109" t="s">
+      <c r="CM6" s="112"/>
+      <c r="CN6" s="112"/>
+      <c r="CO6" s="112"/>
+      <c r="CP6" s="112"/>
+      <c r="CQ6" s="112"/>
+      <c r="CR6" s="113"/>
+      <c r="CS6" s="108" t="s">
         <v>381</v>
       </c>
-      <c r="CT6" s="110"/>
-      <c r="CU6" s="110"/>
-      <c r="CV6" s="110"/>
-      <c r="CW6" s="110"/>
-      <c r="CX6" s="110"/>
-      <c r="CY6" s="110"/>
-      <c r="CZ6" s="111"/>
+      <c r="CT6" s="109"/>
+      <c r="CU6" s="109"/>
+      <c r="CV6" s="109"/>
+      <c r="CW6" s="109"/>
+      <c r="CX6" s="109"/>
+      <c r="CY6" s="109"/>
+      <c r="CZ6" s="110"/>
     </row>
     <row r="7" spans="1:104" ht="114" collapsed="1">
       <c r="A7" s="67" t="s">
@@ -12497,38 +12367,38 @@
       <c r="BI7" s="66" t="s">
         <v>345</v>
       </c>
-      <c r="BJ7" s="117" t="s">
+      <c r="BJ7" s="116" t="s">
         <v>303</v>
       </c>
-      <c r="BK7" s="117"/>
-      <c r="BL7" s="117"/>
-      <c r="BM7" s="117"/>
-      <c r="BN7" s="117"/>
-      <c r="BO7" s="117"/>
-      <c r="BP7" s="117"/>
-      <c r="BQ7" s="117"/>
-      <c r="BR7" s="117"/>
-      <c r="BS7" s="117"/>
-      <c r="BT7" s="117"/>
-      <c r="BU7" s="117"/>
-      <c r="BV7" s="117"/>
-      <c r="BW7" s="117"/>
-      <c r="BX7" s="117" t="s">
+      <c r="BK7" s="116"/>
+      <c r="BL7" s="116"/>
+      <c r="BM7" s="116"/>
+      <c r="BN7" s="116"/>
+      <c r="BO7" s="116"/>
+      <c r="BP7" s="116"/>
+      <c r="BQ7" s="116"/>
+      <c r="BR7" s="116"/>
+      <c r="BS7" s="116"/>
+      <c r="BT7" s="116"/>
+      <c r="BU7" s="116"/>
+      <c r="BV7" s="116"/>
+      <c r="BW7" s="116"/>
+      <c r="BX7" s="116" t="s">
         <v>304</v>
       </c>
-      <c r="BY7" s="117"/>
-      <c r="BZ7" s="117"/>
-      <c r="CA7" s="117"/>
-      <c r="CB7" s="117"/>
-      <c r="CC7" s="117"/>
-      <c r="CD7" s="117"/>
-      <c r="CE7" s="117"/>
-      <c r="CF7" s="117"/>
-      <c r="CG7" s="117"/>
-      <c r="CH7" s="117"/>
-      <c r="CI7" s="117"/>
-      <c r="CJ7" s="117"/>
-      <c r="CK7" s="117"/>
+      <c r="BY7" s="116"/>
+      <c r="BZ7" s="116"/>
+      <c r="CA7" s="116"/>
+      <c r="CB7" s="116"/>
+      <c r="CC7" s="116"/>
+      <c r="CD7" s="116"/>
+      <c r="CE7" s="116"/>
+      <c r="CF7" s="116"/>
+      <c r="CG7" s="116"/>
+      <c r="CH7" s="116"/>
+      <c r="CI7" s="116"/>
+      <c r="CJ7" s="116"/>
+      <c r="CK7" s="116"/>
       <c r="CL7" s="48" t="s">
         <v>377</v>
       </c>
@@ -13654,10 +13524,10 @@
         <f>SUBSTITUTE(SUBSTITUTE(J11," ",""),"-","")</f>
         <v>378206SAT310M6</v>
       </c>
-      <c r="AN11" s="108" t="s">
+      <c r="AN11" s="107" t="s">
         <v>500</v>
       </c>
-      <c r="AO11" s="108" t="s">
+      <c r="AO11" s="107" t="s">
         <v>506</v>
       </c>
       <c r="AP11" s="51" t="s">
@@ -13684,7 +13554,7 @@
       <c r="AV11" s="51" t="s">
         <v>453</v>
       </c>
-      <c r="AW11" s="106" t="s">
+      <c r="AW11" s="107" t="s">
         <v>527</v>
       </c>
       <c r="AX11" s="54" t="str">
@@ -13859,7 +13729,7 @@
         <f>SUBSTITUTE(J11," ","")</f>
         <v>37820-6SA-T310-M6</v>
       </c>
-      <c r="CT11" s="108" t="s">
+      <c r="CT11" s="107" t="s">
         <v>471</v>
       </c>
       <c r="CU11" s="51" t="s">
@@ -13993,7 +13863,7 @@
       <c r="AV12" s="47" t="s">
         <v>453</v>
       </c>
-      <c r="AW12" s="107" t="s">
+      <c r="AW12" s="106" t="s">
         <v>527</v>
       </c>
       <c r="AX12" s="47" t="s">
@@ -14513,7 +14383,7 @@
     <row r="14" spans="1:104" s="42" customFormat="1" ht="44.25" customHeight="1" collapsed="1">
       <c r="A14" s="45"/>
       <c r="B14" s="51">
-        <f t="shared" ref="B14:B55" si="56">B11+1</f>
+        <f t="shared" ref="B14:B34" si="56">B11+1</f>
         <v>2</v>
       </c>
       <c r="C14" s="52">
@@ -14629,10 +14499,10 @@
         <f>SUBSTITUTE(SUBSTITUTE(J14," ",""),"-","")</f>
         <v>378206SAT410M6</v>
       </c>
-      <c r="AN14" s="108" t="s">
+      <c r="AN14" s="107" t="s">
         <v>501</v>
       </c>
-      <c r="AO14" s="108" t="s">
+      <c r="AO14" s="107" t="s">
         <v>507</v>
       </c>
       <c r="AP14" s="51" t="s">
@@ -14659,7 +14529,7 @@
       <c r="AV14" s="51" t="s">
         <v>453</v>
       </c>
-      <c r="AW14" s="106" t="s">
+      <c r="AW14" s="107" t="s">
         <v>528</v>
       </c>
       <c r="AX14" s="54" t="str">
@@ -14834,7 +14704,7 @@
         <f>SUBSTITUTE(J14," ","")</f>
         <v>37820-6SA-T410-M6</v>
       </c>
-      <c r="CT14" s="108" t="s">
+      <c r="CT14" s="107" t="s">
         <v>472</v>
       </c>
       <c r="CU14" s="51" t="s">
@@ -14969,7 +14839,7 @@
       <c r="AV15" s="47" t="s">
         <v>453</v>
       </c>
-      <c r="AW15" s="107" t="s">
+      <c r="AW15" s="106" t="s">
         <v>528</v>
       </c>
       <c r="AX15" s="47" t="s">
@@ -15606,10 +15476,10 @@
         <f>SUBSTITUTE(SUBSTITUTE(J17," ",""),"-","")</f>
         <v>378206SAT810M6</v>
       </c>
-      <c r="AN17" s="108" t="s">
+      <c r="AN17" s="107" t="s">
         <v>502</v>
       </c>
-      <c r="AO17" s="108" t="s">
+      <c r="AO17" s="107" t="s">
         <v>508</v>
       </c>
       <c r="AP17" s="51" t="s">
@@ -15636,7 +15506,7 @@
       <c r="AV17" s="51" t="s">
         <v>453</v>
       </c>
-      <c r="AW17" s="106" t="s">
+      <c r="AW17" s="107" t="s">
         <v>529</v>
       </c>
       <c r="AX17" s="54" t="str">
@@ -15811,7 +15681,7 @@
         <f>SUBSTITUTE(J17," ","")</f>
         <v>37820-6SA-T810-M6</v>
       </c>
-      <c r="CT17" s="108" t="s">
+      <c r="CT17" s="107" t="s">
         <v>473</v>
       </c>
       <c r="CU17" s="51" t="s">
@@ -15946,7 +15816,7 @@
       <c r="AV18" s="47" t="s">
         <v>453</v>
       </c>
-      <c r="AW18" s="107" t="s">
+      <c r="AW18" s="106" t="s">
         <v>529</v>
       </c>
       <c r="AX18" s="47" t="s">
@@ -16583,10 +16453,10 @@
         <f>SUBSTITUTE(SUBSTITUTE(J20," ",""),"-","")</f>
         <v>378206SAT910M6</v>
       </c>
-      <c r="AN20" s="108" t="s">
+      <c r="AN20" s="107" t="s">
         <v>503</v>
       </c>
-      <c r="AO20" s="108" t="s">
+      <c r="AO20" s="107" t="s">
         <v>509</v>
       </c>
       <c r="AP20" s="51" t="s">
@@ -16613,7 +16483,7 @@
       <c r="AV20" s="51" t="s">
         <v>453</v>
       </c>
-      <c r="AW20" s="106" t="s">
+      <c r="AW20" s="107" t="s">
         <v>530</v>
       </c>
       <c r="AX20" s="54" t="str">
@@ -16788,7 +16658,7 @@
         <f>SUBSTITUTE(J20," ","")</f>
         <v>37820-6SA-T910-M6</v>
       </c>
-      <c r="CT20" s="108" t="s">
+      <c r="CT20" s="107" t="s">
         <v>474</v>
       </c>
       <c r="CU20" s="51" t="s">
@@ -16923,7 +16793,7 @@
       <c r="AV21" s="47" t="s">
         <v>453</v>
       </c>
-      <c r="AW21" s="107" t="s">
+      <c r="AW21" s="106" t="s">
         <v>530</v>
       </c>
       <c r="AX21" s="47" t="s">
@@ -17560,10 +17430,10 @@
         <f>SUBSTITUTE(SUBSTITUTE(J23," ",""),"-","")</f>
         <v>378206SATA10M6</v>
       </c>
-      <c r="AN23" s="108" t="s">
+      <c r="AN23" s="107" t="s">
         <v>504</v>
       </c>
-      <c r="AO23" s="108" t="s">
+      <c r="AO23" s="107" t="s">
         <v>510</v>
       </c>
       <c r="AP23" s="51" t="s">
@@ -17590,7 +17460,7 @@
       <c r="AV23" s="51" t="s">
         <v>453</v>
       </c>
-      <c r="AW23" s="106" t="s">
+      <c r="AW23" s="107" t="s">
         <v>531</v>
       </c>
       <c r="AX23" s="54" t="str">
@@ -17765,7 +17635,7 @@
         <f>SUBSTITUTE(J23," ","")</f>
         <v>37820-6SA-TA10-M6</v>
       </c>
-      <c r="CT23" s="108" t="s">
+      <c r="CT23" s="107" t="s">
         <v>475</v>
       </c>
       <c r="CU23" s="51" t="s">
@@ -17900,7 +17770,7 @@
       <c r="AV24" s="47" t="s">
         <v>453</v>
       </c>
-      <c r="AW24" s="107" t="s">
+      <c r="AW24" s="106" t="s">
         <v>531</v>
       </c>
       <c r="AX24" s="47" t="s">
@@ -18537,10 +18407,10 @@
         <f>SUBSTITUTE(SUBSTITUTE(J26," ",""),"-","")</f>
         <v>378206SATB10M6</v>
       </c>
-      <c r="AN26" s="108" t="s">
+      <c r="AN26" s="107" t="s">
         <v>505</v>
       </c>
-      <c r="AO26" s="108" t="s">
+      <c r="AO26" s="107" t="s">
         <v>511</v>
       </c>
       <c r="AP26" s="51" t="s">
@@ -18567,7 +18437,7 @@
       <c r="AV26" s="51" t="s">
         <v>453</v>
       </c>
-      <c r="AW26" s="106" t="s">
+      <c r="AW26" s="107" t="s">
         <v>532</v>
       </c>
       <c r="AX26" s="54" t="str">
@@ -18742,7 +18612,7 @@
         <f>SUBSTITUTE(J26," ","")</f>
         <v>37820-6SA-TB10-M6</v>
       </c>
-      <c r="CT26" s="108" t="s">
+      <c r="CT26" s="107" t="s">
         <v>476</v>
       </c>
       <c r="CU26" s="51" t="s">
@@ -18877,7 +18747,7 @@
       <c r="AV27" s="47" t="s">
         <v>453</v>
       </c>
-      <c r="AW27" s="107" t="s">
+      <c r="AW27" s="106" t="s">
         <v>532</v>
       </c>
       <c r="AX27" s="47" t="s">
@@ -19404,7 +19274,7 @@
         <v>7</v>
       </c>
       <c r="C29" s="52">
-        <v>46324.200844907406</v>
+        <v>46324.656747685185</v>
       </c>
       <c r="D29" s="51" t="s">
         <v>254</v>
@@ -19435,7 +19305,7 @@
         <v>442</v>
       </c>
       <c r="S29" s="51" t="s">
-        <v>443</v>
+        <v>558</v>
       </c>
       <c r="T29" s="51" t="s">
         <v>39</v>
@@ -19462,31 +19332,31 @@
         <v>444</v>
       </c>
       <c r="AB29" s="51" t="s">
-        <v>563</v>
+        <v>559</v>
       </c>
       <c r="AC29" s="51">
-        <v>66</v>
+        <v>93</v>
       </c>
       <c r="AD29" s="51" t="s">
         <v>446</v>
       </c>
       <c r="AE29" s="51">
-        <v>1.2</v>
-      </c>
-      <c r="AF29" s="51" t="s">
-        <v>558</v>
+        <v>1.5</v>
+      </c>
+      <c r="AF29" s="51">
+        <v>2028</v>
       </c>
       <c r="AG29" s="51" t="s">
-        <v>433</v>
+        <v>560</v>
       </c>
       <c r="AH29" s="51" t="s">
-        <v>559</v>
+        <v>37</v>
       </c>
       <c r="AI29" s="51" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AJ29" s="51" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="AK29" s="51">
         <v>4</v>
@@ -19496,24 +19366,24 @@
       </c>
       <c r="AM29" s="54" t="str">
         <f>SUBSTITUTE(SUBSTITUTE(J29," ",""),"-","")</f>
-        <v>378206SATD10M6</v>
-      </c>
-      <c r="AN29" s="108" t="s">
-        <v>561</v>
-      </c>
-      <c r="AO29" s="108" t="s">
+        <v>378206WZM610M6</v>
+      </c>
+      <c r="AN29" s="107" t="s">
         <v>562</v>
       </c>
+      <c r="AO29" s="107" t="s">
+        <v>563</v>
+      </c>
       <c r="AP29" s="51" t="s">
-        <v>512</v>
+        <v>558</v>
       </c>
       <c r="AQ29" s="54" t="str">
         <f>SUBSTITUTE(J29," ","")</f>
-        <v>37820-6SA-TD10-M6</v>
+        <v>37820-6WZ-M610-M6</v>
       </c>
       <c r="AR29" s="54" t="str">
         <f>IF(RIGHT(SUBSTITUTE(J29," ",""),4)="0-M6",LEFT(SUBSTITUTE(J29," ",""),LEN(SUBSTITUTE(J29," ",""))-4),SUBSTITUTE(J29," ",""))</f>
-        <v>37820-6SA-TD1</v>
+        <v>37820-6WZ-M61</v>
       </c>
       <c r="AS29" s="54">
         <f>K29</f>
@@ -19526,38 +19396,36 @@
       <c r="AV29" s="51" t="s">
         <v>453</v>
       </c>
-      <c r="AW29" s="106"/>
+      <c r="AW29" s="107"/>
       <c r="AX29" s="54">
         <f>K29</f>
         <v>0</v>
       </c>
-      <c r="AY29" s="51" t="s">
-        <v>454</v>
-      </c>
+      <c r="AY29" s="51"/>
       <c r="AZ29" s="51"/>
       <c r="BA29" s="51"/>
       <c r="BB29" s="51"/>
       <c r="BC29" s="51" t="s">
-        <v>490</v>
+        <v>564</v>
       </c>
       <c r="BD29" s="54" t="str">
         <f>AP29</f>
-        <v>MG1CA020-2.30</v>
+        <v>MG1CS022</v>
       </c>
       <c r="BE29" s="51" t="s">
-        <v>563</v>
+        <v>559</v>
       </c>
       <c r="BF29" s="51" t="s">
-        <v>461</v>
+        <v>565</v>
       </c>
       <c r="BG29" s="51" t="s">
-        <v>462</v>
+        <v>566</v>
       </c>
       <c r="BH29" s="51" t="s">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="BI29" s="51" t="s">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="BJ29" s="54" t="str">
         <f t="shared" si="57"/>
@@ -19589,11 +19457,11 @@
       </c>
       <c r="BQ29" s="54" t="str">
         <f t="shared" si="57"/>
-        <v>S</v>
+        <v>W</v>
       </c>
       <c r="BR29" s="54" t="str">
         <f t="shared" si="57"/>
-        <v>A</v>
+        <v>Z</v>
       </c>
       <c r="BS29" s="54" t="str">
         <f t="shared" si="57"/>
@@ -19601,11 +19469,11 @@
       </c>
       <c r="BT29" s="54" t="str">
         <f t="shared" si="57"/>
-        <v>T</v>
+        <v>M</v>
       </c>
       <c r="BU29" s="54" t="str">
         <f t="shared" si="57"/>
-        <v>D</v>
+        <v>6</v>
       </c>
       <c r="BV29" s="54" t="str">
         <f t="shared" si="57"/>
@@ -19645,11 +19513,11 @@
       </c>
       <c r="CE29" s="55" t="str">
         <f t="shared" ref="CE29:CE30" si="150">DEC2HEX(CODE(BQ29),2)</f>
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="CF29" s="55" t="str">
         <f t="shared" ref="CF29:CF30" si="151">DEC2HEX(CODE(BR29),2)</f>
-        <v>41</v>
+        <v>5A</v>
       </c>
       <c r="CG29" s="55" t="str">
         <f t="shared" ref="CG29:CG30" si="152">DEC2HEX(CODE(BS29),2)</f>
@@ -19657,11 +19525,11 @@
       </c>
       <c r="CH29" s="55" t="str">
         <f t="shared" ref="CH29:CH30" si="153">DEC2HEX(CODE(BT29),2)</f>
-        <v>54</v>
+        <v>4D</v>
       </c>
       <c r="CI29" s="55" t="str">
         <f t="shared" ref="CI29:CI30" si="154">DEC2HEX(CODE(BU29),2)</f>
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="CJ29" s="55" t="str">
         <f t="shared" ref="CJ29:CJ30" si="155">DEC2HEX(CODE(BV29),2)</f>
@@ -19673,49 +19541,47 @@
       </c>
       <c r="CL29" s="54" t="str">
         <f>BX29&amp;BY29&amp;BZ29&amp;CA29&amp;CB29&amp;CC29&amp;CD29&amp;CE29&amp;CF29&amp;CG29&amp;CH29&amp;CI29&amp;CJ29&amp;CK29</f>
-        <v>33373830352D3653412D54443130</v>
+        <v>33373830352D36575A2D4D363130</v>
       </c>
       <c r="CM29" s="104" t="s">
         <v>513</v>
       </c>
       <c r="CN29" s="51" t="s">
-        <v>470</v>
+        <v>569</v>
       </c>
       <c r="CO29" s="51" t="s">
-        <v>240</v>
+        <v>308</v>
       </c>
       <c r="CP29" s="51" t="s">
-        <v>240</v>
-      </c>
-      <c r="CQ29" s="51" t="s">
-        <v>240</v>
-      </c>
-      <c r="CR29" s="56" t="s">
-        <v>240</v>
-      </c>
+        <v>308</v>
+      </c>
+      <c r="CQ29" s="107" t="s">
+        <v>570</v>
+      </c>
+      <c r="CR29" s="56"/>
       <c r="CS29" s="54" t="str">
         <f>SUBSTITUTE(J29," ","")</f>
-        <v>37820-6SA-TD10-M6</v>
-      </c>
-      <c r="CT29" s="108" t="s">
-        <v>566</v>
+        <v>37820-6WZ-M610-M6</v>
+      </c>
+      <c r="CT29" s="107" t="s">
+        <v>571</v>
       </c>
       <c r="CU29" s="51" t="s">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="CV29" s="51" t="s">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="CW29" s="56"/>
       <c r="CX29" s="51" t="str">
         <f>AR29</f>
-        <v>37820-6SA-TD1</v>
+        <v>37820-6WZ-M61</v>
       </c>
       <c r="CY29" s="51" t="s">
-        <v>477</v>
+        <v>572</v>
       </c>
       <c r="CZ29" s="51" t="s">
-        <v>567</v>
+        <v>572</v>
       </c>
     </row>
     <row r="30" spans="1:104" s="42" customFormat="1" ht="44.25" hidden="1" customHeight="1" outlineLevel="1" collapsed="1">
@@ -19772,7 +19638,7 @@
       <c r="AT30" s="47"/>
       <c r="AU30" s="47"/>
       <c r="AV30" s="47"/>
-      <c r="AW30" s="107"/>
+      <c r="AW30" s="106"/>
       <c r="AX30" s="47"/>
       <c r="AY30" s="47"/>
       <c r="AZ30" s="47"/>
@@ -20091,7 +19957,7 @@
       </c>
       <c r="AY31" s="47" t="b">
         <f t="shared" si="158"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ31" s="47" t="b">
         <f t="shared" si="158"/>
@@ -20271,7 +20137,7 @@
         <v>8</v>
       </c>
       <c r="C32" s="52">
-        <v>46324.200868055559</v>
+        <v>46324.656793981485</v>
       </c>
       <c r="D32" s="51" t="s">
         <v>254</v>
@@ -20284,7 +20150,7 @@
       </c>
       <c r="I32" s="105"/>
       <c r="J32" s="53" t="s">
-        <v>568</v>
+        <v>573</v>
       </c>
       <c r="K32" s="53"/>
       <c r="L32" s="51"/>
@@ -20302,7 +20168,7 @@
         <v>442</v>
       </c>
       <c r="S32" s="51" t="s">
-        <v>443</v>
+        <v>558</v>
       </c>
       <c r="T32" s="51" t="s">
         <v>39</v>
@@ -20329,31 +20195,31 @@
         <v>444</v>
       </c>
       <c r="AB32" s="51" t="s">
-        <v>563</v>
+        <v>559</v>
       </c>
       <c r="AC32" s="51">
-        <v>66</v>
+        <v>93</v>
       </c>
       <c r="AD32" s="51" t="s">
         <v>446</v>
       </c>
       <c r="AE32" s="51">
-        <v>1.2</v>
-      </c>
-      <c r="AF32" s="51" t="s">
-        <v>558</v>
+        <v>1.5</v>
+      </c>
+      <c r="AF32" s="51">
+        <v>2028</v>
       </c>
       <c r="AG32" s="51" t="s">
-        <v>433</v>
+        <v>560</v>
       </c>
       <c r="AH32" s="51" t="s">
-        <v>559</v>
+        <v>37</v>
       </c>
       <c r="AI32" s="51" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AJ32" s="51" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="AK32" s="51">
         <v>4</v>
@@ -20363,24 +20229,24 @@
       </c>
       <c r="AM32" s="54" t="str">
         <f>SUBSTITUTE(SUBSTITUTE(J32," ",""),"-","")</f>
-        <v>378206SATE10M6</v>
-      </c>
-      <c r="AN32" s="108" t="s">
-        <v>569</v>
-      </c>
-      <c r="AO32" s="108" t="s">
-        <v>570</v>
+        <v>378206WZM710M6</v>
+      </c>
+      <c r="AN32" s="107" t="s">
+        <v>574</v>
+      </c>
+      <c r="AO32" s="107" t="s">
+        <v>575</v>
       </c>
       <c r="AP32" s="51" t="s">
-        <v>512</v>
+        <v>558</v>
       </c>
       <c r="AQ32" s="54" t="str">
         <f>SUBSTITUTE(J32," ","")</f>
-        <v>37820-6SA-TE10-M6</v>
+        <v>37820-6WZ-M710-M6</v>
       </c>
       <c r="AR32" s="54" t="str">
         <f>IF(RIGHT(SUBSTITUTE(J32," ",""),4)="0-M6",LEFT(SUBSTITUTE(J32," ",""),LEN(SUBSTITUTE(J32," ",""))-4),SUBSTITUTE(J32," ",""))</f>
-        <v>37820-6SA-TE1</v>
+        <v>37820-6WZ-M71</v>
       </c>
       <c r="AS32" s="54">
         <f>K32</f>
@@ -20393,41 +20259,39 @@
       <c r="AV32" s="51" t="s">
         <v>453</v>
       </c>
-      <c r="AW32" s="106"/>
+      <c r="AW32" s="107"/>
       <c r="AX32" s="54">
         <f>K32</f>
         <v>0</v>
       </c>
-      <c r="AY32" s="51" t="s">
-        <v>454</v>
-      </c>
+      <c r="AY32" s="51"/>
       <c r="AZ32" s="51"/>
       <c r="BA32" s="51"/>
       <c r="BB32" s="51"/>
       <c r="BC32" s="51" t="s">
-        <v>490</v>
+        <v>564</v>
       </c>
       <c r="BD32" s="54" t="str">
         <f>AP32</f>
-        <v>MG1CA020-2.30</v>
+        <v>MG1CS022</v>
       </c>
       <c r="BE32" s="51" t="s">
-        <v>563</v>
+        <v>559</v>
       </c>
       <c r="BF32" s="51" t="s">
-        <v>461</v>
+        <v>565</v>
       </c>
       <c r="BG32" s="51" t="s">
-        <v>462</v>
+        <v>566</v>
       </c>
       <c r="BH32" s="51" t="s">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="BI32" s="51" t="s">
-        <v>571</v>
+        <v>576</v>
       </c>
       <c r="BJ32" s="54" t="str">
-        <f t="shared" ref="BJ32:BW47" si="162">MID($BI32,BJ$6,1)</f>
+        <f t="shared" ref="BJ32:BW34" si="162">MID($BI32,BJ$6,1)</f>
         <v>3</v>
       </c>
       <c r="BK32" s="54" t="str">
@@ -20456,11 +20320,11 @@
       </c>
       <c r="BQ32" s="54" t="str">
         <f t="shared" si="162"/>
-        <v>S</v>
+        <v>W</v>
       </c>
       <c r="BR32" s="54" t="str">
         <f t="shared" si="162"/>
-        <v>A</v>
+        <v>Z</v>
       </c>
       <c r="BS32" s="54" t="str">
         <f t="shared" si="162"/>
@@ -20468,11 +20332,11 @@
       </c>
       <c r="BT32" s="54" t="str">
         <f t="shared" si="162"/>
-        <v>T</v>
+        <v>M</v>
       </c>
       <c r="BU32" s="54" t="str">
         <f t="shared" si="162"/>
-        <v>E</v>
+        <v>7</v>
       </c>
       <c r="BV32" s="54" t="str">
         <f t="shared" si="162"/>
@@ -20512,11 +20376,11 @@
       </c>
       <c r="CE32" s="55" t="str">
         <f t="shared" ref="CE32:CE33" si="169">DEC2HEX(CODE(BQ32),2)</f>
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="CF32" s="55" t="str">
         <f t="shared" ref="CF32:CF33" si="170">DEC2HEX(CODE(BR32),2)</f>
-        <v>41</v>
+        <v>5A</v>
       </c>
       <c r="CG32" s="55" t="str">
         <f t="shared" ref="CG32:CG33" si="171">DEC2HEX(CODE(BS32),2)</f>
@@ -20524,11 +20388,11 @@
       </c>
       <c r="CH32" s="55" t="str">
         <f t="shared" ref="CH32:CH33" si="172">DEC2HEX(CODE(BT32),2)</f>
-        <v>54</v>
+        <v>4D</v>
       </c>
       <c r="CI32" s="55" t="str">
         <f t="shared" ref="CI32:CI33" si="173">DEC2HEX(CODE(BU32),2)</f>
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="CJ32" s="55" t="str">
         <f t="shared" ref="CJ32:CJ33" si="174">DEC2HEX(CODE(BV32),2)</f>
@@ -20540,49 +20404,47 @@
       </c>
       <c r="CL32" s="54" t="str">
         <f>BX32&amp;BY32&amp;BZ32&amp;CA32&amp;CB32&amp;CC32&amp;CD32&amp;CE32&amp;CF32&amp;CG32&amp;CH32&amp;CI32&amp;CJ32&amp;CK32</f>
-        <v>33373830352D3653412D54453130</v>
+        <v>33373830352D36575A2D4D373130</v>
       </c>
       <c r="CM32" s="104" t="s">
         <v>513</v>
       </c>
       <c r="CN32" s="51" t="s">
-        <v>470</v>
+        <v>569</v>
       </c>
       <c r="CO32" s="51" t="s">
-        <v>240</v>
+        <v>308</v>
       </c>
       <c r="CP32" s="51" t="s">
-        <v>240</v>
-      </c>
-      <c r="CQ32" s="51" t="s">
-        <v>240</v>
-      </c>
-      <c r="CR32" s="56" t="s">
-        <v>240</v>
-      </c>
+        <v>308</v>
+      </c>
+      <c r="CQ32" s="107" t="s">
+        <v>570</v>
+      </c>
+      <c r="CR32" s="56"/>
       <c r="CS32" s="54" t="str">
         <f>SUBSTITUTE(J32," ","")</f>
-        <v>37820-6SA-TE10-M6</v>
-      </c>
-      <c r="CT32" s="108" t="s">
-        <v>572</v>
+        <v>37820-6WZ-M710-M6</v>
+      </c>
+      <c r="CT32" s="107" t="s">
+        <v>577</v>
       </c>
       <c r="CU32" s="51" t="s">
-        <v>571</v>
+        <v>576</v>
       </c>
       <c r="CV32" s="51" t="s">
-        <v>571</v>
+        <v>576</v>
       </c>
       <c r="CW32" s="56"/>
       <c r="CX32" s="51" t="str">
         <f>AR32</f>
-        <v>37820-6SA-TE1</v>
+        <v>37820-6WZ-M71</v>
       </c>
       <c r="CY32" s="51" t="s">
-        <v>479</v>
+        <v>572</v>
       </c>
       <c r="CZ32" s="51" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
     </row>
     <row r="33" spans="1:104" s="42" customFormat="1" ht="44.25" hidden="1" customHeight="1" outlineLevel="1" collapsed="1">
@@ -20639,7 +20501,7 @@
       <c r="AT33" s="47"/>
       <c r="AU33" s="47"/>
       <c r="AV33" s="47"/>
-      <c r="AW33" s="107"/>
+      <c r="AW33" s="106"/>
       <c r="AX33" s="47"/>
       <c r="AY33" s="47"/>
       <c r="AZ33" s="47"/>
@@ -20958,7 +20820,7 @@
       </c>
       <c r="AY34" s="47" t="b">
         <f t="shared" si="176"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ34" s="47" t="b">
         <f t="shared" si="176"/>
@@ -21128,6075 +20990,6 @@
         <v>264</v>
       </c>
       <c r="CZ34" s="47" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="35" spans="1:104" s="42" customFormat="1" ht="44.25" customHeight="1" collapsed="1">
-      <c r="A35" s="45"/>
-      <c r="B35" s="51">
-        <f t="shared" si="56"/>
-        <v>9</v>
-      </c>
-      <c r="C35" s="52">
-        <v>46324.200891203705</v>
-      </c>
-      <c r="D35" s="51" t="s">
-        <v>254</v>
-      </c>
-      <c r="E35" s="51"/>
-      <c r="F35" s="51"/>
-      <c r="G35" s="104"/>
-      <c r="H35" s="51" t="s">
-        <v>557</v>
-      </c>
-      <c r="I35" s="105"/>
-      <c r="J35" s="53" t="s">
-        <v>574</v>
-      </c>
-      <c r="K35" s="53"/>
-      <c r="L35" s="51"/>
-      <c r="M35" s="51"/>
-      <c r="N35" s="51"/>
-      <c r="O35" s="51" t="str">
-        <f>IF(COUNTIF(C37:CZ37,"FALSE")&gt;0,"NG","OK")</f>
-        <v>NG</v>
-      </c>
-      <c r="P35" s="51"/>
-      <c r="Q35" s="51" t="s">
-        <v>441</v>
-      </c>
-      <c r="R35" s="51" t="s">
-        <v>442</v>
-      </c>
-      <c r="S35" s="51" t="s">
-        <v>443</v>
-      </c>
-      <c r="T35" s="51" t="s">
-        <v>39</v>
-      </c>
-      <c r="U35" s="51" t="s">
-        <v>28</v>
-      </c>
-      <c r="V35" s="51" t="s">
-        <v>38</v>
-      </c>
-      <c r="W35" s="51" t="s">
-        <v>79</v>
-      </c>
-      <c r="X35" s="51" t="s">
-        <v>444</v>
-      </c>
-      <c r="Y35" s="51" t="s">
-        <v>444</v>
-      </c>
-      <c r="Z35" s="51" t="s">
-        <v>444</v>
-      </c>
-      <c r="AA35" s="51" t="s">
-        <v>444</v>
-      </c>
-      <c r="AB35" s="51" t="s">
-        <v>563</v>
-      </c>
-      <c r="AC35" s="51">
-        <v>66</v>
-      </c>
-      <c r="AD35" s="51" t="s">
-        <v>446</v>
-      </c>
-      <c r="AE35" s="51">
-        <v>1.2</v>
-      </c>
-      <c r="AF35" s="51" t="s">
-        <v>558</v>
-      </c>
-      <c r="AG35" s="51" t="s">
-        <v>433</v>
-      </c>
-      <c r="AH35" s="51" t="s">
-        <v>559</v>
-      </c>
-      <c r="AI35" s="51" t="s">
-        <v>448</v>
-      </c>
-      <c r="AJ35" s="51" t="s">
-        <v>560</v>
-      </c>
-      <c r="AK35" s="51">
-        <v>4</v>
-      </c>
-      <c r="AL35" s="51">
-        <v>159</v>
-      </c>
-      <c r="AM35" s="54" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(J35," ",""),"-","")</f>
-        <v>378206SATF10M6</v>
-      </c>
-      <c r="AN35" s="108" t="s">
-        <v>575</v>
-      </c>
-      <c r="AO35" s="108" t="s">
-        <v>576</v>
-      </c>
-      <c r="AP35" s="51" t="s">
-        <v>512</v>
-      </c>
-      <c r="AQ35" s="54" t="str">
-        <f>SUBSTITUTE(J35," ","")</f>
-        <v>37820-6SA-TF10-M6</v>
-      </c>
-      <c r="AR35" s="54" t="str">
-        <f>IF(RIGHT(SUBSTITUTE(J35," ",""),4)="0-M6",LEFT(SUBSTITUTE(J35," ",""),LEN(SUBSTITUTE(J35," ",""))-4),SUBSTITUTE(J35," ",""))</f>
-        <v>37820-6SA-TF1</v>
-      </c>
-      <c r="AS35" s="54">
-        <f>K35</f>
-        <v>0</v>
-      </c>
-      <c r="AT35" s="51"/>
-      <c r="AU35" s="51" t="s">
-        <v>452</v>
-      </c>
-      <c r="AV35" s="51" t="s">
-        <v>453</v>
-      </c>
-      <c r="AW35" s="106"/>
-      <c r="AX35" s="54">
-        <f>K35</f>
-        <v>0</v>
-      </c>
-      <c r="AY35" s="51" t="s">
-        <v>454</v>
-      </c>
-      <c r="AZ35" s="51"/>
-      <c r="BA35" s="51"/>
-      <c r="BB35" s="51"/>
-      <c r="BC35" s="51" t="s">
-        <v>490</v>
-      </c>
-      <c r="BD35" s="54" t="str">
-        <f>AP35</f>
-        <v>MG1CA020-2.30</v>
-      </c>
-      <c r="BE35" s="51" t="s">
-        <v>563</v>
-      </c>
-      <c r="BF35" s="51" t="s">
-        <v>461</v>
-      </c>
-      <c r="BG35" s="51" t="s">
-        <v>462</v>
-      </c>
-      <c r="BH35" s="51" t="s">
-        <v>564</v>
-      </c>
-      <c r="BI35" s="51" t="s">
-        <v>577</v>
-      </c>
-      <c r="BJ35" s="54" t="str">
-        <f t="shared" si="162"/>
-        <v>3</v>
-      </c>
-      <c r="BK35" s="54" t="str">
-        <f t="shared" si="162"/>
-        <v>7</v>
-      </c>
-      <c r="BL35" s="54" t="str">
-        <f t="shared" si="162"/>
-        <v>8</v>
-      </c>
-      <c r="BM35" s="54" t="str">
-        <f t="shared" si="162"/>
-        <v>0</v>
-      </c>
-      <c r="BN35" s="54" t="str">
-        <f t="shared" si="162"/>
-        <v>5</v>
-      </c>
-      <c r="BO35" s="54" t="str">
-        <f t="shared" si="162"/>
-        <v>-</v>
-      </c>
-      <c r="BP35" s="54" t="str">
-        <f t="shared" si="162"/>
-        <v>6</v>
-      </c>
-      <c r="BQ35" s="54" t="str">
-        <f t="shared" si="162"/>
-        <v>S</v>
-      </c>
-      <c r="BR35" s="54" t="str">
-        <f t="shared" si="162"/>
-        <v>A</v>
-      </c>
-      <c r="BS35" s="54" t="str">
-        <f t="shared" si="162"/>
-        <v>-</v>
-      </c>
-      <c r="BT35" s="54" t="str">
-        <f t="shared" si="162"/>
-        <v>T</v>
-      </c>
-      <c r="BU35" s="54" t="str">
-        <f t="shared" si="162"/>
-        <v>F</v>
-      </c>
-      <c r="BV35" s="54" t="str">
-        <f t="shared" si="162"/>
-        <v>1</v>
-      </c>
-      <c r="BW35" s="54" t="str">
-        <f t="shared" si="162"/>
-        <v>0</v>
-      </c>
-      <c r="BX35" s="55" t="str">
-        <f>DEC2HEX(CODE(BJ35),2)</f>
-        <v>33</v>
-      </c>
-      <c r="BY35" s="55" t="str">
-        <f t="shared" ref="BY35:BY36" si="180">DEC2HEX(CODE(BK35),2)</f>
-        <v>37</v>
-      </c>
-      <c r="BZ35" s="55" t="str">
-        <f t="shared" ref="BZ35:BZ36" si="181">DEC2HEX(CODE(BL35),2)</f>
-        <v>38</v>
-      </c>
-      <c r="CA35" s="55" t="str">
-        <f t="shared" ref="CA35:CA36" si="182">DEC2HEX(CODE(BM35),2)</f>
-        <v>30</v>
-      </c>
-      <c r="CB35" s="55" t="str">
-        <f t="shared" ref="CB35:CB36" si="183">DEC2HEX(CODE(BN35),2)</f>
-        <v>35</v>
-      </c>
-      <c r="CC35" s="55" t="str">
-        <f t="shared" ref="CC35:CC36" si="184">DEC2HEX(CODE(BO35),2)</f>
-        <v>2D</v>
-      </c>
-      <c r="CD35" s="55" t="str">
-        <f t="shared" ref="CD35:CD36" si="185">DEC2HEX(CODE(BP35),2)</f>
-        <v>36</v>
-      </c>
-      <c r="CE35" s="55" t="str">
-        <f t="shared" ref="CE35:CE36" si="186">DEC2HEX(CODE(BQ35),2)</f>
-        <v>53</v>
-      </c>
-      <c r="CF35" s="55" t="str">
-        <f t="shared" ref="CF35:CF36" si="187">DEC2HEX(CODE(BR35),2)</f>
-        <v>41</v>
-      </c>
-      <c r="CG35" s="55" t="str">
-        <f t="shared" ref="CG35:CG36" si="188">DEC2HEX(CODE(BS35),2)</f>
-        <v>2D</v>
-      </c>
-      <c r="CH35" s="55" t="str">
-        <f t="shared" ref="CH35:CH36" si="189">DEC2HEX(CODE(BT35),2)</f>
-        <v>54</v>
-      </c>
-      <c r="CI35" s="55" t="str">
-        <f t="shared" ref="CI35:CI36" si="190">DEC2HEX(CODE(BU35),2)</f>
-        <v>46</v>
-      </c>
-      <c r="CJ35" s="55" t="str">
-        <f t="shared" ref="CJ35:CJ36" si="191">DEC2HEX(CODE(BV35),2)</f>
-        <v>31</v>
-      </c>
-      <c r="CK35" s="55" t="str">
-        <f t="shared" ref="CK35:CK36" si="192">DEC2HEX(CODE(BW35),2)</f>
-        <v>30</v>
-      </c>
-      <c r="CL35" s="54" t="str">
-        <f>BX35&amp;BY35&amp;BZ35&amp;CA35&amp;CB35&amp;CC35&amp;CD35&amp;CE35&amp;CF35&amp;CG35&amp;CH35&amp;CI35&amp;CJ35&amp;CK35</f>
-        <v>33373830352D3653412D54463130</v>
-      </c>
-      <c r="CM35" s="104" t="s">
-        <v>513</v>
-      </c>
-      <c r="CN35" s="51" t="s">
-        <v>470</v>
-      </c>
-      <c r="CO35" s="51" t="s">
-        <v>240</v>
-      </c>
-      <c r="CP35" s="51" t="s">
-        <v>240</v>
-      </c>
-      <c r="CQ35" s="51" t="s">
-        <v>240</v>
-      </c>
-      <c r="CR35" s="56" t="s">
-        <v>240</v>
-      </c>
-      <c r="CS35" s="54" t="str">
-        <f>SUBSTITUTE(J35," ","")</f>
-        <v>37820-6SA-TF10-M6</v>
-      </c>
-      <c r="CT35" s="108" t="s">
-        <v>578</v>
-      </c>
-      <c r="CU35" s="51" t="s">
-        <v>577</v>
-      </c>
-      <c r="CV35" s="51" t="s">
-        <v>577</v>
-      </c>
-      <c r="CW35" s="56"/>
-      <c r="CX35" s="51" t="str">
-        <f>AR35</f>
-        <v>37820-6SA-TF1</v>
-      </c>
-      <c r="CY35" s="51" t="s">
-        <v>485</v>
-      </c>
-      <c r="CZ35" s="51" t="s">
-        <v>579</v>
-      </c>
-    </row>
-    <row r="36" spans="1:104" s="42" customFormat="1" ht="44.25" hidden="1" customHeight="1" outlineLevel="1" collapsed="1">
-      <c r="A36" s="45"/>
-      <c r="B36" s="47">
-        <f t="shared" si="56"/>
-        <v>9</v>
-      </c>
-      <c r="C36" s="57"/>
-      <c r="D36" s="47" t="s">
-        <v>245</v>
-      </c>
-      <c r="E36" s="47"/>
-      <c r="F36" s="47"/>
-      <c r="G36" s="57"/>
-      <c r="H36" s="47"/>
-      <c r="I36" s="47"/>
-      <c r="J36" s="47"/>
-      <c r="K36" s="47"/>
-      <c r="L36" s="47"/>
-      <c r="M36" s="47"/>
-      <c r="N36" s="47"/>
-      <c r="O36" s="47"/>
-      <c r="P36" s="47"/>
-      <c r="Q36" s="47"/>
-      <c r="R36" s="47"/>
-      <c r="S36" s="47"/>
-      <c r="T36" s="47"/>
-      <c r="U36" s="47"/>
-      <c r="V36" s="47"/>
-      <c r="W36" s="47"/>
-      <c r="X36" s="47"/>
-      <c r="Y36" s="47"/>
-      <c r="Z36" s="47"/>
-      <c r="AA36" s="47"/>
-      <c r="AB36" s="47"/>
-      <c r="AC36" s="47"/>
-      <c r="AD36" s="47"/>
-      <c r="AE36" s="47"/>
-      <c r="AF36" s="47"/>
-      <c r="AG36" s="47"/>
-      <c r="AH36" s="47"/>
-      <c r="AI36" s="47"/>
-      <c r="AJ36" s="47"/>
-      <c r="AK36" s="47"/>
-      <c r="AL36" s="47"/>
-      <c r="AM36" s="47"/>
-      <c r="AN36" s="47"/>
-      <c r="AO36" s="47"/>
-      <c r="AP36" s="47"/>
-      <c r="AQ36" s="47"/>
-      <c r="AR36" s="47"/>
-      <c r="AS36" s="47"/>
-      <c r="AT36" s="47"/>
-      <c r="AU36" s="47"/>
-      <c r="AV36" s="47"/>
-      <c r="AW36" s="107"/>
-      <c r="AX36" s="47"/>
-      <c r="AY36" s="47"/>
-      <c r="AZ36" s="47"/>
-      <c r="BA36" s="47"/>
-      <c r="BB36" s="47"/>
-      <c r="BC36" s="47"/>
-      <c r="BD36" s="47"/>
-      <c r="BE36" s="47"/>
-      <c r="BF36" s="47"/>
-      <c r="BG36" s="47"/>
-      <c r="BH36" s="47"/>
-      <c r="BI36" s="47"/>
-      <c r="BJ36" s="47" t="str">
-        <f t="shared" si="162"/>
-        <v/>
-      </c>
-      <c r="BK36" s="47" t="str">
-        <f t="shared" si="162"/>
-        <v/>
-      </c>
-      <c r="BL36" s="47" t="str">
-        <f t="shared" si="162"/>
-        <v/>
-      </c>
-      <c r="BM36" s="47" t="str">
-        <f t="shared" si="162"/>
-        <v/>
-      </c>
-      <c r="BN36" s="47" t="str">
-        <f t="shared" si="162"/>
-        <v/>
-      </c>
-      <c r="BO36" s="47" t="str">
-        <f t="shared" si="162"/>
-        <v/>
-      </c>
-      <c r="BP36" s="47" t="str">
-        <f t="shared" si="162"/>
-        <v/>
-      </c>
-      <c r="BQ36" s="47" t="str">
-        <f t="shared" si="162"/>
-        <v/>
-      </c>
-      <c r="BR36" s="47" t="str">
-        <f t="shared" si="162"/>
-        <v/>
-      </c>
-      <c r="BS36" s="47" t="str">
-        <f t="shared" si="162"/>
-        <v/>
-      </c>
-      <c r="BT36" s="47" t="str">
-        <f t="shared" si="162"/>
-        <v/>
-      </c>
-      <c r="BU36" s="47" t="str">
-        <f t="shared" si="162"/>
-        <v/>
-      </c>
-      <c r="BV36" s="47" t="str">
-        <f t="shared" si="162"/>
-        <v/>
-      </c>
-      <c r="BW36" s="47" t="str">
-        <f t="shared" si="162"/>
-        <v/>
-      </c>
-      <c r="BX36" s="47" t="e">
-        <f>DEC2HEX(CODE(BJ36),2)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="BY36" s="47" t="e">
-        <f t="shared" si="180"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="BZ36" s="47" t="e">
-        <f t="shared" si="181"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="CA36" s="47" t="e">
-        <f t="shared" si="182"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="CB36" s="47" t="e">
-        <f t="shared" si="183"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="CC36" s="47" t="e">
-        <f t="shared" si="184"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="CD36" s="47" t="e">
-        <f t="shared" si="185"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="CE36" s="47" t="e">
-        <f t="shared" si="186"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="CF36" s="47" t="e">
-        <f t="shared" si="187"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="CG36" s="47" t="e">
-        <f t="shared" si="188"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="CH36" s="47" t="e">
-        <f t="shared" si="189"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="CI36" s="47" t="e">
-        <f t="shared" si="190"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="CJ36" s="47" t="e">
-        <f t="shared" si="191"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="CK36" s="47" t="e">
-        <f t="shared" si="192"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="CL36" s="47"/>
-      <c r="CM36" s="58"/>
-      <c r="CN36" s="47"/>
-      <c r="CO36" s="47"/>
-      <c r="CP36" s="47"/>
-      <c r="CQ36" s="47"/>
-      <c r="CR36" s="47"/>
-      <c r="CS36" s="47" t="str">
-        <f>SUBSTITUTE(J36," ","")</f>
-        <v/>
-      </c>
-      <c r="CT36" s="47"/>
-      <c r="CU36" s="47"/>
-      <c r="CV36" s="47"/>
-      <c r="CW36" s="47"/>
-      <c r="CX36" s="47"/>
-      <c r="CY36" s="47"/>
-      <c r="CZ36" s="47"/>
-    </row>
-    <row r="37" spans="1:104" s="43" customFormat="1" ht="39.950000000000003" hidden="1" customHeight="1" outlineLevel="1">
-      <c r="A37" s="45"/>
-      <c r="B37" s="46">
-        <f t="shared" si="56"/>
-        <v>9</v>
-      </c>
-      <c r="C37" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="D37" s="46" t="s">
-        <v>251</v>
-      </c>
-      <c r="E37" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="F37" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="G37" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="H37" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="I37" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="J37" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="K37" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="L37" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="M37" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="N37" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="O37" s="47"/>
-      <c r="P37" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="Q37" s="47"/>
-      <c r="R37" s="47"/>
-      <c r="S37" s="47"/>
-      <c r="T37" s="47" t="b">
-        <f>T35=T36</f>
-        <v>0</v>
-      </c>
-      <c r="U37" s="47" t="b">
-        <f t="shared" ref="U37:AZ37" si="193">U35=U36</f>
-        <v>0</v>
-      </c>
-      <c r="V37" s="47" t="b">
-        <f t="shared" si="193"/>
-        <v>0</v>
-      </c>
-      <c r="W37" s="47" t="b">
-        <f t="shared" si="193"/>
-        <v>0</v>
-      </c>
-      <c r="X37" s="47" t="b">
-        <f t="shared" si="193"/>
-        <v>0</v>
-      </c>
-      <c r="Y37" s="47" t="b">
-        <f t="shared" si="193"/>
-        <v>0</v>
-      </c>
-      <c r="Z37" s="47" t="b">
-        <f t="shared" si="193"/>
-        <v>0</v>
-      </c>
-      <c r="AA37" s="47" t="b">
-        <f t="shared" si="193"/>
-        <v>0</v>
-      </c>
-      <c r="AB37" s="47" t="b">
-        <f t="shared" si="193"/>
-        <v>0</v>
-      </c>
-      <c r="AC37" s="47" t="b">
-        <f t="shared" si="193"/>
-        <v>0</v>
-      </c>
-      <c r="AD37" s="47" t="b">
-        <f t="shared" si="193"/>
-        <v>0</v>
-      </c>
-      <c r="AE37" s="47" t="b">
-        <f t="shared" si="193"/>
-        <v>0</v>
-      </c>
-      <c r="AF37" s="47" t="b">
-        <f t="shared" si="193"/>
-        <v>0</v>
-      </c>
-      <c r="AG37" s="47" t="b">
-        <f t="shared" si="193"/>
-        <v>0</v>
-      </c>
-      <c r="AH37" s="47" t="b">
-        <f t="shared" si="193"/>
-        <v>0</v>
-      </c>
-      <c r="AI37" s="47" t="b">
-        <f t="shared" si="193"/>
-        <v>0</v>
-      </c>
-      <c r="AJ37" s="47" t="b">
-        <f t="shared" si="193"/>
-        <v>0</v>
-      </c>
-      <c r="AK37" s="47" t="b">
-        <f t="shared" si="193"/>
-        <v>0</v>
-      </c>
-      <c r="AL37" s="47" t="b">
-        <f t="shared" si="193"/>
-        <v>0</v>
-      </c>
-      <c r="AM37" s="47" t="b">
-        <f t="shared" si="193"/>
-        <v>0</v>
-      </c>
-      <c r="AN37" s="47" t="b">
-        <f t="shared" si="193"/>
-        <v>0</v>
-      </c>
-      <c r="AO37" s="47" t="b">
-        <f t="shared" si="193"/>
-        <v>0</v>
-      </c>
-      <c r="AP37" s="47" t="b">
-        <f t="shared" si="193"/>
-        <v>0</v>
-      </c>
-      <c r="AQ37" s="47" t="b">
-        <f t="shared" si="193"/>
-        <v>0</v>
-      </c>
-      <c r="AR37" s="47" t="b">
-        <f t="shared" si="193"/>
-        <v>0</v>
-      </c>
-      <c r="AS37" s="47" t="b">
-        <f t="shared" si="193"/>
-        <v>1</v>
-      </c>
-      <c r="AT37" s="47" t="b">
-        <f t="shared" si="193"/>
-        <v>1</v>
-      </c>
-      <c r="AU37" s="47" t="b">
-        <f t="shared" si="193"/>
-        <v>0</v>
-      </c>
-      <c r="AV37" s="47" t="b">
-        <f t="shared" si="193"/>
-        <v>0</v>
-      </c>
-      <c r="AW37" s="47" t="b">
-        <f t="shared" si="193"/>
-        <v>1</v>
-      </c>
-      <c r="AX37" s="47" t="b">
-        <f t="shared" si="193"/>
-        <v>1</v>
-      </c>
-      <c r="AY37" s="47" t="b">
-        <f t="shared" si="193"/>
-        <v>0</v>
-      </c>
-      <c r="AZ37" s="47" t="b">
-        <f t="shared" si="193"/>
-        <v>1</v>
-      </c>
-      <c r="BA37" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="BB37" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="BC37" s="47" t="b">
-        <f t="shared" ref="BC37:BH37" si="194">BC35=BC36</f>
-        <v>0</v>
-      </c>
-      <c r="BD37" s="47" t="b">
-        <f t="shared" si="194"/>
-        <v>0</v>
-      </c>
-      <c r="BE37" s="47" t="b">
-        <f t="shared" si="194"/>
-        <v>0</v>
-      </c>
-      <c r="BF37" s="47" t="b">
-        <f t="shared" si="194"/>
-        <v>0</v>
-      </c>
-      <c r="BG37" s="47" t="b">
-        <f t="shared" si="194"/>
-        <v>0</v>
-      </c>
-      <c r="BH37" s="47" t="b">
-        <f t="shared" si="194"/>
-        <v>0</v>
-      </c>
-      <c r="BI37" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="BJ37" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="BK37" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="BL37" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="BM37" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="BN37" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="BO37" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="BP37" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="BQ37" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="BR37" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="BS37" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="BT37" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="BU37" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="BV37" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="BW37" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="BX37" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="BY37" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="BZ37" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CA37" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CB37" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CC37" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CD37" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CE37" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CF37" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CG37" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CH37" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CI37" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CJ37" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CK37" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CL37" s="47" t="b">
-        <f>CL35=CL36</f>
-        <v>0</v>
-      </c>
-      <c r="CM37" s="47" t="b">
-        <f t="shared" ref="CM37:CN37" si="195">CM35=CM36</f>
-        <v>0</v>
-      </c>
-      <c r="CN37" s="47" t="b">
-        <f t="shared" si="195"/>
-        <v>0</v>
-      </c>
-      <c r="CO37" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CP37" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CQ37" s="47" t="b">
-        <f t="shared" ref="CQ37" si="196">CQ35=CQ36</f>
-        <v>0</v>
-      </c>
-      <c r="CR37" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CS37" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CT37" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CU37" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CV37" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CW37" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CX37" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CY37" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CZ37" s="47" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="38" spans="1:104" s="42" customFormat="1" ht="44.25" customHeight="1" collapsed="1">
-      <c r="A38" s="45"/>
-      <c r="B38" s="51">
-        <f t="shared" si="56"/>
-        <v>10</v>
-      </c>
-      <c r="C38" s="52">
-        <v>46324.200902777775</v>
-      </c>
-      <c r="D38" s="51" t="s">
-        <v>254</v>
-      </c>
-      <c r="E38" s="51"/>
-      <c r="F38" s="51"/>
-      <c r="G38" s="104"/>
-      <c r="H38" s="51" t="s">
-        <v>557</v>
-      </c>
-      <c r="I38" s="105"/>
-      <c r="J38" s="53" t="s">
-        <v>580</v>
-      </c>
-      <c r="K38" s="53"/>
-      <c r="L38" s="51"/>
-      <c r="M38" s="51"/>
-      <c r="N38" s="51"/>
-      <c r="O38" s="51" t="str">
-        <f>IF(COUNTIF(C40:CZ40,"FALSE")&gt;0,"NG","OK")</f>
-        <v>NG</v>
-      </c>
-      <c r="P38" s="51"/>
-      <c r="Q38" s="51" t="s">
-        <v>441</v>
-      </c>
-      <c r="R38" s="51" t="s">
-        <v>442</v>
-      </c>
-      <c r="S38" s="51" t="s">
-        <v>443</v>
-      </c>
-      <c r="T38" s="51" t="s">
-        <v>39</v>
-      </c>
-      <c r="U38" s="51" t="s">
-        <v>28</v>
-      </c>
-      <c r="V38" s="51" t="s">
-        <v>38</v>
-      </c>
-      <c r="W38" s="51" t="s">
-        <v>79</v>
-      </c>
-      <c r="X38" s="51" t="s">
-        <v>444</v>
-      </c>
-      <c r="Y38" s="51" t="s">
-        <v>444</v>
-      </c>
-      <c r="Z38" s="51" t="s">
-        <v>444</v>
-      </c>
-      <c r="AA38" s="51" t="s">
-        <v>444</v>
-      </c>
-      <c r="AB38" s="51" t="s">
-        <v>563</v>
-      </c>
-      <c r="AC38" s="51">
-        <v>66</v>
-      </c>
-      <c r="AD38" s="51" t="s">
-        <v>446</v>
-      </c>
-      <c r="AE38" s="51">
-        <v>1.2</v>
-      </c>
-      <c r="AF38" s="51" t="s">
-        <v>558</v>
-      </c>
-      <c r="AG38" s="51" t="s">
-        <v>433</v>
-      </c>
-      <c r="AH38" s="51" t="s">
-        <v>559</v>
-      </c>
-      <c r="AI38" s="51" t="s">
-        <v>449</v>
-      </c>
-      <c r="AJ38" s="51" t="s">
-        <v>560</v>
-      </c>
-      <c r="AK38" s="51">
-        <v>4</v>
-      </c>
-      <c r="AL38" s="51">
-        <v>159</v>
-      </c>
-      <c r="AM38" s="54" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(J38," ",""),"-","")</f>
-        <v>378206SATG10M6</v>
-      </c>
-      <c r="AN38" s="108" t="s">
-        <v>581</v>
-      </c>
-      <c r="AO38" s="108" t="s">
-        <v>582</v>
-      </c>
-      <c r="AP38" s="51" t="s">
-        <v>512</v>
-      </c>
-      <c r="AQ38" s="54" t="str">
-        <f>SUBSTITUTE(J38," ","")</f>
-        <v>37820-6SA-TG10-M6</v>
-      </c>
-      <c r="AR38" s="54" t="str">
-        <f>IF(RIGHT(SUBSTITUTE(J38," ",""),4)="0-M6",LEFT(SUBSTITUTE(J38," ",""),LEN(SUBSTITUTE(J38," ",""))-4),SUBSTITUTE(J38," ",""))</f>
-        <v>37820-6SA-TG1</v>
-      </c>
-      <c r="AS38" s="54">
-        <f>K38</f>
-        <v>0</v>
-      </c>
-      <c r="AT38" s="51"/>
-      <c r="AU38" s="51" t="s">
-        <v>452</v>
-      </c>
-      <c r="AV38" s="51" t="s">
-        <v>453</v>
-      </c>
-      <c r="AW38" s="106"/>
-      <c r="AX38" s="54">
-        <f>K38</f>
-        <v>0</v>
-      </c>
-      <c r="AY38" s="51" t="s">
-        <v>454</v>
-      </c>
-      <c r="AZ38" s="51"/>
-      <c r="BA38" s="51"/>
-      <c r="BB38" s="51"/>
-      <c r="BC38" s="51" t="s">
-        <v>490</v>
-      </c>
-      <c r="BD38" s="54" t="str">
-        <f>AP38</f>
-        <v>MG1CA020-2.30</v>
-      </c>
-      <c r="BE38" s="51" t="s">
-        <v>563</v>
-      </c>
-      <c r="BF38" s="51" t="s">
-        <v>461</v>
-      </c>
-      <c r="BG38" s="51" t="s">
-        <v>462</v>
-      </c>
-      <c r="BH38" s="51" t="s">
-        <v>564</v>
-      </c>
-      <c r="BI38" s="51" t="s">
-        <v>583</v>
-      </c>
-      <c r="BJ38" s="54" t="str">
-        <f t="shared" si="162"/>
-        <v>3</v>
-      </c>
-      <c r="BK38" s="54" t="str">
-        <f t="shared" si="162"/>
-        <v>7</v>
-      </c>
-      <c r="BL38" s="54" t="str">
-        <f t="shared" si="162"/>
-        <v>8</v>
-      </c>
-      <c r="BM38" s="54" t="str">
-        <f t="shared" si="162"/>
-        <v>0</v>
-      </c>
-      <c r="BN38" s="54" t="str">
-        <f t="shared" si="162"/>
-        <v>5</v>
-      </c>
-      <c r="BO38" s="54" t="str">
-        <f t="shared" si="162"/>
-        <v>-</v>
-      </c>
-      <c r="BP38" s="54" t="str">
-        <f t="shared" si="162"/>
-        <v>6</v>
-      </c>
-      <c r="BQ38" s="54" t="str">
-        <f t="shared" si="162"/>
-        <v>S</v>
-      </c>
-      <c r="BR38" s="54" t="str">
-        <f t="shared" si="162"/>
-        <v>A</v>
-      </c>
-      <c r="BS38" s="54" t="str">
-        <f t="shared" si="162"/>
-        <v>-</v>
-      </c>
-      <c r="BT38" s="54" t="str">
-        <f t="shared" si="162"/>
-        <v>T</v>
-      </c>
-      <c r="BU38" s="54" t="str">
-        <f t="shared" si="162"/>
-        <v>G</v>
-      </c>
-      <c r="BV38" s="54" t="str">
-        <f t="shared" si="162"/>
-        <v>1</v>
-      </c>
-      <c r="BW38" s="54" t="str">
-        <f t="shared" si="162"/>
-        <v>0</v>
-      </c>
-      <c r="BX38" s="55" t="str">
-        <f>DEC2HEX(CODE(BJ38),2)</f>
-        <v>33</v>
-      </c>
-      <c r="BY38" s="55" t="str">
-        <f t="shared" ref="BY38:BY39" si="197">DEC2HEX(CODE(BK38),2)</f>
-        <v>37</v>
-      </c>
-      <c r="BZ38" s="55" t="str">
-        <f t="shared" ref="BZ38:BZ39" si="198">DEC2HEX(CODE(BL38),2)</f>
-        <v>38</v>
-      </c>
-      <c r="CA38" s="55" t="str">
-        <f t="shared" ref="CA38:CA39" si="199">DEC2HEX(CODE(BM38),2)</f>
-        <v>30</v>
-      </c>
-      <c r="CB38" s="55" t="str">
-        <f t="shared" ref="CB38:CB39" si="200">DEC2HEX(CODE(BN38),2)</f>
-        <v>35</v>
-      </c>
-      <c r="CC38" s="55" t="str">
-        <f t="shared" ref="CC38:CC39" si="201">DEC2HEX(CODE(BO38),2)</f>
-        <v>2D</v>
-      </c>
-      <c r="CD38" s="55" t="str">
-        <f t="shared" ref="CD38:CD39" si="202">DEC2HEX(CODE(BP38),2)</f>
-        <v>36</v>
-      </c>
-      <c r="CE38" s="55" t="str">
-        <f t="shared" ref="CE38:CE39" si="203">DEC2HEX(CODE(BQ38),2)</f>
-        <v>53</v>
-      </c>
-      <c r="CF38" s="55" t="str">
-        <f t="shared" ref="CF38:CF39" si="204">DEC2HEX(CODE(BR38),2)</f>
-        <v>41</v>
-      </c>
-      <c r="CG38" s="55" t="str">
-        <f t="shared" ref="CG38:CG39" si="205">DEC2HEX(CODE(BS38),2)</f>
-        <v>2D</v>
-      </c>
-      <c r="CH38" s="55" t="str">
-        <f t="shared" ref="CH38:CH39" si="206">DEC2HEX(CODE(BT38),2)</f>
-        <v>54</v>
-      </c>
-      <c r="CI38" s="55" t="str">
-        <f t="shared" ref="CI38:CI39" si="207">DEC2HEX(CODE(BU38),2)</f>
-        <v>47</v>
-      </c>
-      <c r="CJ38" s="55" t="str">
-        <f t="shared" ref="CJ38:CJ39" si="208">DEC2HEX(CODE(BV38),2)</f>
-        <v>31</v>
-      </c>
-      <c r="CK38" s="55" t="str">
-        <f t="shared" ref="CK38:CK39" si="209">DEC2HEX(CODE(BW38),2)</f>
-        <v>30</v>
-      </c>
-      <c r="CL38" s="54" t="str">
-        <f>BX38&amp;BY38&amp;BZ38&amp;CA38&amp;CB38&amp;CC38&amp;CD38&amp;CE38&amp;CF38&amp;CG38&amp;CH38&amp;CI38&amp;CJ38&amp;CK38</f>
-        <v>33373830352D3653412D54473130</v>
-      </c>
-      <c r="CM38" s="104" t="s">
-        <v>513</v>
-      </c>
-      <c r="CN38" s="51" t="s">
-        <v>470</v>
-      </c>
-      <c r="CO38" s="51" t="s">
-        <v>240</v>
-      </c>
-      <c r="CP38" s="51" t="s">
-        <v>240</v>
-      </c>
-      <c r="CQ38" s="51" t="s">
-        <v>240</v>
-      </c>
-      <c r="CR38" s="56" t="s">
-        <v>240</v>
-      </c>
-      <c r="CS38" s="54" t="str">
-        <f>SUBSTITUTE(J38," ","")</f>
-        <v>37820-6SA-TG10-M6</v>
-      </c>
-      <c r="CT38" s="108" t="s">
-        <v>584</v>
-      </c>
-      <c r="CU38" s="51" t="s">
-        <v>583</v>
-      </c>
-      <c r="CV38" s="51" t="s">
-        <v>583</v>
-      </c>
-      <c r="CW38" s="56"/>
-      <c r="CX38" s="51" t="str">
-        <f>AR38</f>
-        <v>37820-6SA-TG1</v>
-      </c>
-      <c r="CY38" s="106">
-        <v>400000</v>
-      </c>
-      <c r="CZ38" s="51" t="s">
-        <v>585</v>
-      </c>
-    </row>
-    <row r="39" spans="1:104" s="42" customFormat="1" ht="44.25" hidden="1" customHeight="1" outlineLevel="1" collapsed="1">
-      <c r="A39" s="45"/>
-      <c r="B39" s="47">
-        <f t="shared" si="56"/>
-        <v>10</v>
-      </c>
-      <c r="C39" s="57"/>
-      <c r="D39" s="47" t="s">
-        <v>245</v>
-      </c>
-      <c r="E39" s="47"/>
-      <c r="F39" s="47"/>
-      <c r="G39" s="57"/>
-      <c r="H39" s="47"/>
-      <c r="I39" s="47"/>
-      <c r="J39" s="47"/>
-      <c r="K39" s="47"/>
-      <c r="L39" s="47"/>
-      <c r="M39" s="47"/>
-      <c r="N39" s="47"/>
-      <c r="O39" s="47"/>
-      <c r="P39" s="47"/>
-      <c r="Q39" s="47"/>
-      <c r="R39" s="47"/>
-      <c r="S39" s="47"/>
-      <c r="T39" s="47"/>
-      <c r="U39" s="47"/>
-      <c r="V39" s="47"/>
-      <c r="W39" s="47"/>
-      <c r="X39" s="47"/>
-      <c r="Y39" s="47"/>
-      <c r="Z39" s="47"/>
-      <c r="AA39" s="47"/>
-      <c r="AB39" s="47"/>
-      <c r="AC39" s="47"/>
-      <c r="AD39" s="47"/>
-      <c r="AE39" s="47"/>
-      <c r="AF39" s="47"/>
-      <c r="AG39" s="47"/>
-      <c r="AH39" s="47"/>
-      <c r="AI39" s="47"/>
-      <c r="AJ39" s="47"/>
-      <c r="AK39" s="47"/>
-      <c r="AL39" s="47"/>
-      <c r="AM39" s="47"/>
-      <c r="AN39" s="47"/>
-      <c r="AO39" s="47"/>
-      <c r="AP39" s="47"/>
-      <c r="AQ39" s="47"/>
-      <c r="AR39" s="47"/>
-      <c r="AS39" s="47"/>
-      <c r="AT39" s="47"/>
-      <c r="AU39" s="47"/>
-      <c r="AV39" s="47"/>
-      <c r="AW39" s="107"/>
-      <c r="AX39" s="47"/>
-      <c r="AY39" s="47"/>
-      <c r="AZ39" s="47"/>
-      <c r="BA39" s="47"/>
-      <c r="BB39" s="47"/>
-      <c r="BC39" s="47"/>
-      <c r="BD39" s="47"/>
-      <c r="BE39" s="47"/>
-      <c r="BF39" s="47"/>
-      <c r="BG39" s="47"/>
-      <c r="BH39" s="47"/>
-      <c r="BI39" s="47"/>
-      <c r="BJ39" s="47" t="str">
-        <f t="shared" si="162"/>
-        <v/>
-      </c>
-      <c r="BK39" s="47" t="str">
-        <f t="shared" si="162"/>
-        <v/>
-      </c>
-      <c r="BL39" s="47" t="str">
-        <f t="shared" si="162"/>
-        <v/>
-      </c>
-      <c r="BM39" s="47" t="str">
-        <f t="shared" si="162"/>
-        <v/>
-      </c>
-      <c r="BN39" s="47" t="str">
-        <f t="shared" si="162"/>
-        <v/>
-      </c>
-      <c r="BO39" s="47" t="str">
-        <f t="shared" si="162"/>
-        <v/>
-      </c>
-      <c r="BP39" s="47" t="str">
-        <f t="shared" si="162"/>
-        <v/>
-      </c>
-      <c r="BQ39" s="47" t="str">
-        <f t="shared" si="162"/>
-        <v/>
-      </c>
-      <c r="BR39" s="47" t="str">
-        <f t="shared" si="162"/>
-        <v/>
-      </c>
-      <c r="BS39" s="47" t="str">
-        <f t="shared" si="162"/>
-        <v/>
-      </c>
-      <c r="BT39" s="47" t="str">
-        <f t="shared" si="162"/>
-        <v/>
-      </c>
-      <c r="BU39" s="47" t="str">
-        <f t="shared" si="162"/>
-        <v/>
-      </c>
-      <c r="BV39" s="47" t="str">
-        <f t="shared" si="162"/>
-        <v/>
-      </c>
-      <c r="BW39" s="47" t="str">
-        <f t="shared" si="162"/>
-        <v/>
-      </c>
-      <c r="BX39" s="47" t="e">
-        <f>DEC2HEX(CODE(BJ39),2)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="BY39" s="47" t="e">
-        <f t="shared" si="197"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="BZ39" s="47" t="e">
-        <f t="shared" si="198"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="CA39" s="47" t="e">
-        <f t="shared" si="199"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="CB39" s="47" t="e">
-        <f t="shared" si="200"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="CC39" s="47" t="e">
-        <f t="shared" si="201"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="CD39" s="47" t="e">
-        <f t="shared" si="202"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="CE39" s="47" t="e">
-        <f t="shared" si="203"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="CF39" s="47" t="e">
-        <f t="shared" si="204"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="CG39" s="47" t="e">
-        <f t="shared" si="205"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="CH39" s="47" t="e">
-        <f t="shared" si="206"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="CI39" s="47" t="e">
-        <f t="shared" si="207"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="CJ39" s="47" t="e">
-        <f t="shared" si="208"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="CK39" s="47" t="e">
-        <f t="shared" si="209"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="CL39" s="47"/>
-      <c r="CM39" s="58"/>
-      <c r="CN39" s="47"/>
-      <c r="CO39" s="47"/>
-      <c r="CP39" s="47"/>
-      <c r="CQ39" s="47"/>
-      <c r="CR39" s="47"/>
-      <c r="CS39" s="47" t="str">
-        <f>SUBSTITUTE(J39," ","")</f>
-        <v/>
-      </c>
-      <c r="CT39" s="47"/>
-      <c r="CU39" s="47"/>
-      <c r="CV39" s="47"/>
-      <c r="CW39" s="47"/>
-      <c r="CX39" s="47"/>
-      <c r="CY39" s="47"/>
-      <c r="CZ39" s="47"/>
-    </row>
-    <row r="40" spans="1:104" s="43" customFormat="1" ht="39.950000000000003" hidden="1" customHeight="1" outlineLevel="1">
-      <c r="A40" s="45"/>
-      <c r="B40" s="46">
-        <f t="shared" si="56"/>
-        <v>10</v>
-      </c>
-      <c r="C40" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="D40" s="46" t="s">
-        <v>251</v>
-      </c>
-      <c r="E40" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="F40" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="G40" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="H40" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="I40" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="J40" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="K40" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="L40" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="M40" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="N40" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="O40" s="47"/>
-      <c r="P40" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="Q40" s="47"/>
-      <c r="R40" s="47"/>
-      <c r="S40" s="47"/>
-      <c r="T40" s="47" t="b">
-        <f>T38=T39</f>
-        <v>0</v>
-      </c>
-      <c r="U40" s="47" t="b">
-        <f t="shared" ref="U40:AZ40" si="210">U38=U39</f>
-        <v>0</v>
-      </c>
-      <c r="V40" s="47" t="b">
-        <f t="shared" si="210"/>
-        <v>0</v>
-      </c>
-      <c r="W40" s="47" t="b">
-        <f t="shared" si="210"/>
-        <v>0</v>
-      </c>
-      <c r="X40" s="47" t="b">
-        <f t="shared" si="210"/>
-        <v>0</v>
-      </c>
-      <c r="Y40" s="47" t="b">
-        <f t="shared" si="210"/>
-        <v>0</v>
-      </c>
-      <c r="Z40" s="47" t="b">
-        <f t="shared" si="210"/>
-        <v>0</v>
-      </c>
-      <c r="AA40" s="47" t="b">
-        <f t="shared" si="210"/>
-        <v>0</v>
-      </c>
-      <c r="AB40" s="47" t="b">
-        <f t="shared" si="210"/>
-        <v>0</v>
-      </c>
-      <c r="AC40" s="47" t="b">
-        <f t="shared" si="210"/>
-        <v>0</v>
-      </c>
-      <c r="AD40" s="47" t="b">
-        <f t="shared" si="210"/>
-        <v>0</v>
-      </c>
-      <c r="AE40" s="47" t="b">
-        <f t="shared" si="210"/>
-        <v>0</v>
-      </c>
-      <c r="AF40" s="47" t="b">
-        <f t="shared" si="210"/>
-        <v>0</v>
-      </c>
-      <c r="AG40" s="47" t="b">
-        <f t="shared" si="210"/>
-        <v>0</v>
-      </c>
-      <c r="AH40" s="47" t="b">
-        <f t="shared" si="210"/>
-        <v>0</v>
-      </c>
-      <c r="AI40" s="47" t="b">
-        <f t="shared" si="210"/>
-        <v>0</v>
-      </c>
-      <c r="AJ40" s="47" t="b">
-        <f t="shared" si="210"/>
-        <v>0</v>
-      </c>
-      <c r="AK40" s="47" t="b">
-        <f t="shared" si="210"/>
-        <v>0</v>
-      </c>
-      <c r="AL40" s="47" t="b">
-        <f t="shared" si="210"/>
-        <v>0</v>
-      </c>
-      <c r="AM40" s="47" t="b">
-        <f t="shared" si="210"/>
-        <v>0</v>
-      </c>
-      <c r="AN40" s="47" t="b">
-        <f t="shared" si="210"/>
-        <v>0</v>
-      </c>
-      <c r="AO40" s="47" t="b">
-        <f t="shared" si="210"/>
-        <v>0</v>
-      </c>
-      <c r="AP40" s="47" t="b">
-        <f t="shared" si="210"/>
-        <v>0</v>
-      </c>
-      <c r="AQ40" s="47" t="b">
-        <f t="shared" si="210"/>
-        <v>0</v>
-      </c>
-      <c r="AR40" s="47" t="b">
-        <f t="shared" si="210"/>
-        <v>0</v>
-      </c>
-      <c r="AS40" s="47" t="b">
-        <f t="shared" si="210"/>
-        <v>1</v>
-      </c>
-      <c r="AT40" s="47" t="b">
-        <f t="shared" si="210"/>
-        <v>1</v>
-      </c>
-      <c r="AU40" s="47" t="b">
-        <f t="shared" si="210"/>
-        <v>0</v>
-      </c>
-      <c r="AV40" s="47" t="b">
-        <f t="shared" si="210"/>
-        <v>0</v>
-      </c>
-      <c r="AW40" s="47" t="b">
-        <f t="shared" si="210"/>
-        <v>1</v>
-      </c>
-      <c r="AX40" s="47" t="b">
-        <f t="shared" si="210"/>
-        <v>1</v>
-      </c>
-      <c r="AY40" s="47" t="b">
-        <f t="shared" si="210"/>
-        <v>0</v>
-      </c>
-      <c r="AZ40" s="47" t="b">
-        <f t="shared" si="210"/>
-        <v>1</v>
-      </c>
-      <c r="BA40" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="BB40" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="BC40" s="47" t="b">
-        <f t="shared" ref="BC40:BH40" si="211">BC38=BC39</f>
-        <v>0</v>
-      </c>
-      <c r="BD40" s="47" t="b">
-        <f t="shared" si="211"/>
-        <v>0</v>
-      </c>
-      <c r="BE40" s="47" t="b">
-        <f t="shared" si="211"/>
-        <v>0</v>
-      </c>
-      <c r="BF40" s="47" t="b">
-        <f t="shared" si="211"/>
-        <v>0</v>
-      </c>
-      <c r="BG40" s="47" t="b">
-        <f t="shared" si="211"/>
-        <v>0</v>
-      </c>
-      <c r="BH40" s="47" t="b">
-        <f t="shared" si="211"/>
-        <v>0</v>
-      </c>
-      <c r="BI40" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="BJ40" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="BK40" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="BL40" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="BM40" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="BN40" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="BO40" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="BP40" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="BQ40" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="BR40" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="BS40" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="BT40" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="BU40" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="BV40" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="BW40" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="BX40" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="BY40" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="BZ40" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CA40" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CB40" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CC40" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CD40" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CE40" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CF40" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CG40" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CH40" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CI40" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CJ40" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CK40" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CL40" s="47" t="b">
-        <f>CL38=CL39</f>
-        <v>0</v>
-      </c>
-      <c r="CM40" s="47" t="b">
-        <f t="shared" ref="CM40:CN40" si="212">CM38=CM39</f>
-        <v>0</v>
-      </c>
-      <c r="CN40" s="47" t="b">
-        <f t="shared" si="212"/>
-        <v>0</v>
-      </c>
-      <c r="CO40" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CP40" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CQ40" s="47" t="b">
-        <f t="shared" ref="CQ40" si="213">CQ38=CQ39</f>
-        <v>0</v>
-      </c>
-      <c r="CR40" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CS40" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CT40" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CU40" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CV40" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CW40" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CX40" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CY40" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CZ40" s="47" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="41" spans="1:104" s="42" customFormat="1" ht="44.25" customHeight="1" collapsed="1">
-      <c r="A41" s="45"/>
-      <c r="B41" s="51">
-        <f t="shared" si="56"/>
-        <v>11</v>
-      </c>
-      <c r="C41" s="52">
-        <v>46324.200925925928</v>
-      </c>
-      <c r="D41" s="51" t="s">
-        <v>254</v>
-      </c>
-      <c r="E41" s="51"/>
-      <c r="F41" s="51"/>
-      <c r="G41" s="104"/>
-      <c r="H41" s="51" t="s">
-        <v>557</v>
-      </c>
-      <c r="I41" s="105"/>
-      <c r="J41" s="53" t="s">
-        <v>586</v>
-      </c>
-      <c r="K41" s="53"/>
-      <c r="L41" s="51"/>
-      <c r="M41" s="51"/>
-      <c r="N41" s="51"/>
-      <c r="O41" s="51" t="str">
-        <f>IF(COUNTIF(C43:CZ43,"FALSE")&gt;0,"NG","OK")</f>
-        <v>NG</v>
-      </c>
-      <c r="P41" s="51"/>
-      <c r="Q41" s="51" t="s">
-        <v>441</v>
-      </c>
-      <c r="R41" s="51" t="s">
-        <v>442</v>
-      </c>
-      <c r="S41" s="51" t="s">
-        <v>443</v>
-      </c>
-      <c r="T41" s="51" t="s">
-        <v>39</v>
-      </c>
-      <c r="U41" s="51" t="s">
-        <v>28</v>
-      </c>
-      <c r="V41" s="51" t="s">
-        <v>38</v>
-      </c>
-      <c r="W41" s="51" t="s">
-        <v>79</v>
-      </c>
-      <c r="X41" s="51" t="s">
-        <v>444</v>
-      </c>
-      <c r="Y41" s="51" t="s">
-        <v>444</v>
-      </c>
-      <c r="Z41" s="51" t="s">
-        <v>444</v>
-      </c>
-      <c r="AA41" s="51" t="s">
-        <v>444</v>
-      </c>
-      <c r="AB41" s="51" t="s">
-        <v>563</v>
-      </c>
-      <c r="AC41" s="51">
-        <v>66</v>
-      </c>
-      <c r="AD41" s="51" t="s">
-        <v>446</v>
-      </c>
-      <c r="AE41" s="51">
-        <v>1.2</v>
-      </c>
-      <c r="AF41" s="51" t="s">
-        <v>558</v>
-      </c>
-      <c r="AG41" s="51" t="s">
-        <v>433</v>
-      </c>
-      <c r="AH41" s="51" t="s">
-        <v>559</v>
-      </c>
-      <c r="AI41" s="51" t="s">
-        <v>449</v>
-      </c>
-      <c r="AJ41" s="51" t="s">
-        <v>560</v>
-      </c>
-      <c r="AK41" s="51">
-        <v>4</v>
-      </c>
-      <c r="AL41" s="51">
-        <v>159</v>
-      </c>
-      <c r="AM41" s="54" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(J41," ",""),"-","")</f>
-        <v>378206SATJ10M6</v>
-      </c>
-      <c r="AN41" s="108" t="s">
-        <v>587</v>
-      </c>
-      <c r="AO41" s="108" t="s">
-        <v>588</v>
-      </c>
-      <c r="AP41" s="51" t="s">
-        <v>512</v>
-      </c>
-      <c r="AQ41" s="54" t="str">
-        <f>SUBSTITUTE(J41," ","")</f>
-        <v>37820-6SA-TJ10-M6</v>
-      </c>
-      <c r="AR41" s="54" t="str">
-        <f>IF(RIGHT(SUBSTITUTE(J41," ",""),4)="0-M6",LEFT(SUBSTITUTE(J41," ",""),LEN(SUBSTITUTE(J41," ",""))-4),SUBSTITUTE(J41," ",""))</f>
-        <v>37820-6SA-TJ1</v>
-      </c>
-      <c r="AS41" s="54">
-        <f>K41</f>
-        <v>0</v>
-      </c>
-      <c r="AT41" s="51"/>
-      <c r="AU41" s="51" t="s">
-        <v>452</v>
-      </c>
-      <c r="AV41" s="51" t="s">
-        <v>453</v>
-      </c>
-      <c r="AW41" s="106"/>
-      <c r="AX41" s="54">
-        <f>K41</f>
-        <v>0</v>
-      </c>
-      <c r="AY41" s="51" t="s">
-        <v>454</v>
-      </c>
-      <c r="AZ41" s="51"/>
-      <c r="BA41" s="51"/>
-      <c r="BB41" s="51"/>
-      <c r="BC41" s="51" t="s">
-        <v>490</v>
-      </c>
-      <c r="BD41" s="54" t="str">
-        <f>AP41</f>
-        <v>MG1CA020-2.30</v>
-      </c>
-      <c r="BE41" s="51" t="s">
-        <v>563</v>
-      </c>
-      <c r="BF41" s="51" t="s">
-        <v>461</v>
-      </c>
-      <c r="BG41" s="51" t="s">
-        <v>462</v>
-      </c>
-      <c r="BH41" s="51" t="s">
-        <v>564</v>
-      </c>
-      <c r="BI41" s="51" t="s">
-        <v>589</v>
-      </c>
-      <c r="BJ41" s="54" t="str">
-        <f t="shared" si="162"/>
-        <v>3</v>
-      </c>
-      <c r="BK41" s="54" t="str">
-        <f t="shared" si="162"/>
-        <v>7</v>
-      </c>
-      <c r="BL41" s="54" t="str">
-        <f t="shared" si="162"/>
-        <v>8</v>
-      </c>
-      <c r="BM41" s="54" t="str">
-        <f t="shared" si="162"/>
-        <v>0</v>
-      </c>
-      <c r="BN41" s="54" t="str">
-        <f t="shared" si="162"/>
-        <v>5</v>
-      </c>
-      <c r="BO41" s="54" t="str">
-        <f t="shared" si="162"/>
-        <v>-</v>
-      </c>
-      <c r="BP41" s="54" t="str">
-        <f t="shared" si="162"/>
-        <v>6</v>
-      </c>
-      <c r="BQ41" s="54" t="str">
-        <f t="shared" si="162"/>
-        <v>S</v>
-      </c>
-      <c r="BR41" s="54" t="str">
-        <f t="shared" si="162"/>
-        <v>A</v>
-      </c>
-      <c r="BS41" s="54" t="str">
-        <f t="shared" si="162"/>
-        <v>-</v>
-      </c>
-      <c r="BT41" s="54" t="str">
-        <f t="shared" si="162"/>
-        <v>T</v>
-      </c>
-      <c r="BU41" s="54" t="str">
-        <f t="shared" si="162"/>
-        <v>J</v>
-      </c>
-      <c r="BV41" s="54" t="str">
-        <f t="shared" si="162"/>
-        <v>1</v>
-      </c>
-      <c r="BW41" s="54" t="str">
-        <f t="shared" si="162"/>
-        <v>0</v>
-      </c>
-      <c r="BX41" s="55" t="str">
-        <f>DEC2HEX(CODE(BJ41),2)</f>
-        <v>33</v>
-      </c>
-      <c r="BY41" s="55" t="str">
-        <f t="shared" ref="BY41:BY42" si="214">DEC2HEX(CODE(BK41),2)</f>
-        <v>37</v>
-      </c>
-      <c r="BZ41" s="55" t="str">
-        <f t="shared" ref="BZ41:BZ42" si="215">DEC2HEX(CODE(BL41),2)</f>
-        <v>38</v>
-      </c>
-      <c r="CA41" s="55" t="str">
-        <f t="shared" ref="CA41:CA42" si="216">DEC2HEX(CODE(BM41),2)</f>
-        <v>30</v>
-      </c>
-      <c r="CB41" s="55" t="str">
-        <f t="shared" ref="CB41:CB42" si="217">DEC2HEX(CODE(BN41),2)</f>
-        <v>35</v>
-      </c>
-      <c r="CC41" s="55" t="str">
-        <f t="shared" ref="CC41:CC42" si="218">DEC2HEX(CODE(BO41),2)</f>
-        <v>2D</v>
-      </c>
-      <c r="CD41" s="55" t="str">
-        <f t="shared" ref="CD41:CD42" si="219">DEC2HEX(CODE(BP41),2)</f>
-        <v>36</v>
-      </c>
-      <c r="CE41" s="55" t="str">
-        <f t="shared" ref="CE41:CE42" si="220">DEC2HEX(CODE(BQ41),2)</f>
-        <v>53</v>
-      </c>
-      <c r="CF41" s="55" t="str">
-        <f t="shared" ref="CF41:CF42" si="221">DEC2HEX(CODE(BR41),2)</f>
-        <v>41</v>
-      </c>
-      <c r="CG41" s="55" t="str">
-        <f t="shared" ref="CG41:CG42" si="222">DEC2HEX(CODE(BS41),2)</f>
-        <v>2D</v>
-      </c>
-      <c r="CH41" s="55" t="str">
-        <f t="shared" ref="CH41:CH42" si="223">DEC2HEX(CODE(BT41),2)</f>
-        <v>54</v>
-      </c>
-      <c r="CI41" s="55" t="str">
-        <f t="shared" ref="CI41:CI42" si="224">DEC2HEX(CODE(BU41),2)</f>
-        <v>4A</v>
-      </c>
-      <c r="CJ41" s="55" t="str">
-        <f t="shared" ref="CJ41:CJ42" si="225">DEC2HEX(CODE(BV41),2)</f>
-        <v>31</v>
-      </c>
-      <c r="CK41" s="55" t="str">
-        <f t="shared" ref="CK41:CK42" si="226">DEC2HEX(CODE(BW41),2)</f>
-        <v>30</v>
-      </c>
-      <c r="CL41" s="54" t="str">
-        <f>BX41&amp;BY41&amp;BZ41&amp;CA41&amp;CB41&amp;CC41&amp;CD41&amp;CE41&amp;CF41&amp;CG41&amp;CH41&amp;CI41&amp;CJ41&amp;CK41</f>
-        <v>33373830352D3653412D544A3130</v>
-      </c>
-      <c r="CM41" s="104" t="s">
-        <v>513</v>
-      </c>
-      <c r="CN41" s="51" t="s">
-        <v>470</v>
-      </c>
-      <c r="CO41" s="51" t="s">
-        <v>240</v>
-      </c>
-      <c r="CP41" s="51" t="s">
-        <v>240</v>
-      </c>
-      <c r="CQ41" s="51" t="s">
-        <v>240</v>
-      </c>
-      <c r="CR41" s="56" t="s">
-        <v>240</v>
-      </c>
-      <c r="CS41" s="54" t="str">
-        <f>SUBSTITUTE(J41," ","")</f>
-        <v>37820-6SA-TJ10-M6</v>
-      </c>
-      <c r="CT41" s="108" t="s">
-        <v>590</v>
-      </c>
-      <c r="CU41" s="51" t="s">
-        <v>589</v>
-      </c>
-      <c r="CV41" s="51" t="s">
-        <v>589</v>
-      </c>
-      <c r="CW41" s="56"/>
-      <c r="CX41" s="51" t="str">
-        <f>AR41</f>
-        <v>37820-6SA-TJ1</v>
-      </c>
-      <c r="CY41" s="106" t="s">
-        <v>483</v>
-      </c>
-      <c r="CZ41" s="51" t="s">
-        <v>591</v>
-      </c>
-    </row>
-    <row r="42" spans="1:104" s="42" customFormat="1" ht="44.25" hidden="1" customHeight="1" outlineLevel="1" collapsed="1">
-      <c r="A42" s="45"/>
-      <c r="B42" s="47">
-        <f t="shared" si="56"/>
-        <v>11</v>
-      </c>
-      <c r="C42" s="57"/>
-      <c r="D42" s="47" t="s">
-        <v>245</v>
-      </c>
-      <c r="E42" s="47"/>
-      <c r="F42" s="47"/>
-      <c r="G42" s="57"/>
-      <c r="H42" s="47"/>
-      <c r="I42" s="47"/>
-      <c r="J42" s="47"/>
-      <c r="K42" s="47"/>
-      <c r="L42" s="47"/>
-      <c r="M42" s="47"/>
-      <c r="N42" s="47"/>
-      <c r="O42" s="47"/>
-      <c r="P42" s="47"/>
-      <c r="Q42" s="47"/>
-      <c r="R42" s="47"/>
-      <c r="S42" s="47"/>
-      <c r="T42" s="47"/>
-      <c r="U42" s="47"/>
-      <c r="V42" s="47"/>
-      <c r="W42" s="47"/>
-      <c r="X42" s="47"/>
-      <c r="Y42" s="47"/>
-      <c r="Z42" s="47"/>
-      <c r="AA42" s="47"/>
-      <c r="AB42" s="47"/>
-      <c r="AC42" s="47"/>
-      <c r="AD42" s="47"/>
-      <c r="AE42" s="47"/>
-      <c r="AF42" s="47"/>
-      <c r="AG42" s="47"/>
-      <c r="AH42" s="47"/>
-      <c r="AI42" s="47"/>
-      <c r="AJ42" s="47"/>
-      <c r="AK42" s="47"/>
-      <c r="AL42" s="47"/>
-      <c r="AM42" s="47"/>
-      <c r="AN42" s="47"/>
-      <c r="AO42" s="47"/>
-      <c r="AP42" s="47"/>
-      <c r="AQ42" s="47"/>
-      <c r="AR42" s="47"/>
-      <c r="AS42" s="47"/>
-      <c r="AT42" s="47"/>
-      <c r="AU42" s="47"/>
-      <c r="AV42" s="47"/>
-      <c r="AW42" s="107"/>
-      <c r="AX42" s="47"/>
-      <c r="AY42" s="47"/>
-      <c r="AZ42" s="47"/>
-      <c r="BA42" s="47"/>
-      <c r="BB42" s="47"/>
-      <c r="BC42" s="47"/>
-      <c r="BD42" s="47"/>
-      <c r="BE42" s="47"/>
-      <c r="BF42" s="47"/>
-      <c r="BG42" s="47"/>
-      <c r="BH42" s="47"/>
-      <c r="BI42" s="47"/>
-      <c r="BJ42" s="47" t="str">
-        <f t="shared" si="162"/>
-        <v/>
-      </c>
-      <c r="BK42" s="47" t="str">
-        <f t="shared" si="162"/>
-        <v/>
-      </c>
-      <c r="BL42" s="47" t="str">
-        <f t="shared" si="162"/>
-        <v/>
-      </c>
-      <c r="BM42" s="47" t="str">
-        <f t="shared" si="162"/>
-        <v/>
-      </c>
-      <c r="BN42" s="47" t="str">
-        <f t="shared" si="162"/>
-        <v/>
-      </c>
-      <c r="BO42" s="47" t="str">
-        <f t="shared" si="162"/>
-        <v/>
-      </c>
-      <c r="BP42" s="47" t="str">
-        <f t="shared" si="162"/>
-        <v/>
-      </c>
-      <c r="BQ42" s="47" t="str">
-        <f t="shared" si="162"/>
-        <v/>
-      </c>
-      <c r="BR42" s="47" t="str">
-        <f t="shared" si="162"/>
-        <v/>
-      </c>
-      <c r="BS42" s="47" t="str">
-        <f t="shared" si="162"/>
-        <v/>
-      </c>
-      <c r="BT42" s="47" t="str">
-        <f t="shared" si="162"/>
-        <v/>
-      </c>
-      <c r="BU42" s="47" t="str">
-        <f t="shared" si="162"/>
-        <v/>
-      </c>
-      <c r="BV42" s="47" t="str">
-        <f t="shared" si="162"/>
-        <v/>
-      </c>
-      <c r="BW42" s="47" t="str">
-        <f t="shared" si="162"/>
-        <v/>
-      </c>
-      <c r="BX42" s="47" t="e">
-        <f>DEC2HEX(CODE(BJ42),2)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="BY42" s="47" t="e">
-        <f t="shared" si="214"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="BZ42" s="47" t="e">
-        <f t="shared" si="215"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="CA42" s="47" t="e">
-        <f t="shared" si="216"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="CB42" s="47" t="e">
-        <f t="shared" si="217"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="CC42" s="47" t="e">
-        <f t="shared" si="218"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="CD42" s="47" t="e">
-        <f t="shared" si="219"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="CE42" s="47" t="e">
-        <f t="shared" si="220"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="CF42" s="47" t="e">
-        <f t="shared" si="221"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="CG42" s="47" t="e">
-        <f t="shared" si="222"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="CH42" s="47" t="e">
-        <f t="shared" si="223"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="CI42" s="47" t="e">
-        <f t="shared" si="224"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="CJ42" s="47" t="e">
-        <f t="shared" si="225"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="CK42" s="47" t="e">
-        <f t="shared" si="226"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="CL42" s="47"/>
-      <c r="CM42" s="58"/>
-      <c r="CN42" s="47"/>
-      <c r="CO42" s="47"/>
-      <c r="CP42" s="47"/>
-      <c r="CQ42" s="47"/>
-      <c r="CR42" s="47"/>
-      <c r="CS42" s="47" t="str">
-        <f>SUBSTITUTE(J42," ","")</f>
-        <v/>
-      </c>
-      <c r="CT42" s="47"/>
-      <c r="CU42" s="47"/>
-      <c r="CV42" s="47"/>
-      <c r="CW42" s="47"/>
-      <c r="CX42" s="47"/>
-      <c r="CY42" s="47"/>
-      <c r="CZ42" s="47"/>
-    </row>
-    <row r="43" spans="1:104" s="43" customFormat="1" ht="39.950000000000003" hidden="1" customHeight="1" outlineLevel="1">
-      <c r="A43" s="45"/>
-      <c r="B43" s="46">
-        <f t="shared" si="56"/>
-        <v>11</v>
-      </c>
-      <c r="C43" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="D43" s="46" t="s">
-        <v>251</v>
-      </c>
-      <c r="E43" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="F43" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="G43" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="H43" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="I43" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="J43" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="K43" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="L43" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="M43" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="N43" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="O43" s="47"/>
-      <c r="P43" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="Q43" s="47"/>
-      <c r="R43" s="47"/>
-      <c r="S43" s="47"/>
-      <c r="T43" s="47" t="b">
-        <f>T41=T42</f>
-        <v>0</v>
-      </c>
-      <c r="U43" s="47" t="b">
-        <f t="shared" ref="U43:AZ43" si="227">U41=U42</f>
-        <v>0</v>
-      </c>
-      <c r="V43" s="47" t="b">
-        <f t="shared" si="227"/>
-        <v>0</v>
-      </c>
-      <c r="W43" s="47" t="b">
-        <f t="shared" si="227"/>
-        <v>0</v>
-      </c>
-      <c r="X43" s="47" t="b">
-        <f t="shared" si="227"/>
-        <v>0</v>
-      </c>
-      <c r="Y43" s="47" t="b">
-        <f t="shared" si="227"/>
-        <v>0</v>
-      </c>
-      <c r="Z43" s="47" t="b">
-        <f t="shared" si="227"/>
-        <v>0</v>
-      </c>
-      <c r="AA43" s="47" t="b">
-        <f t="shared" si="227"/>
-        <v>0</v>
-      </c>
-      <c r="AB43" s="47" t="b">
-        <f t="shared" si="227"/>
-        <v>0</v>
-      </c>
-      <c r="AC43" s="47" t="b">
-        <f t="shared" si="227"/>
-        <v>0</v>
-      </c>
-      <c r="AD43" s="47" t="b">
-        <f t="shared" si="227"/>
-        <v>0</v>
-      </c>
-      <c r="AE43" s="47" t="b">
-        <f t="shared" si="227"/>
-        <v>0</v>
-      </c>
-      <c r="AF43" s="47" t="b">
-        <f t="shared" si="227"/>
-        <v>0</v>
-      </c>
-      <c r="AG43" s="47" t="b">
-        <f t="shared" si="227"/>
-        <v>0</v>
-      </c>
-      <c r="AH43" s="47" t="b">
-        <f t="shared" si="227"/>
-        <v>0</v>
-      </c>
-      <c r="AI43" s="47" t="b">
-        <f t="shared" si="227"/>
-        <v>0</v>
-      </c>
-      <c r="AJ43" s="47" t="b">
-        <f t="shared" si="227"/>
-        <v>0</v>
-      </c>
-      <c r="AK43" s="47" t="b">
-        <f t="shared" si="227"/>
-        <v>0</v>
-      </c>
-      <c r="AL43" s="47" t="b">
-        <f t="shared" si="227"/>
-        <v>0</v>
-      </c>
-      <c r="AM43" s="47" t="b">
-        <f t="shared" si="227"/>
-        <v>0</v>
-      </c>
-      <c r="AN43" s="47" t="b">
-        <f t="shared" si="227"/>
-        <v>0</v>
-      </c>
-      <c r="AO43" s="47" t="b">
-        <f t="shared" si="227"/>
-        <v>0</v>
-      </c>
-      <c r="AP43" s="47" t="b">
-        <f t="shared" si="227"/>
-        <v>0</v>
-      </c>
-      <c r="AQ43" s="47" t="b">
-        <f t="shared" si="227"/>
-        <v>0</v>
-      </c>
-      <c r="AR43" s="47" t="b">
-        <f t="shared" si="227"/>
-        <v>0</v>
-      </c>
-      <c r="AS43" s="47" t="b">
-        <f t="shared" si="227"/>
-        <v>1</v>
-      </c>
-      <c r="AT43" s="47" t="b">
-        <f t="shared" si="227"/>
-        <v>1</v>
-      </c>
-      <c r="AU43" s="47" t="b">
-        <f t="shared" si="227"/>
-        <v>0</v>
-      </c>
-      <c r="AV43" s="47" t="b">
-        <f t="shared" si="227"/>
-        <v>0</v>
-      </c>
-      <c r="AW43" s="47" t="b">
-        <f t="shared" si="227"/>
-        <v>1</v>
-      </c>
-      <c r="AX43" s="47" t="b">
-        <f t="shared" si="227"/>
-        <v>1</v>
-      </c>
-      <c r="AY43" s="47" t="b">
-        <f t="shared" si="227"/>
-        <v>0</v>
-      </c>
-      <c r="AZ43" s="47" t="b">
-        <f t="shared" si="227"/>
-        <v>1</v>
-      </c>
-      <c r="BA43" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="BB43" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="BC43" s="47" t="b">
-        <f t="shared" ref="BC43:BH43" si="228">BC41=BC42</f>
-        <v>0</v>
-      </c>
-      <c r="BD43" s="47" t="b">
-        <f t="shared" si="228"/>
-        <v>0</v>
-      </c>
-      <c r="BE43" s="47" t="b">
-        <f t="shared" si="228"/>
-        <v>0</v>
-      </c>
-      <c r="BF43" s="47" t="b">
-        <f t="shared" si="228"/>
-        <v>0</v>
-      </c>
-      <c r="BG43" s="47" t="b">
-        <f t="shared" si="228"/>
-        <v>0</v>
-      </c>
-      <c r="BH43" s="47" t="b">
-        <f t="shared" si="228"/>
-        <v>0</v>
-      </c>
-      <c r="BI43" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="BJ43" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="BK43" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="BL43" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="BM43" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="BN43" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="BO43" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="BP43" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="BQ43" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="BR43" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="BS43" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="BT43" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="BU43" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="BV43" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="BW43" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="BX43" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="BY43" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="BZ43" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CA43" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CB43" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CC43" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CD43" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CE43" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CF43" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CG43" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CH43" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CI43" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CJ43" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CK43" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CL43" s="47" t="b">
-        <f>CL41=CL42</f>
-        <v>0</v>
-      </c>
-      <c r="CM43" s="47" t="b">
-        <f t="shared" ref="CM43:CN43" si="229">CM41=CM42</f>
-        <v>0</v>
-      </c>
-      <c r="CN43" s="47" t="b">
-        <f t="shared" si="229"/>
-        <v>0</v>
-      </c>
-      <c r="CO43" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CP43" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CQ43" s="47" t="b">
-        <f t="shared" ref="CQ43" si="230">CQ41=CQ42</f>
-        <v>0</v>
-      </c>
-      <c r="CR43" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CS43" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CT43" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CU43" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CV43" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CW43" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CX43" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CY43" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CZ43" s="47" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="44" spans="1:104" s="42" customFormat="1" ht="44.25" customHeight="1" collapsed="1">
-      <c r="A44" s="45"/>
-      <c r="B44" s="51">
-        <f t="shared" si="56"/>
-        <v>12</v>
-      </c>
-      <c r="C44" s="52">
-        <v>46324.200949074075</v>
-      </c>
-      <c r="D44" s="51" t="s">
-        <v>254</v>
-      </c>
-      <c r="E44" s="51"/>
-      <c r="F44" s="51"/>
-      <c r="G44" s="104"/>
-      <c r="H44" s="51" t="s">
-        <v>557</v>
-      </c>
-      <c r="I44" s="105"/>
-      <c r="J44" s="53" t="s">
-        <v>592</v>
-      </c>
-      <c r="K44" s="53"/>
-      <c r="L44" s="51"/>
-      <c r="M44" s="51"/>
-      <c r="N44" s="51"/>
-      <c r="O44" s="51" t="str">
-        <f>IF(COUNTIF(C46:CZ46,"FALSE")&gt;0,"NG","OK")</f>
-        <v>NG</v>
-      </c>
-      <c r="P44" s="51"/>
-      <c r="Q44" s="51" t="s">
-        <v>441</v>
-      </c>
-      <c r="R44" s="51" t="s">
-        <v>442</v>
-      </c>
-      <c r="S44" s="51" t="s">
-        <v>443</v>
-      </c>
-      <c r="T44" s="51" t="s">
-        <v>39</v>
-      </c>
-      <c r="U44" s="51" t="s">
-        <v>28</v>
-      </c>
-      <c r="V44" s="51" t="s">
-        <v>38</v>
-      </c>
-      <c r="W44" s="51" t="s">
-        <v>79</v>
-      </c>
-      <c r="X44" s="51" t="s">
-        <v>444</v>
-      </c>
-      <c r="Y44" s="51" t="s">
-        <v>444</v>
-      </c>
-      <c r="Z44" s="51" t="s">
-        <v>444</v>
-      </c>
-      <c r="AA44" s="51" t="s">
-        <v>444</v>
-      </c>
-      <c r="AB44" s="51" t="s">
-        <v>595</v>
-      </c>
-      <c r="AC44" s="51">
-        <v>66</v>
-      </c>
-      <c r="AD44" s="51" t="s">
-        <v>446</v>
-      </c>
-      <c r="AE44" s="51">
-        <v>1.2</v>
-      </c>
-      <c r="AF44" s="51" t="s">
-        <v>558</v>
-      </c>
-      <c r="AG44" s="51" t="s">
-        <v>433</v>
-      </c>
-      <c r="AH44" s="51" t="s">
-        <v>559</v>
-      </c>
-      <c r="AI44" s="51" t="s">
-        <v>449</v>
-      </c>
-      <c r="AJ44" s="51" t="s">
-        <v>560</v>
-      </c>
-      <c r="AK44" s="51">
-        <v>4</v>
-      </c>
-      <c r="AL44" s="51">
-        <v>159</v>
-      </c>
-      <c r="AM44" s="54" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(J44," ",""),"-","")</f>
-        <v>378206SATC10M6</v>
-      </c>
-      <c r="AN44" s="108" t="s">
-        <v>593</v>
-      </c>
-      <c r="AO44" s="108" t="s">
-        <v>594</v>
-      </c>
-      <c r="AP44" s="51" t="s">
-        <v>512</v>
-      </c>
-      <c r="AQ44" s="54" t="str">
-        <f>SUBSTITUTE(J44," ","")</f>
-        <v>37820-6SA-TC10-M6</v>
-      </c>
-      <c r="AR44" s="54" t="str">
-        <f>IF(RIGHT(SUBSTITUTE(J44," ",""),4)="0-M6",LEFT(SUBSTITUTE(J44," ",""),LEN(SUBSTITUTE(J44," ",""))-4),SUBSTITUTE(J44," ",""))</f>
-        <v>37820-6SA-TC1</v>
-      </c>
-      <c r="AS44" s="54">
-        <f>K44</f>
-        <v>0</v>
-      </c>
-      <c r="AT44" s="51"/>
-      <c r="AU44" s="51" t="s">
-        <v>452</v>
-      </c>
-      <c r="AV44" s="51" t="s">
-        <v>453</v>
-      </c>
-      <c r="AW44" s="106"/>
-      <c r="AX44" s="54">
-        <f>K44</f>
-        <v>0</v>
-      </c>
-      <c r="AY44" s="51" t="s">
-        <v>454</v>
-      </c>
-      <c r="AZ44" s="51"/>
-      <c r="BA44" s="51"/>
-      <c r="BB44" s="51"/>
-      <c r="BC44" s="51" t="s">
-        <v>490</v>
-      </c>
-      <c r="BD44" s="54" t="str">
-        <f>AP44</f>
-        <v>MG1CA020-2.30</v>
-      </c>
-      <c r="BE44" s="51" t="s">
-        <v>595</v>
-      </c>
-      <c r="BF44" s="51" t="s">
-        <v>461</v>
-      </c>
-      <c r="BG44" s="51" t="s">
-        <v>462</v>
-      </c>
-      <c r="BH44" s="51" t="s">
-        <v>564</v>
-      </c>
-      <c r="BI44" s="51" t="s">
-        <v>596</v>
-      </c>
-      <c r="BJ44" s="54" t="str">
-        <f t="shared" si="162"/>
-        <v>3</v>
-      </c>
-      <c r="BK44" s="54" t="str">
-        <f t="shared" si="162"/>
-        <v>7</v>
-      </c>
-      <c r="BL44" s="54" t="str">
-        <f t="shared" si="162"/>
-        <v>8</v>
-      </c>
-      <c r="BM44" s="54" t="str">
-        <f t="shared" si="162"/>
-        <v>0</v>
-      </c>
-      <c r="BN44" s="54" t="str">
-        <f t="shared" si="162"/>
-        <v>5</v>
-      </c>
-      <c r="BO44" s="54" t="str">
-        <f t="shared" si="162"/>
-        <v>-</v>
-      </c>
-      <c r="BP44" s="54" t="str">
-        <f t="shared" si="162"/>
-        <v>6</v>
-      </c>
-      <c r="BQ44" s="54" t="str">
-        <f t="shared" si="162"/>
-        <v>S</v>
-      </c>
-      <c r="BR44" s="54" t="str">
-        <f t="shared" si="162"/>
-        <v>A</v>
-      </c>
-      <c r="BS44" s="54" t="str">
-        <f t="shared" si="162"/>
-        <v>-</v>
-      </c>
-      <c r="BT44" s="54" t="str">
-        <f t="shared" si="162"/>
-        <v>T</v>
-      </c>
-      <c r="BU44" s="54" t="str">
-        <f t="shared" si="162"/>
-        <v>C</v>
-      </c>
-      <c r="BV44" s="54" t="str">
-        <f t="shared" si="162"/>
-        <v>1</v>
-      </c>
-      <c r="BW44" s="54" t="str">
-        <f t="shared" si="162"/>
-        <v>0</v>
-      </c>
-      <c r="BX44" s="55" t="str">
-        <f>DEC2HEX(CODE(BJ44),2)</f>
-        <v>33</v>
-      </c>
-      <c r="BY44" s="55" t="str">
-        <f t="shared" ref="BY44:BY45" si="231">DEC2HEX(CODE(BK44),2)</f>
-        <v>37</v>
-      </c>
-      <c r="BZ44" s="55" t="str">
-        <f t="shared" ref="BZ44:BZ45" si="232">DEC2HEX(CODE(BL44),2)</f>
-        <v>38</v>
-      </c>
-      <c r="CA44" s="55" t="str">
-        <f t="shared" ref="CA44:CA45" si="233">DEC2HEX(CODE(BM44),2)</f>
-        <v>30</v>
-      </c>
-      <c r="CB44" s="55" t="str">
-        <f t="shared" ref="CB44:CB45" si="234">DEC2HEX(CODE(BN44),2)</f>
-        <v>35</v>
-      </c>
-      <c r="CC44" s="55" t="str">
-        <f t="shared" ref="CC44:CC45" si="235">DEC2HEX(CODE(BO44),2)</f>
-        <v>2D</v>
-      </c>
-      <c r="CD44" s="55" t="str">
-        <f t="shared" ref="CD44:CD45" si="236">DEC2HEX(CODE(BP44),2)</f>
-        <v>36</v>
-      </c>
-      <c r="CE44" s="55" t="str">
-        <f t="shared" ref="CE44:CE45" si="237">DEC2HEX(CODE(BQ44),2)</f>
-        <v>53</v>
-      </c>
-      <c r="CF44" s="55" t="str">
-        <f t="shared" ref="CF44:CF45" si="238">DEC2HEX(CODE(BR44),2)</f>
-        <v>41</v>
-      </c>
-      <c r="CG44" s="55" t="str">
-        <f t="shared" ref="CG44:CG45" si="239">DEC2HEX(CODE(BS44),2)</f>
-        <v>2D</v>
-      </c>
-      <c r="CH44" s="55" t="str">
-        <f t="shared" ref="CH44:CH45" si="240">DEC2HEX(CODE(BT44),2)</f>
-        <v>54</v>
-      </c>
-      <c r="CI44" s="55" t="str">
-        <f t="shared" ref="CI44:CI45" si="241">DEC2HEX(CODE(BU44),2)</f>
-        <v>43</v>
-      </c>
-      <c r="CJ44" s="55" t="str">
-        <f t="shared" ref="CJ44:CJ45" si="242">DEC2HEX(CODE(BV44),2)</f>
-        <v>31</v>
-      </c>
-      <c r="CK44" s="55" t="str">
-        <f t="shared" ref="CK44:CK45" si="243">DEC2HEX(CODE(BW44),2)</f>
-        <v>30</v>
-      </c>
-      <c r="CL44" s="54" t="str">
-        <f>BX44&amp;BY44&amp;BZ44&amp;CA44&amp;CB44&amp;CC44&amp;CD44&amp;CE44&amp;CF44&amp;CG44&amp;CH44&amp;CI44&amp;CJ44&amp;CK44</f>
-        <v>33373830352D3653412D54433130</v>
-      </c>
-      <c r="CM44" s="104" t="s">
-        <v>513</v>
-      </c>
-      <c r="CN44" s="51" t="s">
-        <v>470</v>
-      </c>
-      <c r="CO44" s="51" t="s">
-        <v>240</v>
-      </c>
-      <c r="CP44" s="51" t="s">
-        <v>240</v>
-      </c>
-      <c r="CQ44" s="51" t="s">
-        <v>240</v>
-      </c>
-      <c r="CR44" s="56" t="s">
-        <v>240</v>
-      </c>
-      <c r="CS44" s="54" t="str">
-        <f>SUBSTITUTE(J44," ","")</f>
-        <v>37820-6SA-TC10-M6</v>
-      </c>
-      <c r="CT44" s="108" t="s">
-        <v>597</v>
-      </c>
-      <c r="CU44" s="51" t="s">
-        <v>596</v>
-      </c>
-      <c r="CV44" s="51" t="s">
-        <v>596</v>
-      </c>
-      <c r="CW44" s="56"/>
-      <c r="CX44" s="51" t="str">
-        <f>AR44</f>
-        <v>37820-6SA-TC1</v>
-      </c>
-      <c r="CY44" s="106" t="s">
-        <v>487</v>
-      </c>
-      <c r="CZ44" s="51" t="s">
-        <v>598</v>
-      </c>
-    </row>
-    <row r="45" spans="1:104" s="42" customFormat="1" ht="44.25" hidden="1" customHeight="1" outlineLevel="1" collapsed="1">
-      <c r="A45" s="45"/>
-      <c r="B45" s="47">
-        <f t="shared" si="56"/>
-        <v>12</v>
-      </c>
-      <c r="C45" s="57"/>
-      <c r="D45" s="47" t="s">
-        <v>245</v>
-      </c>
-      <c r="E45" s="47"/>
-      <c r="F45" s="47"/>
-      <c r="G45" s="57"/>
-      <c r="H45" s="47"/>
-      <c r="I45" s="47"/>
-      <c r="J45" s="47"/>
-      <c r="K45" s="47"/>
-      <c r="L45" s="47"/>
-      <c r="M45" s="47"/>
-      <c r="N45" s="47"/>
-      <c r="O45" s="47"/>
-      <c r="P45" s="47"/>
-      <c r="Q45" s="47"/>
-      <c r="R45" s="47"/>
-      <c r="S45" s="47"/>
-      <c r="T45" s="47"/>
-      <c r="U45" s="47"/>
-      <c r="V45" s="47"/>
-      <c r="W45" s="47"/>
-      <c r="X45" s="47"/>
-      <c r="Y45" s="47"/>
-      <c r="Z45" s="47"/>
-      <c r="AA45" s="47"/>
-      <c r="AB45" s="47"/>
-      <c r="AC45" s="47"/>
-      <c r="AD45" s="47"/>
-      <c r="AE45" s="47"/>
-      <c r="AF45" s="47"/>
-      <c r="AG45" s="47"/>
-      <c r="AH45" s="47"/>
-      <c r="AI45" s="47"/>
-      <c r="AJ45" s="47"/>
-      <c r="AK45" s="47"/>
-      <c r="AL45" s="47"/>
-      <c r="AM45" s="47"/>
-      <c r="AN45" s="47"/>
-      <c r="AO45" s="47"/>
-      <c r="AP45" s="47"/>
-      <c r="AQ45" s="47"/>
-      <c r="AR45" s="47"/>
-      <c r="AS45" s="47"/>
-      <c r="AT45" s="47"/>
-      <c r="AU45" s="47"/>
-      <c r="AV45" s="47"/>
-      <c r="AW45" s="107"/>
-      <c r="AX45" s="47"/>
-      <c r="AY45" s="47"/>
-      <c r="AZ45" s="47"/>
-      <c r="BA45" s="47"/>
-      <c r="BB45" s="47"/>
-      <c r="BC45" s="47"/>
-      <c r="BD45" s="47"/>
-      <c r="BE45" s="47"/>
-      <c r="BF45" s="47"/>
-      <c r="BG45" s="47"/>
-      <c r="BH45" s="47"/>
-      <c r="BI45" s="47"/>
-      <c r="BJ45" s="47" t="str">
-        <f t="shared" si="162"/>
-        <v/>
-      </c>
-      <c r="BK45" s="47" t="str">
-        <f t="shared" si="162"/>
-        <v/>
-      </c>
-      <c r="BL45" s="47" t="str">
-        <f t="shared" si="162"/>
-        <v/>
-      </c>
-      <c r="BM45" s="47" t="str">
-        <f t="shared" si="162"/>
-        <v/>
-      </c>
-      <c r="BN45" s="47" t="str">
-        <f t="shared" si="162"/>
-        <v/>
-      </c>
-      <c r="BO45" s="47" t="str">
-        <f t="shared" si="162"/>
-        <v/>
-      </c>
-      <c r="BP45" s="47" t="str">
-        <f t="shared" si="162"/>
-        <v/>
-      </c>
-      <c r="BQ45" s="47" t="str">
-        <f t="shared" si="162"/>
-        <v/>
-      </c>
-      <c r="BR45" s="47" t="str">
-        <f t="shared" si="162"/>
-        <v/>
-      </c>
-      <c r="BS45" s="47" t="str">
-        <f t="shared" si="162"/>
-        <v/>
-      </c>
-      <c r="BT45" s="47" t="str">
-        <f t="shared" si="162"/>
-        <v/>
-      </c>
-      <c r="BU45" s="47" t="str">
-        <f t="shared" si="162"/>
-        <v/>
-      </c>
-      <c r="BV45" s="47" t="str">
-        <f t="shared" si="162"/>
-        <v/>
-      </c>
-      <c r="BW45" s="47" t="str">
-        <f t="shared" si="162"/>
-        <v/>
-      </c>
-      <c r="BX45" s="47" t="e">
-        <f>DEC2HEX(CODE(BJ45),2)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="BY45" s="47" t="e">
-        <f t="shared" si="231"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="BZ45" s="47" t="e">
-        <f t="shared" si="232"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="CA45" s="47" t="e">
-        <f t="shared" si="233"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="CB45" s="47" t="e">
-        <f t="shared" si="234"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="CC45" s="47" t="e">
-        <f t="shared" si="235"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="CD45" s="47" t="e">
-        <f t="shared" si="236"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="CE45" s="47" t="e">
-        <f t="shared" si="237"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="CF45" s="47" t="e">
-        <f t="shared" si="238"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="CG45" s="47" t="e">
-        <f t="shared" si="239"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="CH45" s="47" t="e">
-        <f t="shared" si="240"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="CI45" s="47" t="e">
-        <f t="shared" si="241"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="CJ45" s="47" t="e">
-        <f t="shared" si="242"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="CK45" s="47" t="e">
-        <f t="shared" si="243"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="CL45" s="47"/>
-      <c r="CM45" s="58"/>
-      <c r="CN45" s="47"/>
-      <c r="CO45" s="47"/>
-      <c r="CP45" s="47"/>
-      <c r="CQ45" s="47"/>
-      <c r="CR45" s="47"/>
-      <c r="CS45" s="47" t="str">
-        <f>SUBSTITUTE(J45," ","")</f>
-        <v/>
-      </c>
-      <c r="CT45" s="47"/>
-      <c r="CU45" s="47"/>
-      <c r="CV45" s="47"/>
-      <c r="CW45" s="47"/>
-      <c r="CX45" s="47"/>
-      <c r="CY45" s="47"/>
-      <c r="CZ45" s="47"/>
-    </row>
-    <row r="46" spans="1:104" s="43" customFormat="1" ht="39.950000000000003" hidden="1" customHeight="1" outlineLevel="1">
-      <c r="A46" s="45"/>
-      <c r="B46" s="46">
-        <f t="shared" si="56"/>
-        <v>12</v>
-      </c>
-      <c r="C46" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="D46" s="46" t="s">
-        <v>251</v>
-      </c>
-      <c r="E46" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="F46" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="G46" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="H46" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="I46" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="J46" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="K46" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="L46" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="M46" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="N46" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="O46" s="47"/>
-      <c r="P46" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="Q46" s="47"/>
-      <c r="R46" s="47"/>
-      <c r="S46" s="47"/>
-      <c r="T46" s="47" t="b">
-        <f>T44=T45</f>
-        <v>0</v>
-      </c>
-      <c r="U46" s="47" t="b">
-        <f t="shared" ref="U46:AZ46" si="244">U44=U45</f>
-        <v>0</v>
-      </c>
-      <c r="V46" s="47" t="b">
-        <f t="shared" si="244"/>
-        <v>0</v>
-      </c>
-      <c r="W46" s="47" t="b">
-        <f t="shared" si="244"/>
-        <v>0</v>
-      </c>
-      <c r="X46" s="47" t="b">
-        <f t="shared" si="244"/>
-        <v>0</v>
-      </c>
-      <c r="Y46" s="47" t="b">
-        <f t="shared" si="244"/>
-        <v>0</v>
-      </c>
-      <c r="Z46" s="47" t="b">
-        <f t="shared" si="244"/>
-        <v>0</v>
-      </c>
-      <c r="AA46" s="47" t="b">
-        <f t="shared" si="244"/>
-        <v>0</v>
-      </c>
-      <c r="AB46" s="47" t="b">
-        <f t="shared" si="244"/>
-        <v>0</v>
-      </c>
-      <c r="AC46" s="47" t="b">
-        <f t="shared" si="244"/>
-        <v>0</v>
-      </c>
-      <c r="AD46" s="47" t="b">
-        <f t="shared" si="244"/>
-        <v>0</v>
-      </c>
-      <c r="AE46" s="47" t="b">
-        <f t="shared" si="244"/>
-        <v>0</v>
-      </c>
-      <c r="AF46" s="47" t="b">
-        <f t="shared" si="244"/>
-        <v>0</v>
-      </c>
-      <c r="AG46" s="47" t="b">
-        <f t="shared" si="244"/>
-        <v>0</v>
-      </c>
-      <c r="AH46" s="47" t="b">
-        <f t="shared" si="244"/>
-        <v>0</v>
-      </c>
-      <c r="AI46" s="47" t="b">
-        <f t="shared" si="244"/>
-        <v>0</v>
-      </c>
-      <c r="AJ46" s="47" t="b">
-        <f t="shared" si="244"/>
-        <v>0</v>
-      </c>
-      <c r="AK46" s="47" t="b">
-        <f t="shared" si="244"/>
-        <v>0</v>
-      </c>
-      <c r="AL46" s="47" t="b">
-        <f t="shared" si="244"/>
-        <v>0</v>
-      </c>
-      <c r="AM46" s="47" t="b">
-        <f t="shared" si="244"/>
-        <v>0</v>
-      </c>
-      <c r="AN46" s="47" t="b">
-        <f t="shared" si="244"/>
-        <v>0</v>
-      </c>
-      <c r="AO46" s="47" t="b">
-        <f t="shared" si="244"/>
-        <v>0</v>
-      </c>
-      <c r="AP46" s="47" t="b">
-        <f t="shared" si="244"/>
-        <v>0</v>
-      </c>
-      <c r="AQ46" s="47" t="b">
-        <f t="shared" si="244"/>
-        <v>0</v>
-      </c>
-      <c r="AR46" s="47" t="b">
-        <f t="shared" si="244"/>
-        <v>0</v>
-      </c>
-      <c r="AS46" s="47" t="b">
-        <f t="shared" si="244"/>
-        <v>1</v>
-      </c>
-      <c r="AT46" s="47" t="b">
-        <f t="shared" si="244"/>
-        <v>1</v>
-      </c>
-      <c r="AU46" s="47" t="b">
-        <f t="shared" si="244"/>
-        <v>0</v>
-      </c>
-      <c r="AV46" s="47" t="b">
-        <f t="shared" si="244"/>
-        <v>0</v>
-      </c>
-      <c r="AW46" s="47" t="b">
-        <f t="shared" si="244"/>
-        <v>1</v>
-      </c>
-      <c r="AX46" s="47" t="b">
-        <f t="shared" si="244"/>
-        <v>1</v>
-      </c>
-      <c r="AY46" s="47" t="b">
-        <f t="shared" si="244"/>
-        <v>0</v>
-      </c>
-      <c r="AZ46" s="47" t="b">
-        <f t="shared" si="244"/>
-        <v>1</v>
-      </c>
-      <c r="BA46" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="BB46" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="BC46" s="47" t="b">
-        <f t="shared" ref="BC46:BH46" si="245">BC44=BC45</f>
-        <v>0</v>
-      </c>
-      <c r="BD46" s="47" t="b">
-        <f t="shared" si="245"/>
-        <v>0</v>
-      </c>
-      <c r="BE46" s="47" t="b">
-        <f t="shared" si="245"/>
-        <v>0</v>
-      </c>
-      <c r="BF46" s="47" t="b">
-        <f t="shared" si="245"/>
-        <v>0</v>
-      </c>
-      <c r="BG46" s="47" t="b">
-        <f t="shared" si="245"/>
-        <v>0</v>
-      </c>
-      <c r="BH46" s="47" t="b">
-        <f t="shared" si="245"/>
-        <v>0</v>
-      </c>
-      <c r="BI46" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="BJ46" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="BK46" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="BL46" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="BM46" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="BN46" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="BO46" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="BP46" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="BQ46" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="BR46" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="BS46" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="BT46" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="BU46" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="BV46" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="BW46" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="BX46" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="BY46" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="BZ46" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CA46" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CB46" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CC46" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CD46" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CE46" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CF46" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CG46" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CH46" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CI46" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CJ46" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CK46" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CL46" s="47" t="b">
-        <f>CL44=CL45</f>
-        <v>0</v>
-      </c>
-      <c r="CM46" s="47" t="b">
-        <f t="shared" ref="CM46:CN46" si="246">CM44=CM45</f>
-        <v>0</v>
-      </c>
-      <c r="CN46" s="47" t="b">
-        <f t="shared" si="246"/>
-        <v>0</v>
-      </c>
-      <c r="CO46" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CP46" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CQ46" s="47" t="b">
-        <f t="shared" ref="CQ46" si="247">CQ44=CQ45</f>
-        <v>0</v>
-      </c>
-      <c r="CR46" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CS46" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CT46" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CU46" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CV46" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CW46" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CX46" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CY46" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CZ46" s="47" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="47" spans="1:104" s="42" customFormat="1" ht="44.25" customHeight="1" collapsed="1">
-      <c r="A47" s="45"/>
-      <c r="B47" s="51">
-        <f t="shared" si="56"/>
-        <v>13</v>
-      </c>
-      <c r="C47" s="52">
-        <v>46324.200960648152</v>
-      </c>
-      <c r="D47" s="51" t="s">
-        <v>254</v>
-      </c>
-      <c r="E47" s="51"/>
-      <c r="F47" s="51"/>
-      <c r="G47" s="104"/>
-      <c r="H47" s="51" t="s">
-        <v>557</v>
-      </c>
-      <c r="I47" s="105"/>
-      <c r="J47" s="53" t="s">
-        <v>599</v>
-      </c>
-      <c r="K47" s="53"/>
-      <c r="L47" s="51"/>
-      <c r="M47" s="51"/>
-      <c r="N47" s="51"/>
-      <c r="O47" s="51" t="str">
-        <f>IF(COUNTIF(C49:CZ49,"FALSE")&gt;0,"NG","OK")</f>
-        <v>NG</v>
-      </c>
-      <c r="P47" s="51"/>
-      <c r="Q47" s="51" t="s">
-        <v>441</v>
-      </c>
-      <c r="R47" s="51" t="s">
-        <v>442</v>
-      </c>
-      <c r="S47" s="51" t="s">
-        <v>443</v>
-      </c>
-      <c r="T47" s="51" t="s">
-        <v>39</v>
-      </c>
-      <c r="U47" s="51" t="s">
-        <v>28</v>
-      </c>
-      <c r="V47" s="51" t="s">
-        <v>38</v>
-      </c>
-      <c r="W47" s="51" t="s">
-        <v>79</v>
-      </c>
-      <c r="X47" s="51" t="s">
-        <v>444</v>
-      </c>
-      <c r="Y47" s="51" t="s">
-        <v>444</v>
-      </c>
-      <c r="Z47" s="51" t="s">
-        <v>444</v>
-      </c>
-      <c r="AA47" s="51" t="s">
-        <v>444</v>
-      </c>
-      <c r="AB47" s="51" t="s">
-        <v>563</v>
-      </c>
-      <c r="AC47" s="51">
-        <v>66</v>
-      </c>
-      <c r="AD47" s="51" t="s">
-        <v>446</v>
-      </c>
-      <c r="AE47" s="51">
-        <v>1.2</v>
-      </c>
-      <c r="AF47" s="51" t="s">
-        <v>558</v>
-      </c>
-      <c r="AG47" s="51" t="s">
-        <v>433</v>
-      </c>
-      <c r="AH47" s="51" t="s">
-        <v>600</v>
-      </c>
-      <c r="AI47" s="51" t="s">
-        <v>448</v>
-      </c>
-      <c r="AJ47" s="51" t="s">
-        <v>601</v>
-      </c>
-      <c r="AK47" s="51">
-        <v>4</v>
-      </c>
-      <c r="AL47" s="51">
-        <v>159</v>
-      </c>
-      <c r="AM47" s="54" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(J47," ",""),"-","")</f>
-        <v>378206SAN210M6</v>
-      </c>
-      <c r="AN47" s="108" t="s">
-        <v>602</v>
-      </c>
-      <c r="AO47" s="108" t="s">
-        <v>603</v>
-      </c>
-      <c r="AP47" s="51" t="s">
-        <v>512</v>
-      </c>
-      <c r="AQ47" s="54" t="str">
-        <f>SUBSTITUTE(J47," ","")</f>
-        <v>37820-6SA-N210-M6</v>
-      </c>
-      <c r="AR47" s="54" t="str">
-        <f>IF(RIGHT(SUBSTITUTE(J47," ",""),4)="0-M6",LEFT(SUBSTITUTE(J47," ",""),LEN(SUBSTITUTE(J47," ",""))-4),SUBSTITUTE(J47," ",""))</f>
-        <v>37820-6SA-N21</v>
-      </c>
-      <c r="AS47" s="54">
-        <f>K47</f>
-        <v>0</v>
-      </c>
-      <c r="AT47" s="51"/>
-      <c r="AU47" s="51" t="s">
-        <v>452</v>
-      </c>
-      <c r="AV47" s="51" t="s">
-        <v>453</v>
-      </c>
-      <c r="AW47" s="106"/>
-      <c r="AX47" s="54">
-        <f>K47</f>
-        <v>0</v>
-      </c>
-      <c r="AY47" s="51" t="s">
-        <v>454</v>
-      </c>
-      <c r="AZ47" s="51"/>
-      <c r="BA47" s="51"/>
-      <c r="BB47" s="51"/>
-      <c r="BC47" s="51" t="s">
-        <v>490</v>
-      </c>
-      <c r="BD47" s="54" t="str">
-        <f>AP47</f>
-        <v>MG1CA020-2.30</v>
-      </c>
-      <c r="BE47" s="51" t="s">
-        <v>563</v>
-      </c>
-      <c r="BF47" s="51" t="s">
-        <v>461</v>
-      </c>
-      <c r="BG47" s="51" t="s">
-        <v>462</v>
-      </c>
-      <c r="BH47" s="51" t="s">
-        <v>564</v>
-      </c>
-      <c r="BI47" s="51" t="s">
-        <v>604</v>
-      </c>
-      <c r="BJ47" s="54" t="str">
-        <f t="shared" si="162"/>
-        <v>3</v>
-      </c>
-      <c r="BK47" s="54" t="str">
-        <f t="shared" si="162"/>
-        <v>7</v>
-      </c>
-      <c r="BL47" s="54" t="str">
-        <f t="shared" si="162"/>
-        <v>8</v>
-      </c>
-      <c r="BM47" s="54" t="str">
-        <f t="shared" si="162"/>
-        <v>0</v>
-      </c>
-      <c r="BN47" s="54" t="str">
-        <f t="shared" si="162"/>
-        <v>5</v>
-      </c>
-      <c r="BO47" s="54" t="str">
-        <f t="shared" si="162"/>
-        <v>-</v>
-      </c>
-      <c r="BP47" s="54" t="str">
-        <f t="shared" si="162"/>
-        <v>6</v>
-      </c>
-      <c r="BQ47" s="54" t="str">
-        <f t="shared" si="162"/>
-        <v>S</v>
-      </c>
-      <c r="BR47" s="54" t="str">
-        <f t="shared" si="162"/>
-        <v>A</v>
-      </c>
-      <c r="BS47" s="54" t="str">
-        <f t="shared" si="162"/>
-        <v>-</v>
-      </c>
-      <c r="BT47" s="54" t="str">
-        <f t="shared" si="162"/>
-        <v>N</v>
-      </c>
-      <c r="BU47" s="54" t="str">
-        <f t="shared" si="162"/>
-        <v>2</v>
-      </c>
-      <c r="BV47" s="54" t="str">
-        <f t="shared" si="162"/>
-        <v>1</v>
-      </c>
-      <c r="BW47" s="54" t="str">
-        <f t="shared" si="162"/>
-        <v>0</v>
-      </c>
-      <c r="BX47" s="55" t="str">
-        <f>DEC2HEX(CODE(BJ47),2)</f>
-        <v>33</v>
-      </c>
-      <c r="BY47" s="55" t="str">
-        <f t="shared" ref="BY47:BY48" si="248">DEC2HEX(CODE(BK47),2)</f>
-        <v>37</v>
-      </c>
-      <c r="BZ47" s="55" t="str">
-        <f t="shared" ref="BZ47:BZ48" si="249">DEC2HEX(CODE(BL47),2)</f>
-        <v>38</v>
-      </c>
-      <c r="CA47" s="55" t="str">
-        <f t="shared" ref="CA47:CA48" si="250">DEC2HEX(CODE(BM47),2)</f>
-        <v>30</v>
-      </c>
-      <c r="CB47" s="55" t="str">
-        <f t="shared" ref="CB47:CB48" si="251">DEC2HEX(CODE(BN47),2)</f>
-        <v>35</v>
-      </c>
-      <c r="CC47" s="55" t="str">
-        <f t="shared" ref="CC47:CC48" si="252">DEC2HEX(CODE(BO47),2)</f>
-        <v>2D</v>
-      </c>
-      <c r="CD47" s="55" t="str">
-        <f t="shared" ref="CD47:CD48" si="253">DEC2HEX(CODE(BP47),2)</f>
-        <v>36</v>
-      </c>
-      <c r="CE47" s="55" t="str">
-        <f t="shared" ref="CE47:CE48" si="254">DEC2HEX(CODE(BQ47),2)</f>
-        <v>53</v>
-      </c>
-      <c r="CF47" s="55" t="str">
-        <f t="shared" ref="CF47:CF48" si="255">DEC2HEX(CODE(BR47),2)</f>
-        <v>41</v>
-      </c>
-      <c r="CG47" s="55" t="str">
-        <f t="shared" ref="CG47:CG48" si="256">DEC2HEX(CODE(BS47),2)</f>
-        <v>2D</v>
-      </c>
-      <c r="CH47" s="55" t="str">
-        <f t="shared" ref="CH47:CH48" si="257">DEC2HEX(CODE(BT47),2)</f>
-        <v>4E</v>
-      </c>
-      <c r="CI47" s="55" t="str">
-        <f t="shared" ref="CI47:CI48" si="258">DEC2HEX(CODE(BU47),2)</f>
-        <v>32</v>
-      </c>
-      <c r="CJ47" s="55" t="str">
-        <f t="shared" ref="CJ47:CJ48" si="259">DEC2HEX(CODE(BV47),2)</f>
-        <v>31</v>
-      </c>
-      <c r="CK47" s="55" t="str">
-        <f t="shared" ref="CK47:CK48" si="260">DEC2HEX(CODE(BW47),2)</f>
-        <v>30</v>
-      </c>
-      <c r="CL47" s="54" t="str">
-        <f>BX47&amp;BY47&amp;BZ47&amp;CA47&amp;CB47&amp;CC47&amp;CD47&amp;CE47&amp;CF47&amp;CG47&amp;CH47&amp;CI47&amp;CJ47&amp;CK47</f>
-        <v>33373830352D3653412D4E323130</v>
-      </c>
-      <c r="CM47" s="104" t="s">
-        <v>513</v>
-      </c>
-      <c r="CN47" s="51" t="s">
-        <v>470</v>
-      </c>
-      <c r="CO47" s="51" t="s">
-        <v>240</v>
-      </c>
-      <c r="CP47" s="51" t="s">
-        <v>240</v>
-      </c>
-      <c r="CQ47" s="51" t="s">
-        <v>240</v>
-      </c>
-      <c r="CR47" s="56" t="s">
-        <v>240</v>
-      </c>
-      <c r="CS47" s="54" t="str">
-        <f>SUBSTITUTE(J47," ","")</f>
-        <v>37820-6SA-N210-M6</v>
-      </c>
-      <c r="CT47" s="108" t="s">
-        <v>605</v>
-      </c>
-      <c r="CU47" s="51" t="s">
-        <v>604</v>
-      </c>
-      <c r="CV47" s="51" t="s">
-        <v>604</v>
-      </c>
-      <c r="CW47" s="56"/>
-      <c r="CX47" s="51" t="str">
-        <f>AR47</f>
-        <v>37820-6SA-N21</v>
-      </c>
-      <c r="CY47" s="106" t="s">
-        <v>606</v>
-      </c>
-      <c r="CZ47" s="51" t="s">
-        <v>607</v>
-      </c>
-    </row>
-    <row r="48" spans="1:104" s="42" customFormat="1" ht="44.25" hidden="1" customHeight="1" outlineLevel="1" collapsed="1">
-      <c r="A48" s="45"/>
-      <c r="B48" s="47">
-        <f t="shared" si="56"/>
-        <v>13</v>
-      </c>
-      <c r="C48" s="57"/>
-      <c r="D48" s="47" t="s">
-        <v>245</v>
-      </c>
-      <c r="E48" s="47"/>
-      <c r="F48" s="47"/>
-      <c r="G48" s="57"/>
-      <c r="H48" s="47"/>
-      <c r="I48" s="47"/>
-      <c r="J48" s="47"/>
-      <c r="K48" s="47"/>
-      <c r="L48" s="47"/>
-      <c r="M48" s="47"/>
-      <c r="N48" s="47"/>
-      <c r="O48" s="47"/>
-      <c r="P48" s="47"/>
-      <c r="Q48" s="47"/>
-      <c r="R48" s="47"/>
-      <c r="S48" s="47"/>
-      <c r="T48" s="47"/>
-      <c r="U48" s="47"/>
-      <c r="V48" s="47"/>
-      <c r="W48" s="47"/>
-      <c r="X48" s="47"/>
-      <c r="Y48" s="47"/>
-      <c r="Z48" s="47"/>
-      <c r="AA48" s="47"/>
-      <c r="AB48" s="47"/>
-      <c r="AC48" s="47"/>
-      <c r="AD48" s="47"/>
-      <c r="AE48" s="47"/>
-      <c r="AF48" s="47"/>
-      <c r="AG48" s="47"/>
-      <c r="AH48" s="47"/>
-      <c r="AI48" s="47"/>
-      <c r="AJ48" s="47"/>
-      <c r="AK48" s="47"/>
-      <c r="AL48" s="47"/>
-      <c r="AM48" s="47"/>
-      <c r="AN48" s="47"/>
-      <c r="AO48" s="47"/>
-      <c r="AP48" s="47"/>
-      <c r="AQ48" s="47"/>
-      <c r="AR48" s="47"/>
-      <c r="AS48" s="47"/>
-      <c r="AT48" s="47"/>
-      <c r="AU48" s="47"/>
-      <c r="AV48" s="47"/>
-      <c r="AW48" s="107"/>
-      <c r="AX48" s="47"/>
-      <c r="AY48" s="47"/>
-      <c r="AZ48" s="47"/>
-      <c r="BA48" s="47"/>
-      <c r="BB48" s="47"/>
-      <c r="BC48" s="47"/>
-      <c r="BD48" s="47"/>
-      <c r="BE48" s="47"/>
-      <c r="BF48" s="47"/>
-      <c r="BG48" s="47"/>
-      <c r="BH48" s="47"/>
-      <c r="BI48" s="47"/>
-      <c r="BJ48" s="47" t="str">
-        <f t="shared" ref="BJ48:BW51" si="261">MID($BI48,BJ$6,1)</f>
-        <v/>
-      </c>
-      <c r="BK48" s="47" t="str">
-        <f t="shared" si="261"/>
-        <v/>
-      </c>
-      <c r="BL48" s="47" t="str">
-        <f t="shared" si="261"/>
-        <v/>
-      </c>
-      <c r="BM48" s="47" t="str">
-        <f t="shared" si="261"/>
-        <v/>
-      </c>
-      <c r="BN48" s="47" t="str">
-        <f t="shared" si="261"/>
-        <v/>
-      </c>
-      <c r="BO48" s="47" t="str">
-        <f t="shared" si="261"/>
-        <v/>
-      </c>
-      <c r="BP48" s="47" t="str">
-        <f t="shared" si="261"/>
-        <v/>
-      </c>
-      <c r="BQ48" s="47" t="str">
-        <f t="shared" si="261"/>
-        <v/>
-      </c>
-      <c r="BR48" s="47" t="str">
-        <f t="shared" si="261"/>
-        <v/>
-      </c>
-      <c r="BS48" s="47" t="str">
-        <f t="shared" si="261"/>
-        <v/>
-      </c>
-      <c r="BT48" s="47" t="str">
-        <f t="shared" si="261"/>
-        <v/>
-      </c>
-      <c r="BU48" s="47" t="str">
-        <f t="shared" si="261"/>
-        <v/>
-      </c>
-      <c r="BV48" s="47" t="str">
-        <f t="shared" si="261"/>
-        <v/>
-      </c>
-      <c r="BW48" s="47" t="str">
-        <f t="shared" si="261"/>
-        <v/>
-      </c>
-      <c r="BX48" s="47" t="e">
-        <f>DEC2HEX(CODE(BJ48),2)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="BY48" s="47" t="e">
-        <f t="shared" si="248"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="BZ48" s="47" t="e">
-        <f t="shared" si="249"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="CA48" s="47" t="e">
-        <f t="shared" si="250"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="CB48" s="47" t="e">
-        <f t="shared" si="251"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="CC48" s="47" t="e">
-        <f t="shared" si="252"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="CD48" s="47" t="e">
-        <f t="shared" si="253"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="CE48" s="47" t="e">
-        <f t="shared" si="254"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="CF48" s="47" t="e">
-        <f t="shared" si="255"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="CG48" s="47" t="e">
-        <f t="shared" si="256"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="CH48" s="47" t="e">
-        <f t="shared" si="257"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="CI48" s="47" t="e">
-        <f t="shared" si="258"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="CJ48" s="47" t="e">
-        <f t="shared" si="259"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="CK48" s="47" t="e">
-        <f t="shared" si="260"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="CL48" s="47"/>
-      <c r="CM48" s="58"/>
-      <c r="CN48" s="47"/>
-      <c r="CO48" s="47"/>
-      <c r="CP48" s="47"/>
-      <c r="CQ48" s="47"/>
-      <c r="CR48" s="47"/>
-      <c r="CS48" s="47" t="str">
-        <f>SUBSTITUTE(J48," ","")</f>
-        <v/>
-      </c>
-      <c r="CT48" s="47"/>
-      <c r="CU48" s="47"/>
-      <c r="CV48" s="47"/>
-      <c r="CW48" s="47"/>
-      <c r="CX48" s="47"/>
-      <c r="CY48" s="47"/>
-      <c r="CZ48" s="47"/>
-    </row>
-    <row r="49" spans="1:104" s="43" customFormat="1" ht="39.950000000000003" hidden="1" customHeight="1" outlineLevel="1">
-      <c r="A49" s="45"/>
-      <c r="B49" s="46">
-        <f t="shared" si="56"/>
-        <v>13</v>
-      </c>
-      <c r="C49" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="D49" s="46" t="s">
-        <v>251</v>
-      </c>
-      <c r="E49" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="F49" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="G49" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="H49" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="I49" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="J49" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="K49" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="L49" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="M49" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="N49" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="O49" s="47"/>
-      <c r="P49" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="Q49" s="47"/>
-      <c r="R49" s="47"/>
-      <c r="S49" s="47"/>
-      <c r="T49" s="47" t="b">
-        <f>T47=T48</f>
-        <v>0</v>
-      </c>
-      <c r="U49" s="47" t="b">
-        <f t="shared" ref="U49:AZ49" si="262">U47=U48</f>
-        <v>0</v>
-      </c>
-      <c r="V49" s="47" t="b">
-        <f t="shared" si="262"/>
-        <v>0</v>
-      </c>
-      <c r="W49" s="47" t="b">
-        <f t="shared" si="262"/>
-        <v>0</v>
-      </c>
-      <c r="X49" s="47" t="b">
-        <f t="shared" si="262"/>
-        <v>0</v>
-      </c>
-      <c r="Y49" s="47" t="b">
-        <f t="shared" si="262"/>
-        <v>0</v>
-      </c>
-      <c r="Z49" s="47" t="b">
-        <f t="shared" si="262"/>
-        <v>0</v>
-      </c>
-      <c r="AA49" s="47" t="b">
-        <f t="shared" si="262"/>
-        <v>0</v>
-      </c>
-      <c r="AB49" s="47" t="b">
-        <f t="shared" si="262"/>
-        <v>0</v>
-      </c>
-      <c r="AC49" s="47" t="b">
-        <f t="shared" si="262"/>
-        <v>0</v>
-      </c>
-      <c r="AD49" s="47" t="b">
-        <f t="shared" si="262"/>
-        <v>0</v>
-      </c>
-      <c r="AE49" s="47" t="b">
-        <f t="shared" si="262"/>
-        <v>0</v>
-      </c>
-      <c r="AF49" s="47" t="b">
-        <f t="shared" si="262"/>
-        <v>0</v>
-      </c>
-      <c r="AG49" s="47" t="b">
-        <f t="shared" si="262"/>
-        <v>0</v>
-      </c>
-      <c r="AH49" s="47" t="b">
-        <f t="shared" si="262"/>
-        <v>0</v>
-      </c>
-      <c r="AI49" s="47" t="b">
-        <f t="shared" si="262"/>
-        <v>0</v>
-      </c>
-      <c r="AJ49" s="47" t="b">
-        <f t="shared" si="262"/>
-        <v>0</v>
-      </c>
-      <c r="AK49" s="47" t="b">
-        <f t="shared" si="262"/>
-        <v>0</v>
-      </c>
-      <c r="AL49" s="47" t="b">
-        <f t="shared" si="262"/>
-        <v>0</v>
-      </c>
-      <c r="AM49" s="47" t="b">
-        <f t="shared" si="262"/>
-        <v>0</v>
-      </c>
-      <c r="AN49" s="47" t="b">
-        <f t="shared" si="262"/>
-        <v>0</v>
-      </c>
-      <c r="AO49" s="47" t="b">
-        <f t="shared" si="262"/>
-        <v>0</v>
-      </c>
-      <c r="AP49" s="47" t="b">
-        <f t="shared" si="262"/>
-        <v>0</v>
-      </c>
-      <c r="AQ49" s="47" t="b">
-        <f t="shared" si="262"/>
-        <v>0</v>
-      </c>
-      <c r="AR49" s="47" t="b">
-        <f t="shared" si="262"/>
-        <v>0</v>
-      </c>
-      <c r="AS49" s="47" t="b">
-        <f t="shared" si="262"/>
-        <v>1</v>
-      </c>
-      <c r="AT49" s="47" t="b">
-        <f t="shared" si="262"/>
-        <v>1</v>
-      </c>
-      <c r="AU49" s="47" t="b">
-        <f t="shared" si="262"/>
-        <v>0</v>
-      </c>
-      <c r="AV49" s="47" t="b">
-        <f t="shared" si="262"/>
-        <v>0</v>
-      </c>
-      <c r="AW49" s="47" t="b">
-        <f t="shared" si="262"/>
-        <v>1</v>
-      </c>
-      <c r="AX49" s="47" t="b">
-        <f t="shared" si="262"/>
-        <v>1</v>
-      </c>
-      <c r="AY49" s="47" t="b">
-        <f t="shared" si="262"/>
-        <v>0</v>
-      </c>
-      <c r="AZ49" s="47" t="b">
-        <f t="shared" si="262"/>
-        <v>1</v>
-      </c>
-      <c r="BA49" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="BB49" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="BC49" s="47" t="b">
-        <f t="shared" ref="BC49:BH49" si="263">BC47=BC48</f>
-        <v>0</v>
-      </c>
-      <c r="BD49" s="47" t="b">
-        <f t="shared" si="263"/>
-        <v>0</v>
-      </c>
-      <c r="BE49" s="47" t="b">
-        <f t="shared" si="263"/>
-        <v>0</v>
-      </c>
-      <c r="BF49" s="47" t="b">
-        <f t="shared" si="263"/>
-        <v>0</v>
-      </c>
-      <c r="BG49" s="47" t="b">
-        <f t="shared" si="263"/>
-        <v>0</v>
-      </c>
-      <c r="BH49" s="47" t="b">
-        <f t="shared" si="263"/>
-        <v>0</v>
-      </c>
-      <c r="BI49" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="BJ49" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="BK49" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="BL49" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="BM49" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="BN49" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="BO49" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="BP49" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="BQ49" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="BR49" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="BS49" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="BT49" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="BU49" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="BV49" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="BW49" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="BX49" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="BY49" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="BZ49" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CA49" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CB49" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CC49" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CD49" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CE49" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CF49" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CG49" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CH49" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CI49" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CJ49" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CK49" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CL49" s="47" t="b">
-        <f>CL47=CL48</f>
-        <v>0</v>
-      </c>
-      <c r="CM49" s="47" t="b">
-        <f t="shared" ref="CM49:CN49" si="264">CM47=CM48</f>
-        <v>0</v>
-      </c>
-      <c r="CN49" s="47" t="b">
-        <f t="shared" si="264"/>
-        <v>0</v>
-      </c>
-      <c r="CO49" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CP49" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CQ49" s="47" t="b">
-        <f t="shared" ref="CQ49" si="265">CQ47=CQ48</f>
-        <v>0</v>
-      </c>
-      <c r="CR49" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CS49" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CT49" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CU49" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CV49" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CW49" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CX49" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CY49" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CZ49" s="47" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="50" spans="1:104" s="42" customFormat="1" ht="44.25" customHeight="1" collapsed="1">
-      <c r="A50" s="45"/>
-      <c r="B50" s="51">
-        <f t="shared" si="56"/>
-        <v>14</v>
-      </c>
-      <c r="C50" s="52">
-        <v>46324.200983796298</v>
-      </c>
-      <c r="D50" s="51" t="s">
-        <v>254</v>
-      </c>
-      <c r="E50" s="51"/>
-      <c r="F50" s="51"/>
-      <c r="G50" s="104"/>
-      <c r="H50" s="51" t="s">
-        <v>557</v>
-      </c>
-      <c r="I50" s="105"/>
-      <c r="J50" s="53" t="s">
-        <v>608</v>
-      </c>
-      <c r="K50" s="53"/>
-      <c r="L50" s="51"/>
-      <c r="M50" s="51"/>
-      <c r="N50" s="51"/>
-      <c r="O50" s="51" t="str">
-        <f>IF(COUNTIF(C52:CZ52,"FALSE")&gt;0,"NG","OK")</f>
-        <v>NG</v>
-      </c>
-      <c r="P50" s="51"/>
-      <c r="Q50" s="51" t="s">
-        <v>441</v>
-      </c>
-      <c r="R50" s="51" t="s">
-        <v>442</v>
-      </c>
-      <c r="S50" s="51" t="s">
-        <v>443</v>
-      </c>
-      <c r="T50" s="51" t="s">
-        <v>39</v>
-      </c>
-      <c r="U50" s="51" t="s">
-        <v>28</v>
-      </c>
-      <c r="V50" s="51" t="s">
-        <v>38</v>
-      </c>
-      <c r="W50" s="51" t="s">
-        <v>79</v>
-      </c>
-      <c r="X50" s="51" t="s">
-        <v>444</v>
-      </c>
-      <c r="Y50" s="51" t="s">
-        <v>444</v>
-      </c>
-      <c r="Z50" s="51" t="s">
-        <v>444</v>
-      </c>
-      <c r="AA50" s="51" t="s">
-        <v>444</v>
-      </c>
-      <c r="AB50" s="51" t="s">
-        <v>563</v>
-      </c>
-      <c r="AC50" s="51">
-        <v>66</v>
-      </c>
-      <c r="AD50" s="51" t="s">
-        <v>446</v>
-      </c>
-      <c r="AE50" s="51">
-        <v>1.2</v>
-      </c>
-      <c r="AF50" s="51" t="s">
-        <v>558</v>
-      </c>
-      <c r="AG50" s="51" t="s">
-        <v>433</v>
-      </c>
-      <c r="AH50" s="51" t="s">
-        <v>600</v>
-      </c>
-      <c r="AI50" s="51" t="s">
-        <v>449</v>
-      </c>
-      <c r="AJ50" s="51" t="s">
-        <v>601</v>
-      </c>
-      <c r="AK50" s="51">
-        <v>4</v>
-      </c>
-      <c r="AL50" s="51">
-        <v>159</v>
-      </c>
-      <c r="AM50" s="54" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(J50," ",""),"-","")</f>
-        <v>378206SAN710M6</v>
-      </c>
-      <c r="AN50" s="108" t="s">
-        <v>609</v>
-      </c>
-      <c r="AO50" s="108" t="s">
-        <v>610</v>
-      </c>
-      <c r="AP50" s="51" t="s">
-        <v>512</v>
-      </c>
-      <c r="AQ50" s="54" t="str">
-        <f>SUBSTITUTE(J50," ","")</f>
-        <v>37820-6SA-N710-M6</v>
-      </c>
-      <c r="AR50" s="54" t="str">
-        <f>IF(RIGHT(SUBSTITUTE(J50," ",""),4)="0-M6",LEFT(SUBSTITUTE(J50," ",""),LEN(SUBSTITUTE(J50," ",""))-4),SUBSTITUTE(J50," ",""))</f>
-        <v>37820-6SA-N71</v>
-      </c>
-      <c r="AS50" s="54">
-        <f>K50</f>
-        <v>0</v>
-      </c>
-      <c r="AT50" s="51"/>
-      <c r="AU50" s="51" t="s">
-        <v>452</v>
-      </c>
-      <c r="AV50" s="51" t="s">
-        <v>453</v>
-      </c>
-      <c r="AW50" s="106"/>
-      <c r="AX50" s="54">
-        <f>K50</f>
-        <v>0</v>
-      </c>
-      <c r="AY50" s="51" t="s">
-        <v>454</v>
-      </c>
-      <c r="AZ50" s="51"/>
-      <c r="BA50" s="51"/>
-      <c r="BB50" s="51"/>
-      <c r="BC50" s="51" t="s">
-        <v>490</v>
-      </c>
-      <c r="BD50" s="54" t="str">
-        <f>AP50</f>
-        <v>MG1CA020-2.30</v>
-      </c>
-      <c r="BE50" s="51" t="s">
-        <v>563</v>
-      </c>
-      <c r="BF50" s="51" t="s">
-        <v>461</v>
-      </c>
-      <c r="BG50" s="51" t="s">
-        <v>462</v>
-      </c>
-      <c r="BH50" s="51" t="s">
-        <v>564</v>
-      </c>
-      <c r="BI50" s="51" t="s">
-        <v>611</v>
-      </c>
-      <c r="BJ50" s="54" t="str">
-        <f t="shared" ref="BJ50:BW54" si="266">MID($BI50,BJ$6,1)</f>
-        <v>3</v>
-      </c>
-      <c r="BK50" s="54" t="str">
-        <f t="shared" si="266"/>
-        <v>7</v>
-      </c>
-      <c r="BL50" s="54" t="str">
-        <f t="shared" si="266"/>
-        <v>8</v>
-      </c>
-      <c r="BM50" s="54" t="str">
-        <f t="shared" si="266"/>
-        <v>0</v>
-      </c>
-      <c r="BN50" s="54" t="str">
-        <f t="shared" si="266"/>
-        <v>5</v>
-      </c>
-      <c r="BO50" s="54" t="str">
-        <f t="shared" si="266"/>
-        <v>-</v>
-      </c>
-      <c r="BP50" s="54" t="str">
-        <f t="shared" si="266"/>
-        <v>6</v>
-      </c>
-      <c r="BQ50" s="54" t="str">
-        <f t="shared" si="266"/>
-        <v>S</v>
-      </c>
-      <c r="BR50" s="54" t="str">
-        <f t="shared" si="266"/>
-        <v>A</v>
-      </c>
-      <c r="BS50" s="54" t="str">
-        <f t="shared" si="266"/>
-        <v>-</v>
-      </c>
-      <c r="BT50" s="54" t="str">
-        <f t="shared" si="266"/>
-        <v>N</v>
-      </c>
-      <c r="BU50" s="54" t="str">
-        <f t="shared" si="266"/>
-        <v>7</v>
-      </c>
-      <c r="BV50" s="54" t="str">
-        <f t="shared" si="266"/>
-        <v>1</v>
-      </c>
-      <c r="BW50" s="54" t="str">
-        <f t="shared" si="266"/>
-        <v>0</v>
-      </c>
-      <c r="BX50" s="55" t="str">
-        <f>DEC2HEX(CODE(BJ50),2)</f>
-        <v>33</v>
-      </c>
-      <c r="BY50" s="55" t="str">
-        <f t="shared" ref="BY50:BY51" si="267">DEC2HEX(CODE(BK50),2)</f>
-        <v>37</v>
-      </c>
-      <c r="BZ50" s="55" t="str">
-        <f t="shared" ref="BZ50:BZ51" si="268">DEC2HEX(CODE(BL50),2)</f>
-        <v>38</v>
-      </c>
-      <c r="CA50" s="55" t="str">
-        <f t="shared" ref="CA50:CA51" si="269">DEC2HEX(CODE(BM50),2)</f>
-        <v>30</v>
-      </c>
-      <c r="CB50" s="55" t="str">
-        <f t="shared" ref="CB50:CB51" si="270">DEC2HEX(CODE(BN50),2)</f>
-        <v>35</v>
-      </c>
-      <c r="CC50" s="55" t="str">
-        <f t="shared" ref="CC50:CC51" si="271">DEC2HEX(CODE(BO50),2)</f>
-        <v>2D</v>
-      </c>
-      <c r="CD50" s="55" t="str">
-        <f t="shared" ref="CD50:CD51" si="272">DEC2HEX(CODE(BP50),2)</f>
-        <v>36</v>
-      </c>
-      <c r="CE50" s="55" t="str">
-        <f t="shared" ref="CE50:CE51" si="273">DEC2HEX(CODE(BQ50),2)</f>
-        <v>53</v>
-      </c>
-      <c r="CF50" s="55" t="str">
-        <f t="shared" ref="CF50:CF51" si="274">DEC2HEX(CODE(BR50),2)</f>
-        <v>41</v>
-      </c>
-      <c r="CG50" s="55" t="str">
-        <f t="shared" ref="CG50:CG51" si="275">DEC2HEX(CODE(BS50),2)</f>
-        <v>2D</v>
-      </c>
-      <c r="CH50" s="55" t="str">
-        <f t="shared" ref="CH50:CH51" si="276">DEC2HEX(CODE(BT50),2)</f>
-        <v>4E</v>
-      </c>
-      <c r="CI50" s="55" t="str">
-        <f t="shared" ref="CI50:CI51" si="277">DEC2HEX(CODE(BU50),2)</f>
-        <v>37</v>
-      </c>
-      <c r="CJ50" s="55" t="str">
-        <f t="shared" ref="CJ50:CJ51" si="278">DEC2HEX(CODE(BV50),2)</f>
-        <v>31</v>
-      </c>
-      <c r="CK50" s="55" t="str">
-        <f t="shared" ref="CK50:CK51" si="279">DEC2HEX(CODE(BW50),2)</f>
-        <v>30</v>
-      </c>
-      <c r="CL50" s="54" t="str">
-        <f>BX50&amp;BY50&amp;BZ50&amp;CA50&amp;CB50&amp;CC50&amp;CD50&amp;CE50&amp;CF50&amp;CG50&amp;CH50&amp;CI50&amp;CJ50&amp;CK50</f>
-        <v>33373830352D3653412D4E373130</v>
-      </c>
-      <c r="CM50" s="104" t="s">
-        <v>513</v>
-      </c>
-      <c r="CN50" s="51" t="s">
-        <v>470</v>
-      </c>
-      <c r="CO50" s="51" t="s">
-        <v>240</v>
-      </c>
-      <c r="CP50" s="51" t="s">
-        <v>240</v>
-      </c>
-      <c r="CQ50" s="51" t="s">
-        <v>240</v>
-      </c>
-      <c r="CR50" s="56" t="s">
-        <v>240</v>
-      </c>
-      <c r="CS50" s="54" t="str">
-        <f>SUBSTITUTE(J50," ","")</f>
-        <v>37820-6SA-N710-M6</v>
-      </c>
-      <c r="CT50" s="108" t="s">
-        <v>612</v>
-      </c>
-      <c r="CU50" s="51" t="s">
-        <v>611</v>
-      </c>
-      <c r="CV50" s="51" t="s">
-        <v>611</v>
-      </c>
-      <c r="CW50" s="56"/>
-      <c r="CX50" s="51" t="str">
-        <f>AR50</f>
-        <v>37820-6SA-N71</v>
-      </c>
-      <c r="CY50" s="106" t="s">
-        <v>613</v>
-      </c>
-      <c r="CZ50" s="51" t="s">
-        <v>614</v>
-      </c>
-    </row>
-    <row r="51" spans="1:104" s="42" customFormat="1" ht="44.25" hidden="1" customHeight="1" outlineLevel="1" collapsed="1">
-      <c r="A51" s="45"/>
-      <c r="B51" s="47">
-        <f t="shared" si="56"/>
-        <v>14</v>
-      </c>
-      <c r="C51" s="57"/>
-      <c r="D51" s="47" t="s">
-        <v>245</v>
-      </c>
-      <c r="E51" s="47"/>
-      <c r="F51" s="47"/>
-      <c r="G51" s="57"/>
-      <c r="H51" s="47"/>
-      <c r="I51" s="47"/>
-      <c r="J51" s="47"/>
-      <c r="K51" s="47"/>
-      <c r="L51" s="47"/>
-      <c r="M51" s="47"/>
-      <c r="N51" s="47"/>
-      <c r="O51" s="47"/>
-      <c r="P51" s="47"/>
-      <c r="Q51" s="47"/>
-      <c r="R51" s="47"/>
-      <c r="S51" s="47"/>
-      <c r="T51" s="47"/>
-      <c r="U51" s="47"/>
-      <c r="V51" s="47"/>
-      <c r="W51" s="47"/>
-      <c r="X51" s="47"/>
-      <c r="Y51" s="47"/>
-      <c r="Z51" s="47"/>
-      <c r="AA51" s="47"/>
-      <c r="AB51" s="47"/>
-      <c r="AC51" s="47"/>
-      <c r="AD51" s="47"/>
-      <c r="AE51" s="47"/>
-      <c r="AF51" s="47"/>
-      <c r="AG51" s="47"/>
-      <c r="AH51" s="47"/>
-      <c r="AI51" s="47"/>
-      <c r="AJ51" s="47"/>
-      <c r="AK51" s="47"/>
-      <c r="AL51" s="47"/>
-      <c r="AM51" s="47"/>
-      <c r="AN51" s="47"/>
-      <c r="AO51" s="47"/>
-      <c r="AP51" s="47"/>
-      <c r="AQ51" s="47"/>
-      <c r="AR51" s="47"/>
-      <c r="AS51" s="47"/>
-      <c r="AT51" s="47"/>
-      <c r="AU51" s="47"/>
-      <c r="AV51" s="47"/>
-      <c r="AW51" s="107"/>
-      <c r="AX51" s="47"/>
-      <c r="AY51" s="47"/>
-      <c r="AZ51" s="47"/>
-      <c r="BA51" s="47"/>
-      <c r="BB51" s="47"/>
-      <c r="BC51" s="47"/>
-      <c r="BD51" s="47"/>
-      <c r="BE51" s="47"/>
-      <c r="BF51" s="47"/>
-      <c r="BG51" s="47"/>
-      <c r="BH51" s="47"/>
-      <c r="BI51" s="47"/>
-      <c r="BJ51" s="47" t="str">
-        <f t="shared" si="261"/>
-        <v/>
-      </c>
-      <c r="BK51" s="47" t="str">
-        <f t="shared" si="261"/>
-        <v/>
-      </c>
-      <c r="BL51" s="47" t="str">
-        <f t="shared" si="261"/>
-        <v/>
-      </c>
-      <c r="BM51" s="47" t="str">
-        <f t="shared" si="261"/>
-        <v/>
-      </c>
-      <c r="BN51" s="47" t="str">
-        <f t="shared" si="261"/>
-        <v/>
-      </c>
-      <c r="BO51" s="47" t="str">
-        <f t="shared" si="261"/>
-        <v/>
-      </c>
-      <c r="BP51" s="47" t="str">
-        <f t="shared" si="261"/>
-        <v/>
-      </c>
-      <c r="BQ51" s="47" t="str">
-        <f t="shared" si="261"/>
-        <v/>
-      </c>
-      <c r="BR51" s="47" t="str">
-        <f t="shared" si="261"/>
-        <v/>
-      </c>
-      <c r="BS51" s="47" t="str">
-        <f t="shared" si="261"/>
-        <v/>
-      </c>
-      <c r="BT51" s="47" t="str">
-        <f t="shared" si="261"/>
-        <v/>
-      </c>
-      <c r="BU51" s="47" t="str">
-        <f t="shared" si="261"/>
-        <v/>
-      </c>
-      <c r="BV51" s="47" t="str">
-        <f t="shared" si="261"/>
-        <v/>
-      </c>
-      <c r="BW51" s="47" t="str">
-        <f t="shared" si="261"/>
-        <v/>
-      </c>
-      <c r="BX51" s="47" t="e">
-        <f>DEC2HEX(CODE(BJ51),2)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="BY51" s="47" t="e">
-        <f t="shared" si="267"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="BZ51" s="47" t="e">
-        <f t="shared" si="268"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="CA51" s="47" t="e">
-        <f t="shared" si="269"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="CB51" s="47" t="e">
-        <f t="shared" si="270"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="CC51" s="47" t="e">
-        <f t="shared" si="271"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="CD51" s="47" t="e">
-        <f t="shared" si="272"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="CE51" s="47" t="e">
-        <f t="shared" si="273"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="CF51" s="47" t="e">
-        <f t="shared" si="274"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="CG51" s="47" t="e">
-        <f t="shared" si="275"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="CH51" s="47" t="e">
-        <f t="shared" si="276"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="CI51" s="47" t="e">
-        <f t="shared" si="277"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="CJ51" s="47" t="e">
-        <f t="shared" si="278"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="CK51" s="47" t="e">
-        <f t="shared" si="279"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="CL51" s="47"/>
-      <c r="CM51" s="58"/>
-      <c r="CN51" s="47"/>
-      <c r="CO51" s="47"/>
-      <c r="CP51" s="47"/>
-      <c r="CQ51" s="47"/>
-      <c r="CR51" s="47"/>
-      <c r="CS51" s="47" t="str">
-        <f>SUBSTITUTE(J51," ","")</f>
-        <v/>
-      </c>
-      <c r="CT51" s="47"/>
-      <c r="CU51" s="47"/>
-      <c r="CV51" s="47"/>
-      <c r="CW51" s="47"/>
-      <c r="CX51" s="47"/>
-      <c r="CY51" s="47"/>
-      <c r="CZ51" s="47"/>
-    </row>
-    <row r="52" spans="1:104" s="43" customFormat="1" ht="39.950000000000003" hidden="1" customHeight="1" outlineLevel="1">
-      <c r="A52" s="45"/>
-      <c r="B52" s="46">
-        <f t="shared" si="56"/>
-        <v>14</v>
-      </c>
-      <c r="C52" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="D52" s="46" t="s">
-        <v>251</v>
-      </c>
-      <c r="E52" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="F52" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="G52" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="H52" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="I52" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="J52" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="K52" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="L52" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="M52" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="N52" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="O52" s="47"/>
-      <c r="P52" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="Q52" s="47"/>
-      <c r="R52" s="47"/>
-      <c r="S52" s="47"/>
-      <c r="T52" s="47" t="b">
-        <f>T50=T51</f>
-        <v>0</v>
-      </c>
-      <c r="U52" s="47" t="b">
-        <f t="shared" ref="U52:AZ52" si="280">U50=U51</f>
-        <v>0</v>
-      </c>
-      <c r="V52" s="47" t="b">
-        <f t="shared" si="280"/>
-        <v>0</v>
-      </c>
-      <c r="W52" s="47" t="b">
-        <f t="shared" si="280"/>
-        <v>0</v>
-      </c>
-      <c r="X52" s="47" t="b">
-        <f t="shared" si="280"/>
-        <v>0</v>
-      </c>
-      <c r="Y52" s="47" t="b">
-        <f t="shared" si="280"/>
-        <v>0</v>
-      </c>
-      <c r="Z52" s="47" t="b">
-        <f t="shared" si="280"/>
-        <v>0</v>
-      </c>
-      <c r="AA52" s="47" t="b">
-        <f t="shared" si="280"/>
-        <v>0</v>
-      </c>
-      <c r="AB52" s="47" t="b">
-        <f t="shared" si="280"/>
-        <v>0</v>
-      </c>
-      <c r="AC52" s="47" t="b">
-        <f t="shared" si="280"/>
-        <v>0</v>
-      </c>
-      <c r="AD52" s="47" t="b">
-        <f t="shared" si="280"/>
-        <v>0</v>
-      </c>
-      <c r="AE52" s="47" t="b">
-        <f t="shared" si="280"/>
-        <v>0</v>
-      </c>
-      <c r="AF52" s="47" t="b">
-        <f t="shared" si="280"/>
-        <v>0</v>
-      </c>
-      <c r="AG52" s="47" t="b">
-        <f t="shared" si="280"/>
-        <v>0</v>
-      </c>
-      <c r="AH52" s="47" t="b">
-        <f t="shared" si="280"/>
-        <v>0</v>
-      </c>
-      <c r="AI52" s="47" t="b">
-        <f t="shared" si="280"/>
-        <v>0</v>
-      </c>
-      <c r="AJ52" s="47" t="b">
-        <f t="shared" si="280"/>
-        <v>0</v>
-      </c>
-      <c r="AK52" s="47" t="b">
-        <f t="shared" si="280"/>
-        <v>0</v>
-      </c>
-      <c r="AL52" s="47" t="b">
-        <f t="shared" si="280"/>
-        <v>0</v>
-      </c>
-      <c r="AM52" s="47" t="b">
-        <f t="shared" si="280"/>
-        <v>0</v>
-      </c>
-      <c r="AN52" s="47" t="b">
-        <f t="shared" si="280"/>
-        <v>0</v>
-      </c>
-      <c r="AO52" s="47" t="b">
-        <f t="shared" si="280"/>
-        <v>0</v>
-      </c>
-      <c r="AP52" s="47" t="b">
-        <f t="shared" si="280"/>
-        <v>0</v>
-      </c>
-      <c r="AQ52" s="47" t="b">
-        <f t="shared" si="280"/>
-        <v>0</v>
-      </c>
-      <c r="AR52" s="47" t="b">
-        <f t="shared" si="280"/>
-        <v>0</v>
-      </c>
-      <c r="AS52" s="47" t="b">
-        <f t="shared" si="280"/>
-        <v>1</v>
-      </c>
-      <c r="AT52" s="47" t="b">
-        <f t="shared" si="280"/>
-        <v>1</v>
-      </c>
-      <c r="AU52" s="47" t="b">
-        <f t="shared" si="280"/>
-        <v>0</v>
-      </c>
-      <c r="AV52" s="47" t="b">
-        <f t="shared" si="280"/>
-        <v>0</v>
-      </c>
-      <c r="AW52" s="47" t="b">
-        <f t="shared" si="280"/>
-        <v>1</v>
-      </c>
-      <c r="AX52" s="47" t="b">
-        <f t="shared" si="280"/>
-        <v>1</v>
-      </c>
-      <c r="AY52" s="47" t="b">
-        <f t="shared" si="280"/>
-        <v>0</v>
-      </c>
-      <c r="AZ52" s="47" t="b">
-        <f t="shared" si="280"/>
-        <v>1</v>
-      </c>
-      <c r="BA52" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="BB52" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="BC52" s="47" t="b">
-        <f t="shared" ref="BC52:BH52" si="281">BC50=BC51</f>
-        <v>0</v>
-      </c>
-      <c r="BD52" s="47" t="b">
-        <f t="shared" si="281"/>
-        <v>0</v>
-      </c>
-      <c r="BE52" s="47" t="b">
-        <f t="shared" si="281"/>
-        <v>0</v>
-      </c>
-      <c r="BF52" s="47" t="b">
-        <f t="shared" si="281"/>
-        <v>0</v>
-      </c>
-      <c r="BG52" s="47" t="b">
-        <f t="shared" si="281"/>
-        <v>0</v>
-      </c>
-      <c r="BH52" s="47" t="b">
-        <f t="shared" si="281"/>
-        <v>0</v>
-      </c>
-      <c r="BI52" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="BJ52" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="BK52" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="BL52" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="BM52" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="BN52" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="BO52" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="BP52" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="BQ52" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="BR52" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="BS52" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="BT52" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="BU52" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="BV52" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="BW52" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="BX52" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="BY52" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="BZ52" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CA52" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CB52" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CC52" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CD52" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CE52" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CF52" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CG52" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CH52" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CI52" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CJ52" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CK52" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CL52" s="47" t="b">
-        <f>CL50=CL51</f>
-        <v>0</v>
-      </c>
-      <c r="CM52" s="47" t="b">
-        <f t="shared" ref="CM52:CN52" si="282">CM50=CM51</f>
-        <v>0</v>
-      </c>
-      <c r="CN52" s="47" t="b">
-        <f t="shared" si="282"/>
-        <v>0</v>
-      </c>
-      <c r="CO52" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CP52" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CQ52" s="47" t="b">
-        <f t="shared" ref="CQ52" si="283">CQ50=CQ51</f>
-        <v>0</v>
-      </c>
-      <c r="CR52" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CS52" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CT52" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CU52" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CV52" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CW52" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CX52" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CY52" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CZ52" s="47" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="53" spans="1:104" s="42" customFormat="1" ht="44.25" customHeight="1" collapsed="1">
-      <c r="A53" s="45"/>
-      <c r="B53" s="51">
-        <f t="shared" si="56"/>
-        <v>15</v>
-      </c>
-      <c r="C53" s="52">
-        <v>46324.201006944444</v>
-      </c>
-      <c r="D53" s="51" t="s">
-        <v>254</v>
-      </c>
-      <c r="E53" s="51"/>
-      <c r="F53" s="51"/>
-      <c r="G53" s="104"/>
-      <c r="H53" s="51" t="s">
-        <v>557</v>
-      </c>
-      <c r="I53" s="105"/>
-      <c r="J53" s="53" t="s">
-        <v>615</v>
-      </c>
-      <c r="K53" s="53"/>
-      <c r="L53" s="51"/>
-      <c r="M53" s="51"/>
-      <c r="N53" s="51"/>
-      <c r="O53" s="51" t="str">
-        <f>IF(COUNTIF(C55:CZ55,"FALSE")&gt;0,"NG","OK")</f>
-        <v>NG</v>
-      </c>
-      <c r="P53" s="51"/>
-      <c r="Q53" s="51" t="s">
-        <v>441</v>
-      </c>
-      <c r="R53" s="51" t="s">
-        <v>442</v>
-      </c>
-      <c r="S53" s="51" t="s">
-        <v>443</v>
-      </c>
-      <c r="T53" s="51" t="s">
-        <v>39</v>
-      </c>
-      <c r="U53" s="51" t="s">
-        <v>28</v>
-      </c>
-      <c r="V53" s="51" t="s">
-        <v>38</v>
-      </c>
-      <c r="W53" s="51" t="s">
-        <v>79</v>
-      </c>
-      <c r="X53" s="51" t="s">
-        <v>444</v>
-      </c>
-      <c r="Y53" s="51" t="s">
-        <v>444</v>
-      </c>
-      <c r="Z53" s="51" t="s">
-        <v>444</v>
-      </c>
-      <c r="AA53" s="51" t="s">
-        <v>444</v>
-      </c>
-      <c r="AB53" s="51" t="s">
-        <v>563</v>
-      </c>
-      <c r="AC53" s="51">
-        <v>66</v>
-      </c>
-      <c r="AD53" s="51" t="s">
-        <v>446</v>
-      </c>
-      <c r="AE53" s="51">
-        <v>1.2</v>
-      </c>
-      <c r="AF53" s="51" t="s">
-        <v>558</v>
-      </c>
-      <c r="AG53" s="51" t="s">
-        <v>433</v>
-      </c>
-      <c r="AH53" s="51" t="s">
-        <v>559</v>
-      </c>
-      <c r="AI53" s="51" t="s">
-        <v>449</v>
-      </c>
-      <c r="AJ53" s="51" t="s">
-        <v>560</v>
-      </c>
-      <c r="AK53" s="51">
-        <v>4</v>
-      </c>
-      <c r="AL53" s="51">
-        <v>159</v>
-      </c>
-      <c r="AM53" s="54" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(J53," ",""),"-","")</f>
-        <v>378206SATK10M6</v>
-      </c>
-      <c r="AN53" s="108" t="s">
-        <v>616</v>
-      </c>
-      <c r="AO53" s="108" t="s">
-        <v>617</v>
-      </c>
-      <c r="AP53" s="51" t="s">
-        <v>512</v>
-      </c>
-      <c r="AQ53" s="54" t="str">
-        <f>SUBSTITUTE(J53," ","")</f>
-        <v>37820-6SA-TK10-M6</v>
-      </c>
-      <c r="AR53" s="54" t="str">
-        <f>IF(RIGHT(SUBSTITUTE(J53," ",""),4)="0-M6",LEFT(SUBSTITUTE(J53," ",""),LEN(SUBSTITUTE(J53," ",""))-4),SUBSTITUTE(J53," ",""))</f>
-        <v>37820-6SA-TK1</v>
-      </c>
-      <c r="AS53" s="54">
-        <f>K53</f>
-        <v>0</v>
-      </c>
-      <c r="AT53" s="51"/>
-      <c r="AU53" s="51" t="s">
-        <v>452</v>
-      </c>
-      <c r="AV53" s="51" t="s">
-        <v>453</v>
-      </c>
-      <c r="AW53" s="106"/>
-      <c r="AX53" s="54">
-        <f>K53</f>
-        <v>0</v>
-      </c>
-      <c r="AY53" s="51" t="s">
-        <v>454</v>
-      </c>
-      <c r="AZ53" s="51"/>
-      <c r="BA53" s="51"/>
-      <c r="BB53" s="51"/>
-      <c r="BC53" s="51" t="s">
-        <v>490</v>
-      </c>
-      <c r="BD53" s="54" t="str">
-        <f>AP53</f>
-        <v>MG1CA020-2.30</v>
-      </c>
-      <c r="BE53" s="51" t="s">
-        <v>563</v>
-      </c>
-      <c r="BF53" s="51" t="s">
-        <v>461</v>
-      </c>
-      <c r="BG53" s="51" t="s">
-        <v>462</v>
-      </c>
-      <c r="BH53" s="51" t="s">
-        <v>564</v>
-      </c>
-      <c r="BI53" s="51" t="s">
-        <v>618</v>
-      </c>
-      <c r="BJ53" s="54" t="str">
-        <f t="shared" si="266"/>
-        <v>3</v>
-      </c>
-      <c r="BK53" s="54" t="str">
-        <f t="shared" si="266"/>
-        <v>7</v>
-      </c>
-      <c r="BL53" s="54" t="str">
-        <f t="shared" si="266"/>
-        <v>8</v>
-      </c>
-      <c r="BM53" s="54" t="str">
-        <f t="shared" si="266"/>
-        <v>0</v>
-      </c>
-      <c r="BN53" s="54" t="str">
-        <f t="shared" si="266"/>
-        <v>5</v>
-      </c>
-      <c r="BO53" s="54" t="str">
-        <f t="shared" si="266"/>
-        <v>-</v>
-      </c>
-      <c r="BP53" s="54" t="str">
-        <f t="shared" si="266"/>
-        <v>6</v>
-      </c>
-      <c r="BQ53" s="54" t="str">
-        <f t="shared" si="266"/>
-        <v>S</v>
-      </c>
-      <c r="BR53" s="54" t="str">
-        <f t="shared" si="266"/>
-        <v>A</v>
-      </c>
-      <c r="BS53" s="54" t="str">
-        <f t="shared" si="266"/>
-        <v>-</v>
-      </c>
-      <c r="BT53" s="54" t="str">
-        <f t="shared" si="266"/>
-        <v>T</v>
-      </c>
-      <c r="BU53" s="54" t="str">
-        <f t="shared" si="266"/>
-        <v>K</v>
-      </c>
-      <c r="BV53" s="54" t="str">
-        <f t="shared" si="266"/>
-        <v>1</v>
-      </c>
-      <c r="BW53" s="54" t="str">
-        <f t="shared" si="266"/>
-        <v>0</v>
-      </c>
-      <c r="BX53" s="55" t="str">
-        <f>DEC2HEX(CODE(BJ53),2)</f>
-        <v>33</v>
-      </c>
-      <c r="BY53" s="55" t="str">
-        <f t="shared" ref="BY53:BY54" si="284">DEC2HEX(CODE(BK53),2)</f>
-        <v>37</v>
-      </c>
-      <c r="BZ53" s="55" t="str">
-        <f t="shared" ref="BZ53:BZ54" si="285">DEC2HEX(CODE(BL53),2)</f>
-        <v>38</v>
-      </c>
-      <c r="CA53" s="55" t="str">
-        <f t="shared" ref="CA53:CA54" si="286">DEC2HEX(CODE(BM53),2)</f>
-        <v>30</v>
-      </c>
-      <c r="CB53" s="55" t="str">
-        <f t="shared" ref="CB53:CB54" si="287">DEC2HEX(CODE(BN53),2)</f>
-        <v>35</v>
-      </c>
-      <c r="CC53" s="55" t="str">
-        <f t="shared" ref="CC53:CC54" si="288">DEC2HEX(CODE(BO53),2)</f>
-        <v>2D</v>
-      </c>
-      <c r="CD53" s="55" t="str">
-        <f t="shared" ref="CD53:CD54" si="289">DEC2HEX(CODE(BP53),2)</f>
-        <v>36</v>
-      </c>
-      <c r="CE53" s="55" t="str">
-        <f t="shared" ref="CE53:CE54" si="290">DEC2HEX(CODE(BQ53),2)</f>
-        <v>53</v>
-      </c>
-      <c r="CF53" s="55" t="str">
-        <f t="shared" ref="CF53:CF54" si="291">DEC2HEX(CODE(BR53),2)</f>
-        <v>41</v>
-      </c>
-      <c r="CG53" s="55" t="str">
-        <f t="shared" ref="CG53:CG54" si="292">DEC2HEX(CODE(BS53),2)</f>
-        <v>2D</v>
-      </c>
-      <c r="CH53" s="55" t="str">
-        <f t="shared" ref="CH53:CH54" si="293">DEC2HEX(CODE(BT53),2)</f>
-        <v>54</v>
-      </c>
-      <c r="CI53" s="55" t="str">
-        <f t="shared" ref="CI53:CI54" si="294">DEC2HEX(CODE(BU53),2)</f>
-        <v>4B</v>
-      </c>
-      <c r="CJ53" s="55" t="str">
-        <f t="shared" ref="CJ53:CJ54" si="295">DEC2HEX(CODE(BV53),2)</f>
-        <v>31</v>
-      </c>
-      <c r="CK53" s="55" t="str">
-        <f t="shared" ref="CK53:CK54" si="296">DEC2HEX(CODE(BW53),2)</f>
-        <v>30</v>
-      </c>
-      <c r="CL53" s="54" t="str">
-        <f>BX53&amp;BY53&amp;BZ53&amp;CA53&amp;CB53&amp;CC53&amp;CD53&amp;CE53&amp;CF53&amp;CG53&amp;CH53&amp;CI53&amp;CJ53&amp;CK53</f>
-        <v>33373830352D3653412D544B3130</v>
-      </c>
-      <c r="CM53" s="104" t="s">
-        <v>513</v>
-      </c>
-      <c r="CN53" s="51" t="s">
-        <v>470</v>
-      </c>
-      <c r="CO53" s="51" t="s">
-        <v>240</v>
-      </c>
-      <c r="CP53" s="51" t="s">
-        <v>240</v>
-      </c>
-      <c r="CQ53" s="51" t="s">
-        <v>240</v>
-      </c>
-      <c r="CR53" s="56" t="s">
-        <v>240</v>
-      </c>
-      <c r="CS53" s="54" t="str">
-        <f>SUBSTITUTE(J53," ","")</f>
-        <v>37820-6SA-TK10-M6</v>
-      </c>
-      <c r="CT53" s="108" t="s">
-        <v>619</v>
-      </c>
-      <c r="CU53" s="51" t="s">
-        <v>618</v>
-      </c>
-      <c r="CV53" s="51" t="s">
-        <v>618</v>
-      </c>
-      <c r="CW53" s="56"/>
-      <c r="CX53" s="51" t="str">
-        <f>AR53</f>
-        <v>37820-6SA-TK1</v>
-      </c>
-      <c r="CY53" s="106">
-        <v>400000</v>
-      </c>
-      <c r="CZ53" s="51" t="s">
-        <v>620</v>
-      </c>
-    </row>
-    <row r="54" spans="1:104" s="42" customFormat="1" ht="44.25" hidden="1" customHeight="1" outlineLevel="1" collapsed="1">
-      <c r="A54" s="45"/>
-      <c r="B54" s="47">
-        <f t="shared" si="56"/>
-        <v>15</v>
-      </c>
-      <c r="C54" s="57"/>
-      <c r="D54" s="47" t="s">
-        <v>245</v>
-      </c>
-      <c r="E54" s="47"/>
-      <c r="F54" s="47"/>
-      <c r="G54" s="57"/>
-      <c r="H54" s="47"/>
-      <c r="I54" s="47"/>
-      <c r="J54" s="47"/>
-      <c r="K54" s="47"/>
-      <c r="L54" s="47"/>
-      <c r="M54" s="47"/>
-      <c r="N54" s="47"/>
-      <c r="O54" s="47"/>
-      <c r="P54" s="47"/>
-      <c r="Q54" s="47"/>
-      <c r="R54" s="47"/>
-      <c r="S54" s="47"/>
-      <c r="T54" s="47"/>
-      <c r="U54" s="47"/>
-      <c r="V54" s="47"/>
-      <c r="W54" s="47"/>
-      <c r="X54" s="47"/>
-      <c r="Y54" s="47"/>
-      <c r="Z54" s="47"/>
-      <c r="AA54" s="47"/>
-      <c r="AB54" s="47"/>
-      <c r="AC54" s="47"/>
-      <c r="AD54" s="47"/>
-      <c r="AE54" s="47"/>
-      <c r="AF54" s="47"/>
-      <c r="AG54" s="47"/>
-      <c r="AH54" s="47"/>
-      <c r="AI54" s="47"/>
-      <c r="AJ54" s="47"/>
-      <c r="AK54" s="47"/>
-      <c r="AL54" s="47"/>
-      <c r="AM54" s="47"/>
-      <c r="AN54" s="47"/>
-      <c r="AO54" s="47"/>
-      <c r="AP54" s="47"/>
-      <c r="AQ54" s="47"/>
-      <c r="AR54" s="47"/>
-      <c r="AS54" s="47"/>
-      <c r="AT54" s="47"/>
-      <c r="AU54" s="47"/>
-      <c r="AV54" s="47"/>
-      <c r="AW54" s="107"/>
-      <c r="AX54" s="47"/>
-      <c r="AY54" s="47"/>
-      <c r="AZ54" s="47"/>
-      <c r="BA54" s="47"/>
-      <c r="BB54" s="47"/>
-      <c r="BC54" s="47"/>
-      <c r="BD54" s="47"/>
-      <c r="BE54" s="47"/>
-      <c r="BF54" s="47"/>
-      <c r="BG54" s="47"/>
-      <c r="BH54" s="47"/>
-      <c r="BI54" s="47"/>
-      <c r="BJ54" s="47" t="str">
-        <f t="shared" si="266"/>
-        <v/>
-      </c>
-      <c r="BK54" s="47" t="str">
-        <f t="shared" si="266"/>
-        <v/>
-      </c>
-      <c r="BL54" s="47" t="str">
-        <f t="shared" si="266"/>
-        <v/>
-      </c>
-      <c r="BM54" s="47" t="str">
-        <f t="shared" si="266"/>
-        <v/>
-      </c>
-      <c r="BN54" s="47" t="str">
-        <f t="shared" si="266"/>
-        <v/>
-      </c>
-      <c r="BO54" s="47" t="str">
-        <f t="shared" si="266"/>
-        <v/>
-      </c>
-      <c r="BP54" s="47" t="str">
-        <f t="shared" si="266"/>
-        <v/>
-      </c>
-      <c r="BQ54" s="47" t="str">
-        <f t="shared" si="266"/>
-        <v/>
-      </c>
-      <c r="BR54" s="47" t="str">
-        <f t="shared" si="266"/>
-        <v/>
-      </c>
-      <c r="BS54" s="47" t="str">
-        <f t="shared" si="266"/>
-        <v/>
-      </c>
-      <c r="BT54" s="47" t="str">
-        <f t="shared" si="266"/>
-        <v/>
-      </c>
-      <c r="BU54" s="47" t="str">
-        <f t="shared" si="266"/>
-        <v/>
-      </c>
-      <c r="BV54" s="47" t="str">
-        <f t="shared" si="266"/>
-        <v/>
-      </c>
-      <c r="BW54" s="47" t="str">
-        <f t="shared" si="266"/>
-        <v/>
-      </c>
-      <c r="BX54" s="47" t="e">
-        <f>DEC2HEX(CODE(BJ54),2)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="BY54" s="47" t="e">
-        <f t="shared" si="284"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="BZ54" s="47" t="e">
-        <f t="shared" si="285"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="CA54" s="47" t="e">
-        <f t="shared" si="286"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="CB54" s="47" t="e">
-        <f t="shared" si="287"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="CC54" s="47" t="e">
-        <f t="shared" si="288"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="CD54" s="47" t="e">
-        <f t="shared" si="289"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="CE54" s="47" t="e">
-        <f t="shared" si="290"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="CF54" s="47" t="e">
-        <f t="shared" si="291"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="CG54" s="47" t="e">
-        <f t="shared" si="292"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="CH54" s="47" t="e">
-        <f t="shared" si="293"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="CI54" s="47" t="e">
-        <f t="shared" si="294"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="CJ54" s="47" t="e">
-        <f t="shared" si="295"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="CK54" s="47" t="e">
-        <f t="shared" si="296"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="CL54" s="47"/>
-      <c r="CM54" s="58"/>
-      <c r="CN54" s="47"/>
-      <c r="CO54" s="47"/>
-      <c r="CP54" s="47"/>
-      <c r="CQ54" s="47"/>
-      <c r="CR54" s="47"/>
-      <c r="CS54" s="47" t="str">
-        <f>SUBSTITUTE(J54," ","")</f>
-        <v/>
-      </c>
-      <c r="CT54" s="47"/>
-      <c r="CU54" s="47"/>
-      <c r="CV54" s="47"/>
-      <c r="CW54" s="47"/>
-      <c r="CX54" s="47"/>
-      <c r="CY54" s="47"/>
-      <c r="CZ54" s="47"/>
-    </row>
-    <row r="55" spans="1:104" s="43" customFormat="1" ht="39.950000000000003" hidden="1" customHeight="1" outlineLevel="1">
-      <c r="A55" s="45"/>
-      <c r="B55" s="46">
-        <f t="shared" si="56"/>
-        <v>15</v>
-      </c>
-      <c r="C55" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="D55" s="46" t="s">
-        <v>251</v>
-      </c>
-      <c r="E55" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="F55" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="G55" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="H55" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="I55" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="J55" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="K55" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="L55" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="M55" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="N55" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="O55" s="47"/>
-      <c r="P55" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="Q55" s="47"/>
-      <c r="R55" s="47"/>
-      <c r="S55" s="47"/>
-      <c r="T55" s="47" t="b">
-        <f>T53=T54</f>
-        <v>0</v>
-      </c>
-      <c r="U55" s="47" t="b">
-        <f t="shared" ref="U55:AZ55" si="297">U53=U54</f>
-        <v>0</v>
-      </c>
-      <c r="V55" s="47" t="b">
-        <f t="shared" si="297"/>
-        <v>0</v>
-      </c>
-      <c r="W55" s="47" t="b">
-        <f t="shared" si="297"/>
-        <v>0</v>
-      </c>
-      <c r="X55" s="47" t="b">
-        <f t="shared" si="297"/>
-        <v>0</v>
-      </c>
-      <c r="Y55" s="47" t="b">
-        <f t="shared" si="297"/>
-        <v>0</v>
-      </c>
-      <c r="Z55" s="47" t="b">
-        <f t="shared" si="297"/>
-        <v>0</v>
-      </c>
-      <c r="AA55" s="47" t="b">
-        <f t="shared" si="297"/>
-        <v>0</v>
-      </c>
-      <c r="AB55" s="47" t="b">
-        <f t="shared" si="297"/>
-        <v>0</v>
-      </c>
-      <c r="AC55" s="47" t="b">
-        <f t="shared" si="297"/>
-        <v>0</v>
-      </c>
-      <c r="AD55" s="47" t="b">
-        <f t="shared" si="297"/>
-        <v>0</v>
-      </c>
-      <c r="AE55" s="47" t="b">
-        <f t="shared" si="297"/>
-        <v>0</v>
-      </c>
-      <c r="AF55" s="47" t="b">
-        <f t="shared" si="297"/>
-        <v>0</v>
-      </c>
-      <c r="AG55" s="47" t="b">
-        <f t="shared" si="297"/>
-        <v>0</v>
-      </c>
-      <c r="AH55" s="47" t="b">
-        <f t="shared" si="297"/>
-        <v>0</v>
-      </c>
-      <c r="AI55" s="47" t="b">
-        <f t="shared" si="297"/>
-        <v>0</v>
-      </c>
-      <c r="AJ55" s="47" t="b">
-        <f t="shared" si="297"/>
-        <v>0</v>
-      </c>
-      <c r="AK55" s="47" t="b">
-        <f t="shared" si="297"/>
-        <v>0</v>
-      </c>
-      <c r="AL55" s="47" t="b">
-        <f t="shared" si="297"/>
-        <v>0</v>
-      </c>
-      <c r="AM55" s="47" t="b">
-        <f t="shared" si="297"/>
-        <v>0</v>
-      </c>
-      <c r="AN55" s="47" t="b">
-        <f t="shared" si="297"/>
-        <v>0</v>
-      </c>
-      <c r="AO55" s="47" t="b">
-        <f t="shared" si="297"/>
-        <v>0</v>
-      </c>
-      <c r="AP55" s="47" t="b">
-        <f t="shared" si="297"/>
-        <v>0</v>
-      </c>
-      <c r="AQ55" s="47" t="b">
-        <f t="shared" si="297"/>
-        <v>0</v>
-      </c>
-      <c r="AR55" s="47" t="b">
-        <f t="shared" si="297"/>
-        <v>0</v>
-      </c>
-      <c r="AS55" s="47" t="b">
-        <f t="shared" si="297"/>
-        <v>1</v>
-      </c>
-      <c r="AT55" s="47" t="b">
-        <f t="shared" si="297"/>
-        <v>1</v>
-      </c>
-      <c r="AU55" s="47" t="b">
-        <f t="shared" si="297"/>
-        <v>0</v>
-      </c>
-      <c r="AV55" s="47" t="b">
-        <f t="shared" si="297"/>
-        <v>0</v>
-      </c>
-      <c r="AW55" s="47" t="b">
-        <f t="shared" si="297"/>
-        <v>1</v>
-      </c>
-      <c r="AX55" s="47" t="b">
-        <f t="shared" si="297"/>
-        <v>1</v>
-      </c>
-      <c r="AY55" s="47" t="b">
-        <f t="shared" si="297"/>
-        <v>0</v>
-      </c>
-      <c r="AZ55" s="47" t="b">
-        <f t="shared" si="297"/>
-        <v>1</v>
-      </c>
-      <c r="BA55" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="BB55" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="BC55" s="47" t="b">
-        <f t="shared" ref="BC55:BH55" si="298">BC53=BC54</f>
-        <v>0</v>
-      </c>
-      <c r="BD55" s="47" t="b">
-        <f t="shared" si="298"/>
-        <v>0</v>
-      </c>
-      <c r="BE55" s="47" t="b">
-        <f t="shared" si="298"/>
-        <v>0</v>
-      </c>
-      <c r="BF55" s="47" t="b">
-        <f t="shared" si="298"/>
-        <v>0</v>
-      </c>
-      <c r="BG55" s="47" t="b">
-        <f t="shared" si="298"/>
-        <v>0</v>
-      </c>
-      <c r="BH55" s="47" t="b">
-        <f t="shared" si="298"/>
-        <v>0</v>
-      </c>
-      <c r="BI55" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="BJ55" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="BK55" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="BL55" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="BM55" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="BN55" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="BO55" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="BP55" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="BQ55" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="BR55" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="BS55" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="BT55" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="BU55" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="BV55" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="BW55" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="BX55" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="BY55" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="BZ55" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CA55" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CB55" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CC55" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CD55" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CE55" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CF55" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CG55" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CH55" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CI55" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CJ55" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CK55" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CL55" s="47" t="b">
-        <f>CL53=CL54</f>
-        <v>0</v>
-      </c>
-      <c r="CM55" s="47" t="b">
-        <f t="shared" ref="CM55:CN55" si="299">CM53=CM54</f>
-        <v>0</v>
-      </c>
-      <c r="CN55" s="47" t="b">
-        <f t="shared" si="299"/>
-        <v>0</v>
-      </c>
-      <c r="CO55" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CP55" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CQ55" s="47" t="b">
-        <f t="shared" ref="CQ55" si="300">CQ53=CQ54</f>
-        <v>0</v>
-      </c>
-      <c r="CR55" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CS55" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CT55" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CU55" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CV55" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CW55" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CX55" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CY55" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CZ55" s="47" t="s">
         <v>264</v>
       </c>
     </row>
@@ -27242,7 +21035,7 @@
       <formula>2370014827</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T28:AZ28 T31:AZ31 T34:AZ34 T37:AZ37 T40:AZ40 T43:AZ43 T46:AZ46 T49:AZ49 T52:AZ52 T55:AZ55">
+  <conditionalFormatting sqref="T28:AZ28 T31:AZ31 T34:AZ34">
     <cfRule type="cellIs" dxfId="9" priority="1" operator="equal">
       <formula>2370014827</formula>
     </cfRule>
@@ -27262,15 +21055,15 @@
       <formula>2370014827</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BC28:CR28 BC31:CR31 BC34:CR34 BC37:CR37 BC40:CR40 BC43:CR43 BC46:CR46 BC49:CR49 BC52:CR52 BC55:CR55">
+  <conditionalFormatting sqref="BC28:CR28 BC31:CR31 BC34:CR34">
     <cfRule type="cellIs" dxfId="5" priority="2" operator="equal">
       <formula>2370014827</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations xWindow="1254" yWindow="852" count="3">
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="to be imported from pool and filled later" sqref="AW8:AW12 AW14:AW15 AW17:AW18 AW20:AW21 AW23:AW24 AW26:AW27 AW29:AW30 AW32:AW33 AW35:AW36 AW38:AW39 AW41:AW42 AW44:AW45 AW47:AW48 AW50:AW51 AW53:AW54" xr:uid="{7E3410B7-94B3-4447-9E49-760CE60EEE4F}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="to be pick from PST_Lib, requried D2C" sqref="BD8:BF12 BH17:CZ18 BD26:BF27 BH20:CZ21 BD14:BF15 BH8:CZ12 BD17:BF18 BH23:CZ24 BD20:BF21 BH14:CZ15 BD23:BF24 BH26:CZ27 BD29:BF30 BH29:CZ30 BD32:BF33 BH32:CZ33 BD35:BF36 BH35:CZ36 BD38:BF39 BH38:CZ39 BD41:BF42 BH41:CZ42 BD44:BF45 BH44:CZ45 BD47:BF48 BH47:CZ48 BD50:BF51 BH50:CZ51 BD53:BF54 BH53:CZ54" xr:uid="{F4497FCE-6BFF-4813-BA4D-924E8853B93C}"/>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X8:AA8 X23:AA24 X10:AA12 X14:AA15 X17:AA18 X20:AA21 X26:AA27 X29:AA30 X32:AA33 X35:AA36 X38:AA39 X41:AA42 X44:AA45 X47:AA48 X50:AA51 X53:AA54" xr:uid="{B1F30C27-2B87-435B-A957-C50D2371C83F}">
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="to be imported from pool and filled later" sqref="AW8:AW12 AW14:AW15 AW17:AW18 AW20:AW21 AW23:AW24 AW26:AW27 AW29:AW30 AW32:AW33" xr:uid="{7E3410B7-94B3-4447-9E49-760CE60EEE4F}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="to be pick from PST_Lib, requried D2C" sqref="BD8:BF12 BH17:CZ18 BD26:BF27 BH20:CZ21 BD14:BF15 BH8:CZ12 BD17:BF18 BH23:CZ24 BD20:BF21 BH14:CZ15 BD23:BF24 BH26:CZ27 BD29:BF30 BH29:CZ30 BD32:BF33 BH32:CZ33" xr:uid="{F4497FCE-6BFF-4813-BA4D-924E8853B93C}"/>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X8:AA8 X23:AA24 X10:AA12 X14:AA15 X17:AA18 X20:AA21 X26:AA27 X29:AA30 X32:AA33" xr:uid="{B1F30C27-2B87-435B-A957-C50D2371C83F}">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
   </dataValidations>
@@ -27292,25 +21085,25 @@
           <x14:formula1>
             <xm:f>Term!$B$6:$B$8</xm:f>
           </x14:formula1>
-          <xm:sqref>T8:T12 T23:T24 T14:T15 T17:T18 T20:T21 T26:T27 T29:T30 T32:T33 T35:T36 T38:T39 T41:T42 T44:T45 T47:T48 T50:T51 T53:T54</xm:sqref>
+          <xm:sqref>T8:T12 T23:T24 T14:T15 T17:T18 T20:T21 T26:T27 T29:T30 T32:T33</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{8393420D-CF47-4DAC-823D-054E6C500F4E}">
           <x14:formula1>
             <xm:f>Term!$B$13:$B$20</xm:f>
           </x14:formula1>
-          <xm:sqref>U8 U10:U12 U23:U24 U14:U15 U17:U18 U20:U21 U26:U27 U29:U30 U32:U33 U35:U36 U38:U39 U41:U42 U44:U45 U47:U48 U50:U51 U53:U54</xm:sqref>
+          <xm:sqref>U8 U10:U12 U23:U24 U14:U15 U17:U18 U20:U21 U26:U27 U29:U30 U32:U33</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{D6F878B0-BC66-4D73-B333-AC478B6ECF75}">
           <x14:formula1>
             <xm:f>Term!$B$25:$B$29</xm:f>
           </x14:formula1>
-          <xm:sqref>V8 V10:V12 V23:V24 V14:V15 V17:V18 V20:V21 V26:V27 V29:V30 V32:V33 V35:V36 V38:V39 V41:V42 V44:V45 V47:V48 V50:V51 V53:V54</xm:sqref>
+          <xm:sqref>V8 V10:V12 V23:V24 V14:V15 V17:V18 V20:V21 V26:V27 V29:V30 V32:V33</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{66CAFB4E-FD6E-45D7-B5CC-5BEEE77F060C}">
           <x14:formula1>
             <xm:f>Term!$B$34:$B$36</xm:f>
           </x14:formula1>
-          <xm:sqref>W8 W10:W12 W23:W24 W14:W15 W17:W18 W20:W21 W26:W27 W29:W30 W32:W33 W35:W36 W38:W39 W41:W42 W44:W45 W47:W48 W50:W51 W53:W54</xm:sqref>
+          <xm:sqref>W8 W10:W12 W23:W24 W14:W15 W17:W18 W20:W21 W26:W27 W29:W30 W32:W33</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/datas/mastersheet/Honda_6SAY_Container_MasterSheet_r00.xlsx
+++ b/datas/mastersheet/Honda_6SAY_Container_MasterSheet_r00.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Workspace\Tools\AutoHub\datas\mastersheet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B302ED7-9675-48F6-B321-2DE3AFBFF6B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F80D2576-39B6-49DD-947C-B19EF319961D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="1170" windowWidth="21600" windowHeight="13185" activeTab="1" xr2:uid="{287B7087-B8C3-483B-8615-16E7FDDFEF13}"/>
+    <workbookView xWindow="1170" yWindow="1170" windowWidth="21600" windowHeight="11835" activeTab="1" xr2:uid="{287B7087-B8C3-483B-8615-16E7FDDFEF13}"/>
   </bookViews>
   <sheets>
     <sheet name="WorkFlow_Detail" sheetId="4" r:id="rId1"/>
@@ -84,7 +84,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1629" uniqueCount="579">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1383" uniqueCount="558">
   <si>
     <t>General info</t>
   </si>
@@ -2761,9 +2761,6 @@
     <t>MT_S</t>
   </si>
   <si>
-    <t>CVT_S</t>
-  </si>
-  <si>
     <t>MG1</t>
   </si>
   <si>
@@ -2821,9 +2818,6 @@
     <t>MG1CA020_6SAY_V011_TPROT_IND_MT_S_HV007_HPT.hex</t>
   </si>
   <si>
-    <t>MG1CA020_6SAY_V011_TPROT_IND_CVT_S_HV007_HPT.hex</t>
-  </si>
-  <si>
     <t>V011</t>
   </si>
   <si>
@@ -2839,9 +2833,6 @@
     <t>37805-6SA-T410</t>
   </si>
   <si>
-    <t>37805-6SA-T810</t>
-  </si>
-  <si>
     <t>37805-6SA-T910</t>
   </si>
   <si>
@@ -2860,9 +2851,6 @@
     <t>0A-28-30-01-00</t>
   </si>
   <si>
-    <t>0A-28-30-02-01</t>
-  </si>
-  <si>
     <t>0A-28-30-03-01</t>
   </si>
   <si>
@@ -2882,12 +2870,6 @@
   </si>
   <si>
     <t>FN6</t>
-  </si>
-  <si>
-    <t>4E5</t>
-  </si>
-  <si>
-    <t>Z8J</t>
   </si>
   <si>
     <t>KT7</t>
@@ -2928,9 +2910,6 @@
     <t>37820-6SA-T410-M6</t>
   </si>
   <si>
-    <t>37820-6SA-T810-M6</t>
-  </si>
-  <si>
     <t>37820-6SA-T910-M6</t>
   </si>
   <si>
@@ -2949,9 +2928,6 @@
     <t>0261S10B59</t>
   </si>
   <si>
-    <t>0261S10B5A</t>
-  </si>
-  <si>
     <t>0261S10B5B</t>
   </si>
   <si>
@@ -2965,9 +2941,6 @@
   </si>
   <si>
     <t>0261B00DA9</t>
-  </si>
-  <si>
-    <t>0261B00DB0</t>
   </si>
   <si>
     <t>0261B00DB1</t>
@@ -3002,9 +2975,6 @@
     <t>WF221489</t>
   </si>
   <si>
-    <t>WF221488</t>
-  </si>
-  <si>
     <t>WF221487</t>
   </si>
   <si>
@@ -3014,9 +2984,6 @@
     <t>10SW134790</t>
   </si>
   <si>
-    <t>10SW134797</t>
-  </si>
-  <si>
     <t>10SW134798</t>
   </si>
   <si>
@@ -3032,9 +2999,6 @@
     <t>3E10186670</t>
   </si>
   <si>
-    <t>3E10186682</t>
-  </si>
-  <si>
     <t>3E10186683</t>
   </si>
   <si>
@@ -3069,15 +3033,6 @@
   </si>
   <si>
     <t>33373830352D3653412D54343130</t>
-  </si>
-  <si>
-    <t>378206SAT810M6</t>
-  </si>
-  <si>
-    <t>37820-6SA-T81</t>
-  </si>
-  <si>
-    <t>33373830352D3653412D54383130</t>
   </si>
   <si>
     <t>378206SAT910M6</t>
@@ -3166,24 +3121,6 @@
   </si>
   <si>
     <t>C7C</t>
-  </si>
-  <si>
-    <t>37820-6WZ-M710-M6</t>
-  </si>
-  <si>
-    <t>0261S10BN9</t>
-  </si>
-  <si>
-    <t>0261B00E0C</t>
-  </si>
-  <si>
-    <t>37805-6WZ-M710</t>
-  </si>
-  <si>
-    <t>01-28-41-01-01</t>
-  </si>
-  <si>
-    <t>DTW</t>
   </si>
 </sst>
 </file>
@@ -4005,6 +3942,24 @@
     <xf numFmtId="49" fontId="19" fillId="20" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="24" fillId="21" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -4023,25 +3978,7 @@
     <xf numFmtId="0" fontId="24" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="21" fillId="25" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -11854,7 +11791,7 @@
     <tabColor rgb="FFFFC000"/>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:CZ34"/>
+  <dimension ref="A1:CZ28"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="8.7109375" style="40" customWidth="1"/>
@@ -11919,35 +11856,35 @@
     </row>
     <row r="2" spans="1:104">
       <c r="A2" s="39"/>
-      <c r="B2" s="117" t="s">
-        <v>489</v>
-      </c>
-      <c r="C2" s="117"/>
-      <c r="D2" s="117"/>
-      <c r="E2" s="117"/>
-      <c r="F2" s="117"/>
-      <c r="G2" s="117"/>
-      <c r="H2" s="117"/>
+      <c r="B2" s="108" t="s">
+        <v>483</v>
+      </c>
+      <c r="C2" s="108"/>
+      <c r="D2" s="108"/>
+      <c r="E2" s="108"/>
+      <c r="F2" s="108"/>
+      <c r="G2" s="108"/>
+      <c r="H2" s="108"/>
     </row>
     <row r="3" spans="1:104" ht="4.5" customHeight="1">
       <c r="A3" s="39"/>
-      <c r="B3" s="117"/>
-      <c r="C3" s="117"/>
-      <c r="D3" s="117"/>
-      <c r="E3" s="117"/>
-      <c r="F3" s="117"/>
-      <c r="G3" s="117"/>
-      <c r="H3" s="117"/>
+      <c r="B3" s="108"/>
+      <c r="C3" s="108"/>
+      <c r="D3" s="108"/>
+      <c r="E3" s="108"/>
+      <c r="F3" s="108"/>
+      <c r="G3" s="108"/>
+      <c r="H3" s="108"/>
     </row>
     <row r="4" spans="1:104" ht="4.5" customHeight="1">
       <c r="A4" s="39"/>
-      <c r="B4" s="117"/>
-      <c r="C4" s="117"/>
-      <c r="D4" s="117"/>
-      <c r="E4" s="117"/>
-      <c r="F4" s="117"/>
-      <c r="G4" s="117"/>
-      <c r="H4" s="117"/>
+      <c r="B4" s="108"/>
+      <c r="C4" s="108"/>
+      <c r="D4" s="108"/>
+      <c r="E4" s="108"/>
+      <c r="F4" s="108"/>
+      <c r="G4" s="108"/>
+      <c r="H4" s="108"/>
     </row>
     <row r="5" spans="1:104" s="41" customFormat="1" ht="18.75" customHeight="1">
       <c r="C5" s="68"/>
@@ -11997,75 +11934,75 @@
       <c r="CZ5" s="68"/>
     </row>
     <row r="6" spans="1:104" ht="18" customHeight="1">
-      <c r="B6" s="120" t="s">
+      <c r="B6" s="113" t="s">
         <v>0</v>
       </c>
-      <c r="C6" s="120"/>
-      <c r="D6" s="120"/>
-      <c r="E6" s="120"/>
-      <c r="F6" s="120"/>
-      <c r="G6" s="120"/>
-      <c r="H6" s="120"/>
-      <c r="I6" s="120"/>
-      <c r="J6" s="120"/>
-      <c r="K6" s="120"/>
-      <c r="L6" s="120"/>
-      <c r="M6" s="119" t="s">
+      <c r="C6" s="113"/>
+      <c r="D6" s="113"/>
+      <c r="E6" s="113"/>
+      <c r="F6" s="113"/>
+      <c r="G6" s="113"/>
+      <c r="H6" s="113"/>
+      <c r="I6" s="113"/>
+      <c r="J6" s="113"/>
+      <c r="K6" s="113"/>
+      <c r="L6" s="113"/>
+      <c r="M6" s="112" t="s">
         <v>311</v>
       </c>
-      <c r="N6" s="119"/>
-      <c r="O6" s="119" t="s">
+      <c r="N6" s="112"/>
+      <c r="O6" s="112" t="s">
         <v>312</v>
       </c>
-      <c r="P6" s="119"/>
+      <c r="P6" s="112"/>
       <c r="Q6" s="61" t="s">
         <v>356</v>
       </c>
       <c r="R6" s="61"/>
       <c r="S6" s="61"/>
-      <c r="T6" s="118" t="s">
+      <c r="T6" s="109" t="s">
         <v>100</v>
       </c>
-      <c r="U6" s="118"/>
-      <c r="V6" s="118"/>
-      <c r="W6" s="118"/>
-      <c r="X6" s="118"/>
-      <c r="Y6" s="118"/>
-      <c r="Z6" s="118"/>
-      <c r="AA6" s="118"/>
-      <c r="AB6" s="114" t="s">
+      <c r="U6" s="109"/>
+      <c r="V6" s="109"/>
+      <c r="W6" s="109"/>
+      <c r="X6" s="109"/>
+      <c r="Y6" s="109"/>
+      <c r="Z6" s="109"/>
+      <c r="AA6" s="109"/>
+      <c r="AB6" s="110" t="s">
         <v>124</v>
       </c>
-      <c r="AC6" s="114"/>
-      <c r="AD6" s="114"/>
-      <c r="AE6" s="114"/>
-      <c r="AF6" s="114"/>
-      <c r="AG6" s="114"/>
-      <c r="AH6" s="114"/>
-      <c r="AI6" s="114"/>
-      <c r="AJ6" s="114"/>
-      <c r="AK6" s="114"/>
-      <c r="AL6" s="115" t="s">
+      <c r="AC6" s="110"/>
+      <c r="AD6" s="110"/>
+      <c r="AE6" s="110"/>
+      <c r="AF6" s="110"/>
+      <c r="AG6" s="110"/>
+      <c r="AH6" s="110"/>
+      <c r="AI6" s="110"/>
+      <c r="AJ6" s="110"/>
+      <c r="AK6" s="110"/>
+      <c r="AL6" s="111" t="s">
         <v>125</v>
       </c>
-      <c r="AM6" s="115"/>
-      <c r="AN6" s="115"/>
-      <c r="AO6" s="115"/>
-      <c r="AP6" s="115"/>
-      <c r="AQ6" s="114" t="s">
+      <c r="AM6" s="111"/>
+      <c r="AN6" s="111"/>
+      <c r="AO6" s="111"/>
+      <c r="AP6" s="111"/>
+      <c r="AQ6" s="110" t="s">
         <v>140</v>
       </c>
-      <c r="AR6" s="114"/>
-      <c r="AS6" s="114"/>
-      <c r="AT6" s="114"/>
-      <c r="AU6" s="114"/>
-      <c r="AV6" s="115" t="s">
+      <c r="AR6" s="110"/>
+      <c r="AS6" s="110"/>
+      <c r="AT6" s="110"/>
+      <c r="AU6" s="110"/>
+      <c r="AV6" s="111" t="s">
         <v>165</v>
       </c>
-      <c r="AW6" s="115"/>
-      <c r="AX6" s="115"/>
-      <c r="AY6" s="115"/>
-      <c r="AZ6" s="115"/>
+      <c r="AW6" s="111"/>
+      <c r="AX6" s="111"/>
+      <c r="AY6" s="111"/>
+      <c r="AZ6" s="111"/>
       <c r="BA6" s="48"/>
       <c r="BB6" s="48"/>
       <c r="BC6" s="61" t="s">
@@ -12163,25 +12100,25 @@
       <c r="CK6" s="65">
         <v>14</v>
       </c>
-      <c r="CL6" s="111" t="s">
+      <c r="CL6" s="117" t="s">
         <v>193</v>
       </c>
-      <c r="CM6" s="112"/>
-      <c r="CN6" s="112"/>
-      <c r="CO6" s="112"/>
-      <c r="CP6" s="112"/>
-      <c r="CQ6" s="112"/>
-      <c r="CR6" s="113"/>
-      <c r="CS6" s="108" t="s">
+      <c r="CM6" s="118"/>
+      <c r="CN6" s="118"/>
+      <c r="CO6" s="118"/>
+      <c r="CP6" s="118"/>
+      <c r="CQ6" s="118"/>
+      <c r="CR6" s="119"/>
+      <c r="CS6" s="114" t="s">
         <v>381</v>
       </c>
-      <c r="CT6" s="109"/>
-      <c r="CU6" s="109"/>
-      <c r="CV6" s="109"/>
-      <c r="CW6" s="109"/>
-      <c r="CX6" s="109"/>
-      <c r="CY6" s="109"/>
-      <c r="CZ6" s="110"/>
+      <c r="CT6" s="115"/>
+      <c r="CU6" s="115"/>
+      <c r="CV6" s="115"/>
+      <c r="CW6" s="115"/>
+      <c r="CX6" s="115"/>
+      <c r="CY6" s="115"/>
+      <c r="CZ6" s="116"/>
     </row>
     <row r="7" spans="1:104" ht="114" collapsed="1">
       <c r="A7" s="67" t="s">
@@ -12367,38 +12304,38 @@
       <c r="BI7" s="66" t="s">
         <v>345</v>
       </c>
-      <c r="BJ7" s="116" t="s">
+      <c r="BJ7" s="120" t="s">
         <v>303</v>
       </c>
-      <c r="BK7" s="116"/>
-      <c r="BL7" s="116"/>
-      <c r="BM7" s="116"/>
-      <c r="BN7" s="116"/>
-      <c r="BO7" s="116"/>
-      <c r="BP7" s="116"/>
-      <c r="BQ7" s="116"/>
-      <c r="BR7" s="116"/>
-      <c r="BS7" s="116"/>
-      <c r="BT7" s="116"/>
-      <c r="BU7" s="116"/>
-      <c r="BV7" s="116"/>
-      <c r="BW7" s="116"/>
-      <c r="BX7" s="116" t="s">
+      <c r="BK7" s="120"/>
+      <c r="BL7" s="120"/>
+      <c r="BM7" s="120"/>
+      <c r="BN7" s="120"/>
+      <c r="BO7" s="120"/>
+      <c r="BP7" s="120"/>
+      <c r="BQ7" s="120"/>
+      <c r="BR7" s="120"/>
+      <c r="BS7" s="120"/>
+      <c r="BT7" s="120"/>
+      <c r="BU7" s="120"/>
+      <c r="BV7" s="120"/>
+      <c r="BW7" s="120"/>
+      <c r="BX7" s="120" t="s">
         <v>304</v>
       </c>
-      <c r="BY7" s="116"/>
-      <c r="BZ7" s="116"/>
-      <c r="CA7" s="116"/>
-      <c r="CB7" s="116"/>
-      <c r="CC7" s="116"/>
-      <c r="CD7" s="116"/>
-      <c r="CE7" s="116"/>
-      <c r="CF7" s="116"/>
-      <c r="CG7" s="116"/>
-      <c r="CH7" s="116"/>
-      <c r="CI7" s="116"/>
-      <c r="CJ7" s="116"/>
-      <c r="CK7" s="116"/>
+      <c r="BY7" s="120"/>
+      <c r="BZ7" s="120"/>
+      <c r="CA7" s="120"/>
+      <c r="CB7" s="120"/>
+      <c r="CC7" s="120"/>
+      <c r="CD7" s="120"/>
+      <c r="CE7" s="120"/>
+      <c r="CF7" s="120"/>
+      <c r="CG7" s="120"/>
+      <c r="CH7" s="120"/>
+      <c r="CI7" s="120"/>
+      <c r="CJ7" s="120"/>
+      <c r="CK7" s="120"/>
       <c r="CL7" s="48" t="s">
         <v>377</v>
       </c>
@@ -13256,7 +13193,7 @@
         <v>376</v>
       </c>
       <c r="BH10" s="63" t="s">
-        <v>491</v>
+        <v>485</v>
       </c>
       <c r="BI10" s="63" t="s">
         <v>288</v>
@@ -13424,44 +13361,44 @@
         <v>433</v>
       </c>
       <c r="G11" s="104" t="s">
-        <v>499</v>
+        <v>492</v>
       </c>
       <c r="H11" s="51" t="s">
         <v>434</v>
       </c>
       <c r="I11" s="105" t="s">
-        <v>515</v>
+        <v>506</v>
       </c>
       <c r="J11" s="53" t="s">
-        <v>493</v>
+        <v>487</v>
       </c>
       <c r="K11" s="53" t="s">
-        <v>521</v>
+        <v>511</v>
       </c>
       <c r="L11" s="51" t="s">
         <v>439</v>
       </c>
       <c r="M11" s="51" t="s">
-        <v>514</v>
+        <v>505</v>
       </c>
       <c r="N11" s="51" t="s">
-        <v>554</v>
+        <v>539</v>
       </c>
       <c r="O11" s="51" t="str">
         <f>IF(COUNTIF(C13:CZ13,"FALSE")&gt;0,"NG","OK")</f>
         <v>NG</v>
       </c>
       <c r="P11" s="51" t="s">
-        <v>555</v>
+        <v>540</v>
       </c>
       <c r="Q11" s="51" t="s">
+        <v>440</v>
+      </c>
+      <c r="R11" s="51" t="s">
         <v>441</v>
       </c>
-      <c r="R11" s="51" t="s">
+      <c r="S11" s="51" t="s">
         <v>442</v>
-      </c>
-      <c r="S11" s="51" t="s">
-        <v>443</v>
       </c>
       <c r="T11" s="51" t="s">
         <v>39</v>
@@ -13476,25 +13413,25 @@
         <v>79</v>
       </c>
       <c r="X11" s="51" t="s">
+        <v>443</v>
+      </c>
+      <c r="Y11" s="51" t="s">
+        <v>443</v>
+      </c>
+      <c r="Z11" s="51" t="s">
+        <v>443</v>
+      </c>
+      <c r="AA11" s="51" t="s">
+        <v>443</v>
+      </c>
+      <c r="AB11" s="51" t="s">
         <v>444</v>
-      </c>
-      <c r="Y11" s="51" t="s">
-        <v>444</v>
-      </c>
-      <c r="Z11" s="51" t="s">
-        <v>444</v>
-      </c>
-      <c r="AA11" s="51" t="s">
-        <v>444</v>
-      </c>
-      <c r="AB11" s="51" t="s">
-        <v>445</v>
       </c>
       <c r="AC11" s="51">
         <v>66</v>
       </c>
       <c r="AD11" s="51" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="AE11" s="51">
         <v>1199</v>
@@ -13506,13 +13443,13 @@
         <v>433</v>
       </c>
       <c r="AH11" s="51" t="s">
+        <v>446</v>
+      </c>
+      <c r="AI11" s="51" t="s">
         <v>447</v>
       </c>
-      <c r="AI11" s="51" t="s">
-        <v>448</v>
-      </c>
       <c r="AJ11" s="51" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="AK11" s="51">
         <v>4</v>
@@ -13525,13 +13462,13 @@
         <v>378206SAT310M6</v>
       </c>
       <c r="AN11" s="107" t="s">
-        <v>500</v>
+        <v>493</v>
       </c>
       <c r="AO11" s="107" t="s">
-        <v>506</v>
+        <v>498</v>
       </c>
       <c r="AP11" s="51" t="s">
-        <v>512</v>
+        <v>503</v>
       </c>
       <c r="AQ11" s="54" t="str">
         <f>SUBSTITUTE(J11," ","")</f>
@@ -13546,50 +13483,50 @@
         <v>10SW134789</v>
       </c>
       <c r="AT11" s="51" t="s">
+        <v>450</v>
+      </c>
+      <c r="AU11" s="51" t="s">
         <v>451</v>
       </c>
-      <c r="AU11" s="51" t="s">
+      <c r="AV11" s="51" t="s">
         <v>452</v>
       </c>
-      <c r="AV11" s="51" t="s">
-        <v>453</v>
-      </c>
       <c r="AW11" s="107" t="s">
-        <v>527</v>
+        <v>516</v>
       </c>
       <c r="AX11" s="54" t="str">
         <f>K11</f>
         <v>10SW134789</v>
       </c>
       <c r="AY11" s="51" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="AZ11" s="51" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="BA11" s="51"/>
       <c r="BB11" s="51"/>
       <c r="BC11" s="51" t="s">
-        <v>490</v>
+        <v>484</v>
       </c>
       <c r="BD11" s="54" t="str">
         <f>AP11</f>
         <v>MG1CA020-2.30</v>
       </c>
       <c r="BE11" s="51" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="BF11" s="51" t="s">
+        <v>459</v>
+      </c>
+      <c r="BG11" s="51" t="s">
+        <v>460</v>
+      </c>
+      <c r="BH11" s="51" t="s">
         <v>461</v>
       </c>
-      <c r="BG11" s="51" t="s">
+      <c r="BI11" s="51" t="s">
         <v>462</v>
-      </c>
-      <c r="BH11" s="51" t="s">
-        <v>463</v>
-      </c>
-      <c r="BI11" s="51" t="s">
-        <v>464</v>
       </c>
       <c r="BJ11" s="54" t="str">
         <f t="shared" si="0"/>
@@ -13708,10 +13645,10 @@
         <v>33373830352D3653412D54333130</v>
       </c>
       <c r="CM11" s="104" t="s">
-        <v>513</v>
+        <v>504</v>
       </c>
       <c r="CN11" s="51" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="CO11" s="51" t="s">
         <v>240</v>
@@ -13730,13 +13667,13 @@
         <v>37820-6SA-T310-M6</v>
       </c>
       <c r="CT11" s="107" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="CU11" s="51" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="CV11" s="51" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="CW11" s="56" t="s">
         <v>240</v>
@@ -13746,10 +13683,10 @@
         <v>37820-6SA-T31</v>
       </c>
       <c r="CY11" s="51" t="s">
-        <v>477</v>
+        <v>473</v>
       </c>
       <c r="CZ11" s="51" t="s">
-        <v>478</v>
+        <v>474</v>
       </c>
     </row>
     <row r="12" spans="1:104" s="42" customFormat="1" ht="44.25" hidden="1" customHeight="1" outlineLevel="1" collapsed="1">
@@ -13789,25 +13726,25 @@
         <v>79</v>
       </c>
       <c r="X12" s="47" t="s">
+        <v>443</v>
+      </c>
+      <c r="Y12" s="47" t="s">
+        <v>443</v>
+      </c>
+      <c r="Z12" s="47" t="s">
+        <v>443</v>
+      </c>
+      <c r="AA12" s="47" t="s">
+        <v>443</v>
+      </c>
+      <c r="AB12" s="47" t="s">
         <v>444</v>
-      </c>
-      <c r="Y12" s="47" t="s">
-        <v>444</v>
-      </c>
-      <c r="Z12" s="47" t="s">
-        <v>444</v>
-      </c>
-      <c r="AA12" s="47" t="s">
-        <v>444</v>
-      </c>
-      <c r="AB12" s="47" t="s">
-        <v>445</v>
       </c>
       <c r="AC12" s="47">
         <v>66</v>
       </c>
       <c r="AD12" s="47" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="AE12" s="47">
         <v>1199</v>
@@ -13819,13 +13756,13 @@
         <v>433</v>
       </c>
       <c r="AH12" s="47" t="s">
+        <v>446</v>
+      </c>
+      <c r="AI12" s="47" t="s">
         <v>447</v>
       </c>
-      <c r="AI12" s="47" t="s">
-        <v>448</v>
-      </c>
       <c r="AJ12" s="47" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="AK12" s="47">
         <v>4</v>
@@ -13834,66 +13771,66 @@
         <v>159</v>
       </c>
       <c r="AM12" s="47" t="s">
-        <v>536</v>
+        <v>524</v>
       </c>
       <c r="AN12" s="47" t="s">
-        <v>500</v>
+        <v>493</v>
       </c>
       <c r="AO12" s="47" t="s">
-        <v>506</v>
+        <v>498</v>
       </c>
       <c r="AP12" s="47" t="s">
-        <v>512</v>
+        <v>503</v>
       </c>
       <c r="AQ12" s="47" t="s">
-        <v>493</v>
+        <v>487</v>
       </c>
       <c r="AR12" s="47" t="s">
-        <v>537</v>
+        <v>525</v>
       </c>
       <c r="AS12" s="47" t="s">
-        <v>521</v>
+        <v>511</v>
       </c>
       <c r="AT12" s="47" t="s">
+        <v>450</v>
+      </c>
+      <c r="AU12" s="47" t="s">
         <v>451</v>
       </c>
-      <c r="AU12" s="47" t="s">
+      <c r="AV12" s="47" t="s">
         <v>452</v>
       </c>
-      <c r="AV12" s="47" t="s">
+      <c r="AW12" s="106" t="s">
+        <v>516</v>
+      </c>
+      <c r="AX12" s="47" t="s">
+        <v>511</v>
+      </c>
+      <c r="AY12" s="47" t="s">
         <v>453</v>
       </c>
-      <c r="AW12" s="106" t="s">
-        <v>527</v>
-      </c>
-      <c r="AX12" s="47" t="s">
-        <v>521</v>
-      </c>
-      <c r="AY12" s="47" t="s">
-        <v>454</v>
-      </c>
       <c r="AZ12" s="47" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="BA12" s="47"/>
       <c r="BB12" s="47"/>
       <c r="BC12" s="47" t="s">
-        <v>490</v>
+        <v>484</v>
       </c>
       <c r="BD12" s="47" t="s">
-        <v>512</v>
+        <v>503</v>
       </c>
       <c r="BE12" s="47" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="BF12" s="47" t="s">
+        <v>459</v>
+      </c>
+      <c r="BG12" s="47" t="s">
+        <v>460</v>
+      </c>
+      <c r="BH12" s="47" t="s">
         <v>461</v>
-      </c>
-      <c r="BG12" s="47" t="s">
-        <v>462</v>
-      </c>
-      <c r="BH12" s="47" t="s">
-        <v>463</v>
       </c>
       <c r="BI12" s="47"/>
       <c r="BJ12" s="47" t="str">
@@ -14009,18 +13946,18 @@
         <v>#VALUE!</v>
       </c>
       <c r="CL12" s="47" t="s">
-        <v>538</v>
+        <v>526</v>
       </c>
       <c r="CM12" s="58" t="s">
-        <v>513</v>
+        <v>504</v>
       </c>
       <c r="CN12" s="47" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="CO12" s="47"/>
       <c r="CP12" s="47"/>
       <c r="CQ12" s="47" t="s">
-        <v>492</v>
+        <v>486</v>
       </c>
       <c r="CR12" s="47"/>
       <c r="CS12" s="47" t="str">
@@ -14383,7 +14320,7 @@
     <row r="14" spans="1:104" s="42" customFormat="1" ht="44.25" customHeight="1" collapsed="1">
       <c r="A14" s="45"/>
       <c r="B14" s="51">
-        <f t="shared" ref="B14:B34" si="56">B11+1</f>
+        <f t="shared" ref="B14:B28" si="56">B11+1</f>
         <v>2</v>
       </c>
       <c r="C14" s="52">
@@ -14399,44 +14336,44 @@
         <v>433</v>
       </c>
       <c r="G14" s="104" t="s">
-        <v>499</v>
+        <v>492</v>
       </c>
       <c r="H14" s="51" t="s">
         <v>434</v>
       </c>
       <c r="I14" s="105" t="s">
-        <v>520</v>
+        <v>510</v>
       </c>
       <c r="J14" s="53" t="s">
-        <v>494</v>
+        <v>488</v>
       </c>
       <c r="K14" s="53" t="s">
-        <v>522</v>
+        <v>512</v>
       </c>
       <c r="L14" s="51" t="s">
         <v>436</v>
       </c>
       <c r="M14" s="51" t="s">
-        <v>514</v>
+        <v>505</v>
       </c>
       <c r="N14" s="51" t="s">
-        <v>554</v>
+        <v>539</v>
       </c>
       <c r="O14" s="51" t="str">
         <f>IF(COUNTIF(C16:CZ16,"FALSE")&gt;0,"NG","OK")</f>
         <v>NG</v>
       </c>
       <c r="P14" s="51" t="s">
-        <v>555</v>
+        <v>540</v>
       </c>
       <c r="Q14" s="51" t="s">
+        <v>440</v>
+      </c>
+      <c r="R14" s="51" t="s">
         <v>441</v>
       </c>
-      <c r="R14" s="51" t="s">
+      <c r="S14" s="51" t="s">
         <v>442</v>
-      </c>
-      <c r="S14" s="51" t="s">
-        <v>443</v>
       </c>
       <c r="T14" s="51" t="s">
         <v>39</v>
@@ -14451,25 +14388,25 @@
         <v>79</v>
       </c>
       <c r="X14" s="51" t="s">
+        <v>443</v>
+      </c>
+      <c r="Y14" s="51" t="s">
+        <v>443</v>
+      </c>
+      <c r="Z14" s="51" t="s">
+        <v>443</v>
+      </c>
+      <c r="AA14" s="51" t="s">
+        <v>443</v>
+      </c>
+      <c r="AB14" s="51" t="s">
         <v>444</v>
-      </c>
-      <c r="Y14" s="51" t="s">
-        <v>444</v>
-      </c>
-      <c r="Z14" s="51" t="s">
-        <v>444</v>
-      </c>
-      <c r="AA14" s="51" t="s">
-        <v>444</v>
-      </c>
-      <c r="AB14" s="51" t="s">
-        <v>445</v>
       </c>
       <c r="AC14" s="51">
         <v>66</v>
       </c>
       <c r="AD14" s="51" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="AE14" s="51">
         <v>1199</v>
@@ -14481,13 +14418,13 @@
         <v>433</v>
       </c>
       <c r="AH14" s="51" t="s">
+        <v>446</v>
+      </c>
+      <c r="AI14" s="51" t="s">
         <v>447</v>
       </c>
-      <c r="AI14" s="51" t="s">
-        <v>448</v>
-      </c>
       <c r="AJ14" s="51" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="AK14" s="51">
         <v>4</v>
@@ -14500,13 +14437,13 @@
         <v>378206SAT410M6</v>
       </c>
       <c r="AN14" s="107" t="s">
-        <v>501</v>
+        <v>494</v>
       </c>
       <c r="AO14" s="107" t="s">
-        <v>507</v>
+        <v>499</v>
       </c>
       <c r="AP14" s="51" t="s">
-        <v>512</v>
+        <v>503</v>
       </c>
       <c r="AQ14" s="54" t="str">
         <f>SUBSTITUTE(J14," ","")</f>
@@ -14521,53 +14458,53 @@
         <v>10SW134790</v>
       </c>
       <c r="AT14" s="51" t="s">
+        <v>450</v>
+      </c>
+      <c r="AU14" s="51" t="s">
         <v>451</v>
       </c>
-      <c r="AU14" s="51" t="s">
+      <c r="AV14" s="51" t="s">
         <v>452</v>
       </c>
-      <c r="AV14" s="51" t="s">
-        <v>453</v>
-      </c>
       <c r="AW14" s="107" t="s">
-        <v>528</v>
+        <v>517</v>
       </c>
       <c r="AX14" s="54" t="str">
         <f>K14</f>
         <v>10SW134790</v>
       </c>
       <c r="AY14" s="51" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="AZ14" s="51" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="BA14" s="51"/>
       <c r="BB14" s="51"/>
       <c r="BC14" s="51" t="s">
-        <v>490</v>
+        <v>484</v>
       </c>
       <c r="BD14" s="54" t="str">
         <f>AP14</f>
         <v>MG1CA020-2.30</v>
       </c>
       <c r="BE14" s="51" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="BF14" s="51" t="s">
+        <v>459</v>
+      </c>
+      <c r="BG14" s="51" t="s">
+        <v>460</v>
+      </c>
+      <c r="BH14" s="51" t="s">
         <v>461</v>
       </c>
-      <c r="BG14" s="51" t="s">
-        <v>462</v>
-      </c>
-      <c r="BH14" s="51" t="s">
+      <c r="BI14" s="51" t="s">
         <v>463</v>
       </c>
-      <c r="BI14" s="51" t="s">
-        <v>465</v>
-      </c>
       <c r="BJ14" s="54" t="str">
-        <f t="shared" ref="BJ14:BW29" si="57">MID($BI14,BJ$6,1)</f>
+        <f t="shared" ref="BJ14:BW26" si="57">MID($BI14,BJ$6,1)</f>
         <v>3</v>
       </c>
       <c r="BK14" s="54" t="str">
@@ -14683,10 +14620,10 @@
         <v>33373830352D3653412D54343130</v>
       </c>
       <c r="CM14" s="104" t="s">
-        <v>513</v>
+        <v>504</v>
       </c>
       <c r="CN14" s="51" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="CO14" s="51" t="s">
         <v>240</v>
@@ -14705,13 +14642,13 @@
         <v>37820-6SA-T410-M6</v>
       </c>
       <c r="CT14" s="107" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="CU14" s="51" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="CV14" s="51" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="CW14" s="56" t="s">
         <v>240</v>
@@ -14721,10 +14658,10 @@
         <v>37820-6SA-T41</v>
       </c>
       <c r="CY14" s="51" t="s">
-        <v>479</v>
+        <v>475</v>
       </c>
       <c r="CZ14" s="51" t="s">
-        <v>480</v>
+        <v>476</v>
       </c>
     </row>
     <row r="15" spans="1:104" s="42" customFormat="1" ht="44.25" hidden="1" customHeight="1" outlineLevel="1" collapsed="1">
@@ -14765,25 +14702,25 @@
         <v>79</v>
       </c>
       <c r="X15" s="47" t="s">
+        <v>443</v>
+      </c>
+      <c r="Y15" s="47" t="s">
+        <v>443</v>
+      </c>
+      <c r="Z15" s="47" t="s">
+        <v>443</v>
+      </c>
+      <c r="AA15" s="47" t="s">
+        <v>443</v>
+      </c>
+      <c r="AB15" s="47" t="s">
         <v>444</v>
-      </c>
-      <c r="Y15" s="47" t="s">
-        <v>444</v>
-      </c>
-      <c r="Z15" s="47" t="s">
-        <v>444</v>
-      </c>
-      <c r="AA15" s="47" t="s">
-        <v>444</v>
-      </c>
-      <c r="AB15" s="47" t="s">
-        <v>445</v>
       </c>
       <c r="AC15" s="47">
         <v>66</v>
       </c>
       <c r="AD15" s="47" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="AE15" s="47">
         <v>1199</v>
@@ -14795,13 +14732,13 @@
         <v>433</v>
       </c>
       <c r="AH15" s="47" t="s">
+        <v>446</v>
+      </c>
+      <c r="AI15" s="47" t="s">
         <v>447</v>
       </c>
-      <c r="AI15" s="47" t="s">
-        <v>448</v>
-      </c>
       <c r="AJ15" s="47" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="AK15" s="47">
         <v>4</v>
@@ -14810,66 +14747,66 @@
         <v>159</v>
       </c>
       <c r="AM15" s="47" t="s">
-        <v>539</v>
+        <v>527</v>
       </c>
       <c r="AN15" s="47" t="s">
-        <v>501</v>
+        <v>494</v>
       </c>
       <c r="AO15" s="47" t="s">
-        <v>507</v>
+        <v>499</v>
       </c>
       <c r="AP15" s="47" t="s">
+        <v>503</v>
+      </c>
+      <c r="AQ15" s="47" t="s">
+        <v>488</v>
+      </c>
+      <c r="AR15" s="47" t="s">
+        <v>528</v>
+      </c>
+      <c r="AS15" s="47" t="s">
         <v>512</v>
       </c>
-      <c r="AQ15" s="47" t="s">
-        <v>494</v>
-      </c>
-      <c r="AR15" s="47" t="s">
-        <v>540</v>
-      </c>
-      <c r="AS15" s="47" t="s">
-        <v>522</v>
-      </c>
       <c r="AT15" s="47" t="s">
+        <v>450</v>
+      </c>
+      <c r="AU15" s="47" t="s">
         <v>451</v>
       </c>
-      <c r="AU15" s="47" t="s">
+      <c r="AV15" s="47" t="s">
         <v>452</v>
       </c>
-      <c r="AV15" s="47" t="s">
+      <c r="AW15" s="106" t="s">
+        <v>517</v>
+      </c>
+      <c r="AX15" s="47" t="s">
+        <v>512</v>
+      </c>
+      <c r="AY15" s="47" t="s">
         <v>453</v>
       </c>
-      <c r="AW15" s="106" t="s">
-        <v>528</v>
-      </c>
-      <c r="AX15" s="47" t="s">
-        <v>522</v>
-      </c>
-      <c r="AY15" s="47" t="s">
-        <v>454</v>
-      </c>
       <c r="AZ15" s="47" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="BA15" s="47"/>
       <c r="BB15" s="47"/>
       <c r="BC15" s="47" t="s">
-        <v>490</v>
+        <v>484</v>
       </c>
       <c r="BD15" s="47" t="s">
-        <v>512</v>
+        <v>503</v>
       </c>
       <c r="BE15" s="47" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="BF15" s="47" t="s">
+        <v>459</v>
+      </c>
+      <c r="BG15" s="47" t="s">
+        <v>460</v>
+      </c>
+      <c r="BH15" s="47" t="s">
         <v>461</v>
-      </c>
-      <c r="BG15" s="47" t="s">
-        <v>462</v>
-      </c>
-      <c r="BH15" s="47" t="s">
-        <v>463</v>
       </c>
       <c r="BI15" s="47"/>
       <c r="BJ15" s="47" t="str">
@@ -14985,18 +14922,18 @@
         <v>#VALUE!</v>
       </c>
       <c r="CL15" s="47" t="s">
-        <v>541</v>
+        <v>529</v>
       </c>
       <c r="CM15" s="58" t="s">
-        <v>513</v>
+        <v>504</v>
       </c>
       <c r="CN15" s="47" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="CO15" s="47"/>
       <c r="CP15" s="47"/>
       <c r="CQ15" s="47" t="s">
-        <v>492</v>
+        <v>486</v>
       </c>
       <c r="CR15" s="47"/>
       <c r="CS15" s="47" t="str">
@@ -15359,9 +15296,9 @@
     </row>
     <row r="17" spans="1:104" s="42" customFormat="1" ht="44.25" customHeight="1" collapsed="1">
       <c r="A17" s="45"/>
-      <c r="B17" s="51">
-        <f t="shared" si="56"/>
-        <v>3</v>
+      <c r="B17" s="51" t="e">
+        <f>#REF!+1</f>
+        <v>#REF!</v>
       </c>
       <c r="C17" s="52">
         <v>46176</v>
@@ -15376,44 +15313,44 @@
         <v>433</v>
       </c>
       <c r="G17" s="104" t="s">
-        <v>499</v>
+        <v>492</v>
       </c>
       <c r="H17" s="51" t="s">
         <v>434</v>
       </c>
       <c r="I17" s="105" t="s">
-        <v>519</v>
+        <v>509</v>
       </c>
       <c r="J17" s="53" t="s">
-        <v>495</v>
+        <v>489</v>
       </c>
       <c r="K17" s="53" t="s">
-        <v>523</v>
+        <v>513</v>
       </c>
       <c r="L17" s="51" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="M17" s="51" t="s">
-        <v>514</v>
+        <v>505</v>
       </c>
       <c r="N17" s="51" t="s">
-        <v>554</v>
+        <v>539</v>
       </c>
       <c r="O17" s="51" t="str">
         <f>IF(COUNTIF(C19:CZ19,"FALSE")&gt;0,"NG","OK")</f>
         <v>NG</v>
       </c>
       <c r="P17" s="51" t="s">
-        <v>555</v>
+        <v>540</v>
       </c>
       <c r="Q17" s="51" t="s">
+        <v>440</v>
+      </c>
+      <c r="R17" s="51" t="s">
         <v>441</v>
       </c>
-      <c r="R17" s="51" t="s">
+      <c r="S17" s="51" t="s">
         <v>442</v>
-      </c>
-      <c r="S17" s="51" t="s">
-        <v>443</v>
       </c>
       <c r="T17" s="51" t="s">
         <v>39</v>
@@ -15428,25 +15365,25 @@
         <v>79</v>
       </c>
       <c r="X17" s="51" t="s">
+        <v>443</v>
+      </c>
+      <c r="Y17" s="51" t="s">
+        <v>443</v>
+      </c>
+      <c r="Z17" s="51" t="s">
+        <v>443</v>
+      </c>
+      <c r="AA17" s="51" t="s">
+        <v>443</v>
+      </c>
+      <c r="AB17" s="51" t="s">
         <v>444</v>
-      </c>
-      <c r="Y17" s="51" t="s">
-        <v>444</v>
-      </c>
-      <c r="Z17" s="51" t="s">
-        <v>444</v>
-      </c>
-      <c r="AA17" s="51" t="s">
-        <v>444</v>
-      </c>
-      <c r="AB17" s="51" t="s">
-        <v>445</v>
       </c>
       <c r="AC17" s="51">
         <v>66</v>
       </c>
       <c r="AD17" s="51" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="AE17" s="51">
         <v>1199</v>
@@ -15458,13 +15395,13 @@
         <v>433</v>
       </c>
       <c r="AH17" s="51" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="AI17" s="51" t="s">
+        <v>448</v>
+      </c>
+      <c r="AJ17" s="51" t="s">
         <v>449</v>
-      </c>
-      <c r="AJ17" s="51" t="s">
-        <v>450</v>
       </c>
       <c r="AK17" s="51">
         <v>4</v>
@@ -15474,74 +15411,74 @@
       </c>
       <c r="AM17" s="54" t="str">
         <f>SUBSTITUTE(SUBSTITUTE(J17," ",""),"-","")</f>
-        <v>378206SAT810M6</v>
+        <v>378206SAT910M6</v>
       </c>
       <c r="AN17" s="107" t="s">
-        <v>502</v>
+        <v>495</v>
       </c>
       <c r="AO17" s="107" t="s">
-        <v>508</v>
+        <v>500</v>
       </c>
       <c r="AP17" s="51" t="s">
-        <v>512</v>
+        <v>503</v>
       </c>
       <c r="AQ17" s="54" t="str">
         <f>SUBSTITUTE(J17," ","")</f>
-        <v>37820-6SA-T810-M6</v>
+        <v>37820-6SA-T910-M6</v>
       </c>
       <c r="AR17" s="54" t="str">
         <f>IF(RIGHT(SUBSTITUTE(J17," ",""),4)="0-M6",LEFT(SUBSTITUTE(J17," ",""),LEN(SUBSTITUTE(J17," ",""))-4),SUBSTITUTE(J17," ",""))</f>
-        <v>37820-6SA-T81</v>
+        <v>37820-6SA-T91</v>
       </c>
       <c r="AS17" s="54" t="str">
         <f>K17</f>
-        <v>10SW134797</v>
+        <v>10SW134798</v>
       </c>
       <c r="AT17" s="51" t="s">
+        <v>450</v>
+      </c>
+      <c r="AU17" s="51" t="s">
         <v>451</v>
       </c>
-      <c r="AU17" s="51" t="s">
+      <c r="AV17" s="51" t="s">
         <v>452</v>
       </c>
-      <c r="AV17" s="51" t="s">
-        <v>453</v>
-      </c>
       <c r="AW17" s="107" t="s">
-        <v>529</v>
+        <v>518</v>
       </c>
       <c r="AX17" s="54" t="str">
         <f>K17</f>
-        <v>10SW134797</v>
+        <v>10SW134798</v>
       </c>
       <c r="AY17" s="51" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="AZ17" s="51" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="BA17" s="51"/>
       <c r="BB17" s="51"/>
       <c r="BC17" s="51" t="s">
-        <v>490</v>
+        <v>484</v>
       </c>
       <c r="BD17" s="54" t="str">
         <f>AP17</f>
         <v>MG1CA020-2.30</v>
       </c>
       <c r="BE17" s="51" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="BF17" s="51" t="s">
+        <v>459</v>
+      </c>
+      <c r="BG17" s="51" t="s">
+        <v>460</v>
+      </c>
+      <c r="BH17" s="51" t="s">
         <v>461</v>
       </c>
-      <c r="BG17" s="51" t="s">
-        <v>462</v>
-      </c>
-      <c r="BH17" s="51" t="s">
-        <v>463</v>
-      </c>
       <c r="BI17" s="51" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="BJ17" s="54" t="str">
         <f t="shared" si="57"/>
@@ -15589,7 +15526,7 @@
       </c>
       <c r="BU17" s="54" t="str">
         <f t="shared" si="57"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BV17" s="54" t="str">
         <f t="shared" si="57"/>
@@ -15645,7 +15582,7 @@
       </c>
       <c r="CI17" s="55" t="str">
         <f t="shared" ref="CI17:CI18" si="86">DEC2HEX(CODE(BU17),2)</f>
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="CJ17" s="55" t="str">
         <f t="shared" ref="CJ17:CJ18" si="87">DEC2HEX(CODE(BV17),2)</f>
@@ -15657,13 +15594,13 @@
       </c>
       <c r="CL17" s="54" t="str">
         <f>BX17&amp;BY17&amp;BZ17&amp;CA17&amp;CB17&amp;CC17&amp;CD17&amp;CE17&amp;CF17&amp;CG17&amp;CH17&amp;CI17&amp;CJ17&amp;CK17</f>
-        <v>33373830352D3653412D54383130</v>
+        <v>33373830352D3653412D54393130</v>
       </c>
       <c r="CM17" s="104" t="s">
-        <v>513</v>
+        <v>504</v>
       </c>
       <c r="CN17" s="51" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="CO17" s="51" t="s">
         <v>240</v>
@@ -15679,36 +15616,36 @@
       </c>
       <c r="CS17" s="54" t="str">
         <f>SUBSTITUTE(J17," ","")</f>
-        <v>37820-6SA-T810-M6</v>
+        <v>37820-6SA-T910-M6</v>
       </c>
       <c r="CT17" s="107" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="CU17" s="51" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="CV17" s="51" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="CW17" s="56" t="s">
         <v>240</v>
       </c>
       <c r="CX17" s="51" t="str">
         <f>AR17</f>
-        <v>37820-6SA-T81</v>
-      </c>
-      <c r="CY17" s="104" t="s">
-        <v>481</v>
+        <v>37820-6SA-T91</v>
+      </c>
+      <c r="CY17" s="51" t="s">
+        <v>477</v>
       </c>
       <c r="CZ17" s="51" t="s">
-        <v>482</v>
+        <v>478</v>
       </c>
     </row>
     <row r="18" spans="1:104" s="42" customFormat="1" ht="44.25" hidden="1" customHeight="1" outlineLevel="1" collapsed="1">
       <c r="A18" s="45"/>
-      <c r="B18" s="47">
-        <f t="shared" si="56"/>
-        <v>3</v>
+      <c r="B18" s="47" t="e">
+        <f>#REF!+1</f>
+        <v>#REF!</v>
       </c>
       <c r="C18" s="57"/>
       <c r="D18" s="47" t="s">
@@ -15742,25 +15679,25 @@
         <v>79</v>
       </c>
       <c r="X18" s="47" t="s">
+        <v>443</v>
+      </c>
+      <c r="Y18" s="47" t="s">
+        <v>443</v>
+      </c>
+      <c r="Z18" s="47" t="s">
+        <v>443</v>
+      </c>
+      <c r="AA18" s="47" t="s">
+        <v>443</v>
+      </c>
+      <c r="AB18" s="47" t="s">
         <v>444</v>
-      </c>
-      <c r="Y18" s="47" t="s">
-        <v>444</v>
-      </c>
-      <c r="Z18" s="47" t="s">
-        <v>444</v>
-      </c>
-      <c r="AA18" s="47" t="s">
-        <v>444</v>
-      </c>
-      <c r="AB18" s="47" t="s">
-        <v>445</v>
       </c>
       <c r="AC18" s="47">
         <v>66</v>
       </c>
       <c r="AD18" s="47" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="AE18" s="47">
         <v>1199</v>
@@ -15772,13 +15709,13 @@
         <v>433</v>
       </c>
       <c r="AH18" s="47" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="AI18" s="47" t="s">
+        <v>448</v>
+      </c>
+      <c r="AJ18" s="47" t="s">
         <v>449</v>
-      </c>
-      <c r="AJ18" s="47" t="s">
-        <v>450</v>
       </c>
       <c r="AK18" s="47">
         <v>4</v>
@@ -15787,66 +15724,66 @@
         <v>159</v>
       </c>
       <c r="AM18" s="47" t="s">
-        <v>542</v>
+        <v>530</v>
       </c>
       <c r="AN18" s="47" t="s">
-        <v>502</v>
+        <v>495</v>
       </c>
       <c r="AO18" s="47" t="s">
-        <v>508</v>
+        <v>500</v>
       </c>
       <c r="AP18" s="47" t="s">
-        <v>512</v>
+        <v>503</v>
       </c>
       <c r="AQ18" s="47" t="s">
-        <v>495</v>
+        <v>489</v>
       </c>
       <c r="AR18" s="47" t="s">
-        <v>543</v>
+        <v>531</v>
       </c>
       <c r="AS18" s="47" t="s">
-        <v>523</v>
+        <v>513</v>
       </c>
       <c r="AT18" s="47" t="s">
+        <v>450</v>
+      </c>
+      <c r="AU18" s="47" t="s">
         <v>451</v>
       </c>
-      <c r="AU18" s="47" t="s">
+      <c r="AV18" s="47" t="s">
         <v>452</v>
       </c>
-      <c r="AV18" s="47" t="s">
+      <c r="AW18" s="106" t="s">
+        <v>518</v>
+      </c>
+      <c r="AX18" s="47" t="s">
+        <v>513</v>
+      </c>
+      <c r="AY18" s="47" t="s">
         <v>453</v>
       </c>
-      <c r="AW18" s="106" t="s">
-        <v>529</v>
-      </c>
-      <c r="AX18" s="47" t="s">
-        <v>523</v>
-      </c>
-      <c r="AY18" s="47" t="s">
-        <v>454</v>
-      </c>
       <c r="AZ18" s="47" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="BA18" s="47"/>
       <c r="BB18" s="47"/>
       <c r="BC18" s="47" t="s">
-        <v>490</v>
+        <v>484</v>
       </c>
       <c r="BD18" s="47" t="s">
-        <v>512</v>
+        <v>503</v>
       </c>
       <c r="BE18" s="47" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="BF18" s="47" t="s">
+        <v>459</v>
+      </c>
+      <c r="BG18" s="47" t="s">
+        <v>460</v>
+      </c>
+      <c r="BH18" s="47" t="s">
         <v>461</v>
-      </c>
-      <c r="BG18" s="47" t="s">
-        <v>462</v>
-      </c>
-      <c r="BH18" s="47" t="s">
-        <v>463</v>
       </c>
       <c r="BI18" s="47"/>
       <c r="BJ18" s="47" t="str">
@@ -15962,18 +15899,18 @@
         <v>#VALUE!</v>
       </c>
       <c r="CL18" s="47" t="s">
-        <v>544</v>
+        <v>532</v>
       </c>
       <c r="CM18" s="58" t="s">
-        <v>513</v>
+        <v>504</v>
       </c>
       <c r="CN18" s="47" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="CO18" s="47"/>
       <c r="CP18" s="47"/>
       <c r="CQ18" s="47" t="s">
-        <v>492</v>
+        <v>486</v>
       </c>
       <c r="CR18" s="47"/>
       <c r="CS18" s="47" t="str">
@@ -15990,9 +15927,9 @@
     </row>
     <row r="19" spans="1:104" s="43" customFormat="1" ht="39.950000000000003" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A19" s="45"/>
-      <c r="B19" s="46">
-        <f t="shared" si="56"/>
-        <v>3</v>
+      <c r="B19" s="46" t="e">
+        <f>#REF!+1</f>
+        <v>#REF!</v>
       </c>
       <c r="C19" s="47" t="s">
         <v>264</v>
@@ -16336,9 +16273,9 @@
     </row>
     <row r="20" spans="1:104" s="42" customFormat="1" ht="44.25" customHeight="1" collapsed="1">
       <c r="A20" s="45"/>
-      <c r="B20" s="51">
+      <c r="B20" s="51" t="e">
         <f t="shared" si="56"/>
-        <v>4</v>
+        <v>#REF!</v>
       </c>
       <c r="C20" s="52">
         <v>46176</v>
@@ -16353,44 +16290,44 @@
         <v>433</v>
       </c>
       <c r="G20" s="104" t="s">
-        <v>499</v>
+        <v>492</v>
       </c>
       <c r="H20" s="51" t="s">
         <v>434</v>
       </c>
       <c r="I20" s="105" t="s">
-        <v>518</v>
+        <v>508</v>
       </c>
       <c r="J20" s="53" t="s">
-        <v>496</v>
+        <v>490</v>
       </c>
       <c r="K20" s="53" t="s">
-        <v>524</v>
+        <v>514</v>
       </c>
       <c r="L20" s="51" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="M20" s="51" t="s">
-        <v>514</v>
+        <v>505</v>
       </c>
       <c r="N20" s="51" t="s">
-        <v>554</v>
+        <v>539</v>
       </c>
       <c r="O20" s="51" t="str">
         <f>IF(COUNTIF(C22:CZ22,"FALSE")&gt;0,"NG","OK")</f>
         <v>NG</v>
       </c>
       <c r="P20" s="51" t="s">
-        <v>555</v>
+        <v>540</v>
       </c>
       <c r="Q20" s="51" t="s">
+        <v>440</v>
+      </c>
+      <c r="R20" s="51" t="s">
         <v>441</v>
       </c>
-      <c r="R20" s="51" t="s">
+      <c r="S20" s="51" t="s">
         <v>442</v>
-      </c>
-      <c r="S20" s="51" t="s">
-        <v>443</v>
       </c>
       <c r="T20" s="51" t="s">
         <v>39</v>
@@ -16405,25 +16342,25 @@
         <v>79</v>
       </c>
       <c r="X20" s="51" t="s">
+        <v>443</v>
+      </c>
+      <c r="Y20" s="51" t="s">
+        <v>443</v>
+      </c>
+      <c r="Z20" s="51" t="s">
+        <v>443</v>
+      </c>
+      <c r="AA20" s="51" t="s">
+        <v>443</v>
+      </c>
+      <c r="AB20" s="51" t="s">
         <v>444</v>
-      </c>
-      <c r="Y20" s="51" t="s">
-        <v>444</v>
-      </c>
-      <c r="Z20" s="51" t="s">
-        <v>444</v>
-      </c>
-      <c r="AA20" s="51" t="s">
-        <v>444</v>
-      </c>
-      <c r="AB20" s="51" t="s">
-        <v>445</v>
       </c>
       <c r="AC20" s="51">
         <v>66</v>
       </c>
       <c r="AD20" s="51" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="AE20" s="51">
         <v>1199</v>
@@ -16435,13 +16372,13 @@
         <v>433</v>
       </c>
       <c r="AH20" s="51" t="s">
+        <v>446</v>
+      </c>
+      <c r="AI20" s="51" t="s">
         <v>447</v>
       </c>
-      <c r="AI20" s="51" t="s">
+      <c r="AJ20" s="51" t="s">
         <v>449</v>
-      </c>
-      <c r="AJ20" s="51" t="s">
-        <v>450</v>
       </c>
       <c r="AK20" s="51">
         <v>4</v>
@@ -16451,74 +16388,74 @@
       </c>
       <c r="AM20" s="54" t="str">
         <f>SUBSTITUTE(SUBSTITUTE(J20," ",""),"-","")</f>
-        <v>378206SAT910M6</v>
+        <v>378206SATA10M6</v>
       </c>
       <c r="AN20" s="107" t="s">
+        <v>496</v>
+      </c>
+      <c r="AO20" s="107" t="s">
+        <v>501</v>
+      </c>
+      <c r="AP20" s="51" t="s">
         <v>503</v>
-      </c>
-      <c r="AO20" s="107" t="s">
-        <v>509</v>
-      </c>
-      <c r="AP20" s="51" t="s">
-        <v>512</v>
       </c>
       <c r="AQ20" s="54" t="str">
         <f>SUBSTITUTE(J20," ","")</f>
-        <v>37820-6SA-T910-M6</v>
+        <v>37820-6SA-TA10-M6</v>
       </c>
       <c r="AR20" s="54" t="str">
         <f>IF(RIGHT(SUBSTITUTE(J20," ",""),4)="0-M6",LEFT(SUBSTITUTE(J20," ",""),LEN(SUBSTITUTE(J20," ",""))-4),SUBSTITUTE(J20," ",""))</f>
-        <v>37820-6SA-T91</v>
+        <v>37820-6SA-TA1</v>
       </c>
       <c r="AS20" s="54" t="str">
         <f>K20</f>
-        <v>10SW134798</v>
+        <v>10SW134799</v>
       </c>
       <c r="AT20" s="51" t="s">
+        <v>450</v>
+      </c>
+      <c r="AU20" s="51" t="s">
         <v>451</v>
       </c>
-      <c r="AU20" s="51" t="s">
+      <c r="AV20" s="51" t="s">
         <v>452</v>
       </c>
-      <c r="AV20" s="51" t="s">
-        <v>453</v>
-      </c>
       <c r="AW20" s="107" t="s">
-        <v>530</v>
+        <v>519</v>
       </c>
       <c r="AX20" s="54" t="str">
         <f>K20</f>
-        <v>10SW134798</v>
+        <v>10SW134799</v>
       </c>
       <c r="AY20" s="51" t="s">
+        <v>453</v>
+      </c>
+      <c r="AZ20" s="51" t="s">
         <v>454</v>
-      </c>
-      <c r="AZ20" s="51" t="s">
-        <v>458</v>
       </c>
       <c r="BA20" s="51"/>
       <c r="BB20" s="51"/>
       <c r="BC20" s="51" t="s">
-        <v>490</v>
+        <v>484</v>
       </c>
       <c r="BD20" s="54" t="str">
         <f>AP20</f>
         <v>MG1CA020-2.30</v>
       </c>
       <c r="BE20" s="51" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="BF20" s="51" t="s">
+        <v>459</v>
+      </c>
+      <c r="BG20" s="51" t="s">
+        <v>460</v>
+      </c>
+      <c r="BH20" s="51" t="s">
         <v>461</v>
       </c>
-      <c r="BG20" s="51" t="s">
-        <v>462</v>
-      </c>
-      <c r="BH20" s="51" t="s">
-        <v>463</v>
-      </c>
       <c r="BI20" s="51" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="BJ20" s="54" t="str">
         <f t="shared" si="57"/>
@@ -16566,7 +16503,7 @@
       </c>
       <c r="BU20" s="54" t="str">
         <f t="shared" si="57"/>
-        <v>9</v>
+        <v>A</v>
       </c>
       <c r="BV20" s="54" t="str">
         <f t="shared" si="57"/>
@@ -16622,7 +16559,7 @@
       </c>
       <c r="CI20" s="55" t="str">
         <f t="shared" ref="CI20:CI21" si="103">DEC2HEX(CODE(BU20),2)</f>
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="CJ20" s="55" t="str">
         <f t="shared" ref="CJ20:CJ21" si="104">DEC2HEX(CODE(BV20),2)</f>
@@ -16634,13 +16571,13 @@
       </c>
       <c r="CL20" s="54" t="str">
         <f>BX20&amp;BY20&amp;BZ20&amp;CA20&amp;CB20&amp;CC20&amp;CD20&amp;CE20&amp;CF20&amp;CG20&amp;CH20&amp;CI20&amp;CJ20&amp;CK20</f>
-        <v>33373830352D3653412D54393130</v>
+        <v>33373830352D3653412D54413130</v>
       </c>
       <c r="CM20" s="104" t="s">
-        <v>513</v>
+        <v>504</v>
       </c>
       <c r="CN20" s="51" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="CO20" s="51" t="s">
         <v>240</v>
@@ -16656,36 +16593,36 @@
       </c>
       <c r="CS20" s="54" t="str">
         <f>SUBSTITUTE(J20," ","")</f>
-        <v>37820-6SA-T910-M6</v>
+        <v>37820-6SA-TA10-M6</v>
       </c>
       <c r="CT20" s="107" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="CU20" s="51" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="CV20" s="51" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="CW20" s="56" t="s">
         <v>240</v>
       </c>
       <c r="CX20" s="51" t="str">
         <f>AR20</f>
-        <v>37820-6SA-T91</v>
+        <v>37820-6SA-TA1</v>
       </c>
       <c r="CY20" s="51" t="s">
-        <v>483</v>
+        <v>479</v>
       </c>
       <c r="CZ20" s="51" t="s">
-        <v>484</v>
+        <v>480</v>
       </c>
     </row>
     <row r="21" spans="1:104" s="42" customFormat="1" ht="44.25" hidden="1" customHeight="1" outlineLevel="1" collapsed="1">
       <c r="A21" s="45"/>
-      <c r="B21" s="47">
+      <c r="B21" s="47" t="e">
         <f t="shared" si="56"/>
-        <v>4</v>
+        <v>#REF!</v>
       </c>
       <c r="C21" s="57"/>
       <c r="D21" s="47" t="s">
@@ -16719,25 +16656,25 @@
         <v>79</v>
       </c>
       <c r="X21" s="47" t="s">
+        <v>443</v>
+      </c>
+      <c r="Y21" s="47" t="s">
+        <v>443</v>
+      </c>
+      <c r="Z21" s="47" t="s">
+        <v>443</v>
+      </c>
+      <c r="AA21" s="47" t="s">
+        <v>443</v>
+      </c>
+      <c r="AB21" s="47" t="s">
         <v>444</v>
-      </c>
-      <c r="Y21" s="47" t="s">
-        <v>444</v>
-      </c>
-      <c r="Z21" s="47" t="s">
-        <v>444</v>
-      </c>
-      <c r="AA21" s="47" t="s">
-        <v>444</v>
-      </c>
-      <c r="AB21" s="47" t="s">
-        <v>445</v>
       </c>
       <c r="AC21" s="47">
         <v>66</v>
       </c>
       <c r="AD21" s="47" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="AE21" s="47">
         <v>1199</v>
@@ -16749,13 +16686,13 @@
         <v>433</v>
       </c>
       <c r="AH21" s="47" t="s">
+        <v>446</v>
+      </c>
+      <c r="AI21" s="47" t="s">
         <v>447</v>
       </c>
-      <c r="AI21" s="47" t="s">
+      <c r="AJ21" s="47" t="s">
         <v>449</v>
-      </c>
-      <c r="AJ21" s="47" t="s">
-        <v>450</v>
       </c>
       <c r="AK21" s="47">
         <v>4</v>
@@ -16764,66 +16701,66 @@
         <v>159</v>
       </c>
       <c r="AM21" s="47" t="s">
-        <v>545</v>
+        <v>533</v>
       </c>
       <c r="AN21" s="47" t="s">
+        <v>496</v>
+      </c>
+      <c r="AO21" s="47" t="s">
+        <v>501</v>
+      </c>
+      <c r="AP21" s="47" t="s">
         <v>503</v>
       </c>
-      <c r="AO21" s="47" t="s">
-        <v>509</v>
-      </c>
-      <c r="AP21" s="47" t="s">
-        <v>512</v>
-      </c>
       <c r="AQ21" s="47" t="s">
-        <v>496</v>
+        <v>490</v>
       </c>
       <c r="AR21" s="47" t="s">
-        <v>546</v>
+        <v>534</v>
       </c>
       <c r="AS21" s="47" t="s">
-        <v>524</v>
+        <v>514</v>
       </c>
       <c r="AT21" s="47" t="s">
+        <v>450</v>
+      </c>
+      <c r="AU21" s="47" t="s">
         <v>451</v>
       </c>
-      <c r="AU21" s="47" t="s">
+      <c r="AV21" s="47" t="s">
         <v>452</v>
       </c>
-      <c r="AV21" s="47" t="s">
+      <c r="AW21" s="106" t="s">
+        <v>519</v>
+      </c>
+      <c r="AX21" s="47" t="s">
+        <v>514</v>
+      </c>
+      <c r="AY21" s="47" t="s">
         <v>453</v>
       </c>
-      <c r="AW21" s="106" t="s">
-        <v>530</v>
-      </c>
-      <c r="AX21" s="47" t="s">
-        <v>524</v>
-      </c>
-      <c r="AY21" s="47" t="s">
+      <c r="AZ21" s="47" t="s">
         <v>454</v>
-      </c>
-      <c r="AZ21" s="47" t="s">
-        <v>458</v>
       </c>
       <c r="BA21" s="47"/>
       <c r="BB21" s="47"/>
       <c r="BC21" s="47" t="s">
-        <v>490</v>
+        <v>484</v>
       </c>
       <c r="BD21" s="47" t="s">
-        <v>512</v>
+        <v>503</v>
       </c>
       <c r="BE21" s="47" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="BF21" s="47" t="s">
+        <v>459</v>
+      </c>
+      <c r="BG21" s="47" t="s">
+        <v>460</v>
+      </c>
+      <c r="BH21" s="47" t="s">
         <v>461</v>
-      </c>
-      <c r="BG21" s="47" t="s">
-        <v>462</v>
-      </c>
-      <c r="BH21" s="47" t="s">
-        <v>463</v>
       </c>
       <c r="BI21" s="47"/>
       <c r="BJ21" s="47" t="str">
@@ -16939,18 +16876,18 @@
         <v>#VALUE!</v>
       </c>
       <c r="CL21" s="47" t="s">
-        <v>547</v>
+        <v>535</v>
       </c>
       <c r="CM21" s="58" t="s">
-        <v>513</v>
+        <v>504</v>
       </c>
       <c r="CN21" s="47" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="CO21" s="47"/>
       <c r="CP21" s="47"/>
       <c r="CQ21" s="47" t="s">
-        <v>492</v>
+        <v>486</v>
       </c>
       <c r="CR21" s="47"/>
       <c r="CS21" s="47" t="str">
@@ -16967,9 +16904,9 @@
     </row>
     <row r="22" spans="1:104" s="43" customFormat="1" ht="39.950000000000003" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A22" s="45"/>
-      <c r="B22" s="46">
+      <c r="B22" s="46" t="e">
         <f t="shared" si="56"/>
-        <v>4</v>
+        <v>#REF!</v>
       </c>
       <c r="C22" s="47" t="s">
         <v>264</v>
@@ -17313,9 +17250,9 @@
     </row>
     <row r="23" spans="1:104" s="42" customFormat="1" ht="44.25" customHeight="1" collapsed="1">
       <c r="A23" s="45"/>
-      <c r="B23" s="51">
+      <c r="B23" s="51" t="e">
         <f t="shared" si="56"/>
-        <v>5</v>
+        <v>#REF!</v>
       </c>
       <c r="C23" s="52">
         <v>46176</v>
@@ -17330,44 +17267,44 @@
         <v>433</v>
       </c>
       <c r="G23" s="104" t="s">
-        <v>499</v>
+        <v>492</v>
       </c>
       <c r="H23" s="51" t="s">
         <v>434</v>
       </c>
       <c r="I23" s="105" t="s">
-        <v>517</v>
+        <v>507</v>
       </c>
       <c r="J23" s="53" t="s">
-        <v>497</v>
+        <v>491</v>
       </c>
       <c r="K23" s="53" t="s">
-        <v>525</v>
+        <v>515</v>
       </c>
       <c r="L23" s="51" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="M23" s="51" t="s">
-        <v>514</v>
+        <v>505</v>
       </c>
       <c r="N23" s="51" t="s">
-        <v>554</v>
+        <v>539</v>
       </c>
       <c r="O23" s="51" t="str">
         <f>IF(COUNTIF(C25:CZ25,"FALSE")&gt;0,"NG","OK")</f>
         <v>NG</v>
       </c>
       <c r="P23" s="51" t="s">
-        <v>555</v>
+        <v>540</v>
       </c>
       <c r="Q23" s="51" t="s">
+        <v>440</v>
+      </c>
+      <c r="R23" s="51" t="s">
         <v>441</v>
       </c>
-      <c r="R23" s="51" t="s">
+      <c r="S23" s="51" t="s">
         <v>442</v>
-      </c>
-      <c r="S23" s="51" t="s">
-        <v>443</v>
       </c>
       <c r="T23" s="51" t="s">
         <v>39</v>
@@ -17382,25 +17319,25 @@
         <v>79</v>
       </c>
       <c r="X23" s="51" t="s">
+        <v>443</v>
+      </c>
+      <c r="Y23" s="51" t="s">
+        <v>443</v>
+      </c>
+      <c r="Z23" s="51" t="s">
+        <v>443</v>
+      </c>
+      <c r="AA23" s="51" t="s">
+        <v>443</v>
+      </c>
+      <c r="AB23" s="51" t="s">
         <v>444</v>
-      </c>
-      <c r="Y23" s="51" t="s">
-        <v>444</v>
-      </c>
-      <c r="Z23" s="51" t="s">
-        <v>444</v>
-      </c>
-      <c r="AA23" s="51" t="s">
-        <v>444</v>
-      </c>
-      <c r="AB23" s="51" t="s">
-        <v>445</v>
       </c>
       <c r="AC23" s="51">
         <v>66</v>
       </c>
       <c r="AD23" s="51" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="AE23" s="51">
         <v>1199</v>
@@ -17412,13 +17349,13 @@
         <v>433</v>
       </c>
       <c r="AH23" s="51" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="AI23" s="51" t="s">
         <v>448</v>
       </c>
       <c r="AJ23" s="51" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="AK23" s="51">
         <v>4</v>
@@ -17428,74 +17365,74 @@
       </c>
       <c r="AM23" s="54" t="str">
         <f>SUBSTITUTE(SUBSTITUTE(J23," ",""),"-","")</f>
-        <v>378206SATA10M6</v>
+        <v>378206SATB10M6</v>
       </c>
       <c r="AN23" s="107" t="s">
-        <v>504</v>
+        <v>497</v>
       </c>
       <c r="AO23" s="107" t="s">
-        <v>510</v>
+        <v>502</v>
       </c>
       <c r="AP23" s="51" t="s">
-        <v>512</v>
+        <v>503</v>
       </c>
       <c r="AQ23" s="54" t="str">
         <f>SUBSTITUTE(J23," ","")</f>
-        <v>37820-6SA-TA10-M6</v>
+        <v>37820-6SA-TB10-M6</v>
       </c>
       <c r="AR23" s="54" t="str">
         <f>IF(RIGHT(SUBSTITUTE(J23," ",""),4)="0-M6",LEFT(SUBSTITUTE(J23," ",""),LEN(SUBSTITUTE(J23," ",""))-4),SUBSTITUTE(J23," ",""))</f>
-        <v>37820-6SA-TA1</v>
+        <v>37820-6SA-TB1</v>
       </c>
       <c r="AS23" s="54" t="str">
         <f>K23</f>
-        <v>10SW134799</v>
+        <v>10SW134800</v>
       </c>
       <c r="AT23" s="51" t="s">
+        <v>450</v>
+      </c>
+      <c r="AU23" s="51" t="s">
         <v>451</v>
       </c>
-      <c r="AU23" s="51" t="s">
+      <c r="AV23" s="51" t="s">
         <v>452</v>
       </c>
-      <c r="AV23" s="51" t="s">
-        <v>453</v>
-      </c>
       <c r="AW23" s="107" t="s">
-        <v>531</v>
+        <v>520</v>
       </c>
       <c r="AX23" s="54" t="str">
         <f>K23</f>
-        <v>10SW134799</v>
+        <v>10SW134800</v>
       </c>
       <c r="AY23" s="51" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="AZ23" s="51" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="BA23" s="51"/>
       <c r="BB23" s="51"/>
       <c r="BC23" s="51" t="s">
-        <v>490</v>
+        <v>484</v>
       </c>
       <c r="BD23" s="54" t="str">
         <f>AP23</f>
         <v>MG1CA020-2.30</v>
       </c>
       <c r="BE23" s="51" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="BF23" s="51" t="s">
+        <v>459</v>
+      </c>
+      <c r="BG23" s="51" t="s">
+        <v>460</v>
+      </c>
+      <c r="BH23" s="51" t="s">
         <v>461</v>
       </c>
-      <c r="BG23" s="51" t="s">
-        <v>462</v>
-      </c>
-      <c r="BH23" s="51" t="s">
-        <v>463</v>
-      </c>
       <c r="BI23" s="51" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="BJ23" s="54" t="str">
         <f t="shared" si="57"/>
@@ -17543,7 +17480,7 @@
       </c>
       <c r="BU23" s="54" t="str">
         <f t="shared" si="57"/>
-        <v>A</v>
+        <v>B</v>
       </c>
       <c r="BV23" s="54" t="str">
         <f t="shared" si="57"/>
@@ -17599,7 +17536,7 @@
       </c>
       <c r="CI23" s="55" t="str">
         <f t="shared" ref="CI23:CI24" si="120">DEC2HEX(CODE(BU23),2)</f>
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="CJ23" s="55" t="str">
         <f t="shared" ref="CJ23:CJ24" si="121">DEC2HEX(CODE(BV23),2)</f>
@@ -17611,13 +17548,13 @@
       </c>
       <c r="CL23" s="54" t="str">
         <f>BX23&amp;BY23&amp;BZ23&amp;CA23&amp;CB23&amp;CC23&amp;CD23&amp;CE23&amp;CF23&amp;CG23&amp;CH23&amp;CI23&amp;CJ23&amp;CK23</f>
-        <v>33373830352D3653412D54413130</v>
+        <v>33373830352D3653412D54423130</v>
       </c>
       <c r="CM23" s="104" t="s">
-        <v>513</v>
+        <v>504</v>
       </c>
       <c r="CN23" s="51" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="CO23" s="51" t="s">
         <v>240</v>
@@ -17633,36 +17570,36 @@
       </c>
       <c r="CS23" s="54" t="str">
         <f>SUBSTITUTE(J23," ","")</f>
-        <v>37820-6SA-TA10-M6</v>
+        <v>37820-6SA-TB10-M6</v>
       </c>
       <c r="CT23" s="107" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="CU23" s="51" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="CV23" s="51" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="CW23" s="56" t="s">
         <v>240</v>
       </c>
       <c r="CX23" s="51" t="str">
         <f>AR23</f>
-        <v>37820-6SA-TA1</v>
+        <v>37820-6SA-TB1</v>
       </c>
       <c r="CY23" s="51" t="s">
-        <v>485</v>
+        <v>481</v>
       </c>
       <c r="CZ23" s="51" t="s">
-        <v>486</v>
+        <v>482</v>
       </c>
     </row>
     <row r="24" spans="1:104" s="42" customFormat="1" ht="44.25" hidden="1" customHeight="1" outlineLevel="1" collapsed="1">
       <c r="A24" s="45"/>
-      <c r="B24" s="47">
+      <c r="B24" s="47" t="e">
         <f t="shared" si="56"/>
-        <v>5</v>
+        <v>#REF!</v>
       </c>
       <c r="C24" s="57"/>
       <c r="D24" s="47" t="s">
@@ -17696,25 +17633,25 @@
         <v>79</v>
       </c>
       <c r="X24" s="47" t="s">
+        <v>443</v>
+      </c>
+      <c r="Y24" s="47" t="s">
+        <v>443</v>
+      </c>
+      <c r="Z24" s="47" t="s">
+        <v>443</v>
+      </c>
+      <c r="AA24" s="47" t="s">
+        <v>443</v>
+      </c>
+      <c r="AB24" s="47" t="s">
         <v>444</v>
-      </c>
-      <c r="Y24" s="47" t="s">
-        <v>444</v>
-      </c>
-      <c r="Z24" s="47" t="s">
-        <v>444</v>
-      </c>
-      <c r="AA24" s="47" t="s">
-        <v>444</v>
-      </c>
-      <c r="AB24" s="47" t="s">
-        <v>445</v>
       </c>
       <c r="AC24" s="47">
         <v>66</v>
       </c>
       <c r="AD24" s="47" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="AE24" s="47">
         <v>1199</v>
@@ -17726,13 +17663,13 @@
         <v>433</v>
       </c>
       <c r="AH24" s="47" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="AI24" s="47" t="s">
         <v>448</v>
       </c>
       <c r="AJ24" s="47" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="AK24" s="47">
         <v>4</v>
@@ -17741,66 +17678,66 @@
         <v>159</v>
       </c>
       <c r="AM24" s="47" t="s">
-        <v>548</v>
+        <v>536</v>
       </c>
       <c r="AN24" s="47" t="s">
-        <v>504</v>
+        <v>497</v>
       </c>
       <c r="AO24" s="47" t="s">
-        <v>510</v>
+        <v>502</v>
       </c>
       <c r="AP24" s="47" t="s">
-        <v>512</v>
+        <v>503</v>
       </c>
       <c r="AQ24" s="47" t="s">
-        <v>497</v>
+        <v>491</v>
       </c>
       <c r="AR24" s="47" t="s">
-        <v>549</v>
+        <v>537</v>
       </c>
       <c r="AS24" s="47" t="s">
-        <v>525</v>
+        <v>515</v>
       </c>
       <c r="AT24" s="47" t="s">
+        <v>450</v>
+      </c>
+      <c r="AU24" s="47" t="s">
         <v>451</v>
       </c>
-      <c r="AU24" s="47" t="s">
+      <c r="AV24" s="47" t="s">
         <v>452</v>
       </c>
-      <c r="AV24" s="47" t="s">
+      <c r="AW24" s="106" t="s">
+        <v>520</v>
+      </c>
+      <c r="AX24" s="47" t="s">
+        <v>515</v>
+      </c>
+      <c r="AY24" s="47" t="s">
         <v>453</v>
       </c>
-      <c r="AW24" s="106" t="s">
-        <v>531</v>
-      </c>
-      <c r="AX24" s="47" t="s">
-        <v>525</v>
-      </c>
-      <c r="AY24" s="47" t="s">
-        <v>454</v>
-      </c>
       <c r="AZ24" s="47" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="BA24" s="47"/>
       <c r="BB24" s="47"/>
       <c r="BC24" s="47" t="s">
-        <v>490</v>
+        <v>484</v>
       </c>
       <c r="BD24" s="47" t="s">
-        <v>512</v>
+        <v>503</v>
       </c>
       <c r="BE24" s="47" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="BF24" s="47" t="s">
+        <v>459</v>
+      </c>
+      <c r="BG24" s="47" t="s">
+        <v>460</v>
+      </c>
+      <c r="BH24" s="47" t="s">
         <v>461</v>
-      </c>
-      <c r="BG24" s="47" t="s">
-        <v>462</v>
-      </c>
-      <c r="BH24" s="47" t="s">
-        <v>463</v>
       </c>
       <c r="BI24" s="47"/>
       <c r="BJ24" s="47" t="str">
@@ -17916,18 +17853,18 @@
         <v>#VALUE!</v>
       </c>
       <c r="CL24" s="47" t="s">
-        <v>550</v>
+        <v>538</v>
       </c>
       <c r="CM24" s="58" t="s">
-        <v>513</v>
+        <v>504</v>
       </c>
       <c r="CN24" s="47" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="CO24" s="47"/>
       <c r="CP24" s="47"/>
       <c r="CQ24" s="47" t="s">
-        <v>492</v>
+        <v>486</v>
       </c>
       <c r="CR24" s="47"/>
       <c r="CS24" s="47" t="str">
@@ -17944,9 +17881,9 @@
     </row>
     <row r="25" spans="1:104" s="43" customFormat="1" ht="39.950000000000003" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A25" s="45"/>
-      <c r="B25" s="46">
+      <c r="B25" s="46" t="e">
         <f t="shared" si="56"/>
-        <v>5</v>
+        <v>#REF!</v>
       </c>
       <c r="C25" s="47" t="s">
         <v>264</v>
@@ -17975,7 +17912,9 @@
       <c r="K25" s="47" t="s">
         <v>264</v>
       </c>
-      <c r="L25" s="47"/>
+      <c r="L25" s="47" t="s">
+        <v>264</v>
+      </c>
       <c r="M25" s="47" t="s">
         <v>264</v>
       </c>
@@ -18290,61 +18229,43 @@
     </row>
     <row r="26" spans="1:104" s="42" customFormat="1" ht="44.25" customHeight="1" collapsed="1">
       <c r="A26" s="45"/>
-      <c r="B26" s="51">
+      <c r="B26" s="51" t="e">
         <f t="shared" si="56"/>
-        <v>6</v>
+        <v>#REF!</v>
       </c>
       <c r="C26" s="52">
-        <v>46176</v>
+        <v>46324.656747685185</v>
       </c>
       <c r="D26" s="51" t="s">
         <v>254</v>
       </c>
-      <c r="E26" s="51" t="s">
-        <v>432</v>
-      </c>
-      <c r="F26" s="51" t="s">
-        <v>433</v>
-      </c>
-      <c r="G26" s="104" t="s">
-        <v>499</v>
-      </c>
+      <c r="E26" s="51"/>
+      <c r="F26" s="51"/>
+      <c r="G26" s="104"/>
       <c r="H26" s="51" t="s">
-        <v>434</v>
-      </c>
-      <c r="I26" s="105" t="s">
-        <v>516</v>
-      </c>
+        <v>542</v>
+      </c>
+      <c r="I26" s="105"/>
       <c r="J26" s="53" t="s">
-        <v>498</v>
-      </c>
-      <c r="K26" s="53" t="s">
-        <v>526</v>
-      </c>
-      <c r="L26" s="51" t="s">
-        <v>437</v>
-      </c>
-      <c r="M26" s="51" t="s">
-        <v>514</v>
-      </c>
-      <c r="N26" s="51" t="s">
-        <v>554</v>
-      </c>
+        <v>541</v>
+      </c>
+      <c r="K26" s="53"/>
+      <c r="L26" s="51"/>
+      <c r="M26" s="51"/>
+      <c r="N26" s="51"/>
       <c r="O26" s="51" t="str">
         <f>IF(COUNTIF(C28:CZ28,"FALSE")&gt;0,"NG","OK")</f>
         <v>NG</v>
       </c>
-      <c r="P26" s="51" t="s">
-        <v>555</v>
-      </c>
+      <c r="P26" s="51"/>
       <c r="Q26" s="51" t="s">
+        <v>440</v>
+      </c>
+      <c r="R26" s="51" t="s">
         <v>441</v>
       </c>
-      <c r="R26" s="51" t="s">
-        <v>442</v>
-      </c>
       <c r="S26" s="51" t="s">
-        <v>443</v>
+        <v>543</v>
       </c>
       <c r="T26" s="51" t="s">
         <v>39</v>
@@ -18359,43 +18280,43 @@
         <v>79</v>
       </c>
       <c r="X26" s="51" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="Y26" s="51" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="Z26" s="51" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="AA26" s="51" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="AB26" s="51" t="s">
+        <v>544</v>
+      </c>
+      <c r="AC26" s="51">
+        <v>93</v>
+      </c>
+      <c r="AD26" s="51" t="s">
         <v>445</v>
       </c>
-      <c r="AC26" s="51">
-        <v>66</v>
-      </c>
-      <c r="AD26" s="51" t="s">
-        <v>446</v>
-      </c>
       <c r="AE26" s="51">
-        <v>1199</v>
+        <v>1.5</v>
       </c>
       <c r="AF26" s="51">
         <v>2028</v>
       </c>
       <c r="AG26" s="51" t="s">
-        <v>433</v>
+        <v>545</v>
       </c>
       <c r="AH26" s="51" t="s">
-        <v>447</v>
+        <v>37</v>
       </c>
       <c r="AI26" s="51" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="AJ26" s="51" t="s">
-        <v>450</v>
+        <v>546</v>
       </c>
       <c r="AK26" s="51">
         <v>4</v>
@@ -18405,74 +18326,66 @@
       </c>
       <c r="AM26" s="54" t="str">
         <f>SUBSTITUTE(SUBSTITUTE(J26," ",""),"-","")</f>
-        <v>378206SATB10M6</v>
+        <v>378206WZM610M6</v>
       </c>
       <c r="AN26" s="107" t="s">
-        <v>505</v>
+        <v>547</v>
       </c>
       <c r="AO26" s="107" t="s">
-        <v>511</v>
+        <v>548</v>
       </c>
       <c r="AP26" s="51" t="s">
-        <v>512</v>
+        <v>543</v>
       </c>
       <c r="AQ26" s="54" t="str">
         <f>SUBSTITUTE(J26," ","")</f>
-        <v>37820-6SA-TB10-M6</v>
+        <v>37820-6WZ-M610-M6</v>
       </c>
       <c r="AR26" s="54" t="str">
         <f>IF(RIGHT(SUBSTITUTE(J26," ",""),4)="0-M6",LEFT(SUBSTITUTE(J26," ",""),LEN(SUBSTITUTE(J26," ",""))-4),SUBSTITUTE(J26," ",""))</f>
-        <v>37820-6SA-TB1</v>
-      </c>
-      <c r="AS26" s="54" t="str">
+        <v>37820-6WZ-M61</v>
+      </c>
+      <c r="AS26" s="54">
         <f>K26</f>
-        <v>10SW134800</v>
-      </c>
-      <c r="AT26" s="51" t="s">
+        <v>0</v>
+      </c>
+      <c r="AT26" s="51"/>
+      <c r="AU26" s="51" t="s">
         <v>451</v>
       </c>
-      <c r="AU26" s="51" t="s">
+      <c r="AV26" s="51" t="s">
         <v>452</v>
       </c>
-      <c r="AV26" s="51" t="s">
-        <v>453</v>
-      </c>
-      <c r="AW26" s="107" t="s">
-        <v>532</v>
-      </c>
-      <c r="AX26" s="54" t="str">
+      <c r="AW26" s="107"/>
+      <c r="AX26" s="54">
         <f>K26</f>
-        <v>10SW134800</v>
-      </c>
-      <c r="AY26" s="51" t="s">
-        <v>454</v>
-      </c>
-      <c r="AZ26" s="51" t="s">
-        <v>457</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AY26" s="51"/>
+      <c r="AZ26" s="51"/>
       <c r="BA26" s="51"/>
       <c r="BB26" s="51"/>
       <c r="BC26" s="51" t="s">
-        <v>490</v>
+        <v>549</v>
       </c>
       <c r="BD26" s="54" t="str">
         <f>AP26</f>
-        <v>MG1CA020-2.30</v>
+        <v>MG1CS022</v>
       </c>
       <c r="BE26" s="51" t="s">
-        <v>445</v>
+        <v>544</v>
       </c>
       <c r="BF26" s="51" t="s">
-        <v>461</v>
+        <v>550</v>
       </c>
       <c r="BG26" s="51" t="s">
-        <v>462</v>
+        <v>551</v>
       </c>
       <c r="BH26" s="51" t="s">
-        <v>463</v>
+        <v>552</v>
       </c>
       <c r="BI26" s="51" t="s">
-        <v>469</v>
+        <v>553</v>
       </c>
       <c r="BJ26" s="54" t="str">
         <f t="shared" si="57"/>
@@ -18504,11 +18417,11 @@
       </c>
       <c r="BQ26" s="54" t="str">
         <f t="shared" si="57"/>
-        <v>S</v>
+        <v>W</v>
       </c>
       <c r="BR26" s="54" t="str">
         <f t="shared" si="57"/>
-        <v>A</v>
+        <v>Z</v>
       </c>
       <c r="BS26" s="54" t="str">
         <f t="shared" si="57"/>
@@ -18516,11 +18429,11 @@
       </c>
       <c r="BT26" s="54" t="str">
         <f t="shared" si="57"/>
-        <v>T</v>
+        <v>M</v>
       </c>
       <c r="BU26" s="54" t="str">
         <f t="shared" si="57"/>
-        <v>B</v>
+        <v>6</v>
       </c>
       <c r="BV26" s="54" t="str">
         <f t="shared" si="57"/>
@@ -18560,11 +18473,11 @@
       </c>
       <c r="CE26" s="55" t="str">
         <f t="shared" ref="CE26:CE27" si="133">DEC2HEX(CODE(BQ26),2)</f>
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="CF26" s="55" t="str">
         <f t="shared" ref="CF26:CF27" si="134">DEC2HEX(CODE(BR26),2)</f>
-        <v>41</v>
+        <v>5A</v>
       </c>
       <c r="CG26" s="55" t="str">
         <f t="shared" ref="CG26:CG27" si="135">DEC2HEX(CODE(BS26),2)</f>
@@ -18572,11 +18485,11 @@
       </c>
       <c r="CH26" s="55" t="str">
         <f t="shared" ref="CH26:CH27" si="136">DEC2HEX(CODE(BT26),2)</f>
-        <v>54</v>
+        <v>4D</v>
       </c>
       <c r="CI26" s="55" t="str">
         <f t="shared" ref="CI26:CI27" si="137">DEC2HEX(CODE(BU26),2)</f>
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="CJ26" s="55" t="str">
         <f t="shared" ref="CJ26:CJ27" si="138">DEC2HEX(CODE(BV26),2)</f>
@@ -18588,58 +18501,54 @@
       </c>
       <c r="CL26" s="54" t="str">
         <f>BX26&amp;BY26&amp;BZ26&amp;CA26&amp;CB26&amp;CC26&amp;CD26&amp;CE26&amp;CF26&amp;CG26&amp;CH26&amp;CI26&amp;CJ26&amp;CK26</f>
-        <v>33373830352D3653412D54423130</v>
+        <v>33373830352D36575A2D4D363130</v>
       </c>
       <c r="CM26" s="104" t="s">
-        <v>513</v>
+        <v>504</v>
       </c>
       <c r="CN26" s="51" t="s">
-        <v>470</v>
+        <v>554</v>
       </c>
       <c r="CO26" s="51" t="s">
-        <v>240</v>
+        <v>308</v>
       </c>
       <c r="CP26" s="51" t="s">
-        <v>240</v>
-      </c>
-      <c r="CQ26" s="51" t="s">
-        <v>240</v>
-      </c>
-      <c r="CR26" s="56" t="s">
-        <v>240</v>
-      </c>
+        <v>308</v>
+      </c>
+      <c r="CQ26" s="107" t="s">
+        <v>555</v>
+      </c>
+      <c r="CR26" s="56"/>
       <c r="CS26" s="54" t="str">
         <f>SUBSTITUTE(J26," ","")</f>
-        <v>37820-6SA-TB10-M6</v>
+        <v>37820-6WZ-M610-M6</v>
       </c>
       <c r="CT26" s="107" t="s">
-        <v>476</v>
+        <v>556</v>
       </c>
       <c r="CU26" s="51" t="s">
-        <v>469</v>
+        <v>553</v>
       </c>
       <c r="CV26" s="51" t="s">
-        <v>469</v>
-      </c>
-      <c r="CW26" s="56" t="s">
-        <v>240</v>
-      </c>
+        <v>553</v>
+      </c>
+      <c r="CW26" s="56"/>
       <c r="CX26" s="51" t="str">
         <f>AR26</f>
-        <v>37820-6SA-TB1</v>
+        <v>37820-6WZ-M61</v>
       </c>
       <c r="CY26" s="51" t="s">
-        <v>487</v>
+        <v>557</v>
       </c>
       <c r="CZ26" s="51" t="s">
-        <v>488</v>
+        <v>557</v>
       </c>
     </row>
     <row r="27" spans="1:104" s="42" customFormat="1" ht="44.25" hidden="1" customHeight="1" outlineLevel="1" collapsed="1">
       <c r="A27" s="45"/>
-      <c r="B27" s="47">
+      <c r="B27" s="47" t="e">
         <f t="shared" si="56"/>
-        <v>6</v>
+        <v>#REF!</v>
       </c>
       <c r="C27" s="57"/>
       <c r="D27" s="47" t="s">
@@ -18660,180 +18569,102 @@
       <c r="Q27" s="47"/>
       <c r="R27" s="47"/>
       <c r="S27" s="47"/>
-      <c r="T27" s="47" t="s">
-        <v>39</v>
-      </c>
-      <c r="U27" s="47" t="s">
-        <v>28</v>
-      </c>
-      <c r="V27" s="47" t="s">
-        <v>38</v>
-      </c>
-      <c r="W27" s="47" t="s">
-        <v>79</v>
-      </c>
-      <c r="X27" s="47" t="s">
-        <v>444</v>
-      </c>
-      <c r="Y27" s="47" t="s">
-        <v>444</v>
-      </c>
-      <c r="Z27" s="47" t="s">
-        <v>444</v>
-      </c>
-      <c r="AA27" s="47" t="s">
-        <v>444</v>
-      </c>
-      <c r="AB27" s="47" t="s">
-        <v>445</v>
-      </c>
-      <c r="AC27" s="47">
-        <v>66</v>
-      </c>
-      <c r="AD27" s="47" t="s">
-        <v>446</v>
-      </c>
-      <c r="AE27" s="47">
-        <v>1199</v>
-      </c>
-      <c r="AF27" s="47">
-        <v>2028</v>
-      </c>
-      <c r="AG27" s="47" t="s">
-        <v>433</v>
-      </c>
-      <c r="AH27" s="47" t="s">
-        <v>447</v>
-      </c>
-      <c r="AI27" s="47" t="s">
-        <v>449</v>
-      </c>
-      <c r="AJ27" s="47" t="s">
-        <v>450</v>
-      </c>
-      <c r="AK27" s="47">
-        <v>4</v>
-      </c>
-      <c r="AL27" s="47">
-        <v>159</v>
-      </c>
-      <c r="AM27" s="47" t="s">
-        <v>551</v>
-      </c>
-      <c r="AN27" s="47" t="s">
-        <v>505</v>
-      </c>
-      <c r="AO27" s="47" t="s">
-        <v>511</v>
-      </c>
-      <c r="AP27" s="47" t="s">
-        <v>512</v>
-      </c>
-      <c r="AQ27" s="47" t="s">
-        <v>498</v>
-      </c>
-      <c r="AR27" s="47" t="s">
-        <v>552</v>
-      </c>
-      <c r="AS27" s="47" t="s">
-        <v>526</v>
-      </c>
-      <c r="AT27" s="47" t="s">
-        <v>451</v>
-      </c>
-      <c r="AU27" s="47" t="s">
-        <v>452</v>
-      </c>
-      <c r="AV27" s="47" t="s">
-        <v>453</v>
-      </c>
-      <c r="AW27" s="106" t="s">
-        <v>532</v>
-      </c>
-      <c r="AX27" s="47" t="s">
-        <v>526</v>
-      </c>
-      <c r="AY27" s="47" t="s">
-        <v>454</v>
-      </c>
-      <c r="AZ27" s="47" t="s">
-        <v>457</v>
-      </c>
+      <c r="T27" s="47"/>
+      <c r="U27" s="47"/>
+      <c r="V27" s="47"/>
+      <c r="W27" s="47"/>
+      <c r="X27" s="47"/>
+      <c r="Y27" s="47"/>
+      <c r="Z27" s="47"/>
+      <c r="AA27" s="47"/>
+      <c r="AB27" s="47"/>
+      <c r="AC27" s="47"/>
+      <c r="AD27" s="47"/>
+      <c r="AE27" s="47"/>
+      <c r="AF27" s="47"/>
+      <c r="AG27" s="47"/>
+      <c r="AH27" s="47"/>
+      <c r="AI27" s="47"/>
+      <c r="AJ27" s="47"/>
+      <c r="AK27" s="47"/>
+      <c r="AL27" s="47"/>
+      <c r="AM27" s="47"/>
+      <c r="AN27" s="47"/>
+      <c r="AO27" s="47"/>
+      <c r="AP27" s="47"/>
+      <c r="AQ27" s="47"/>
+      <c r="AR27" s="47"/>
+      <c r="AS27" s="47"/>
+      <c r="AT27" s="47"/>
+      <c r="AU27" s="47"/>
+      <c r="AV27" s="47"/>
+      <c r="AW27" s="106"/>
+      <c r="AX27" s="47"/>
+      <c r="AY27" s="47"/>
+      <c r="AZ27" s="47"/>
       <c r="BA27" s="47"/>
       <c r="BB27" s="47"/>
-      <c r="BC27" s="47" t="s">
-        <v>490</v>
-      </c>
-      <c r="BD27" s="47" t="s">
-        <v>512</v>
-      </c>
-      <c r="BE27" s="47" t="s">
-        <v>445</v>
-      </c>
-      <c r="BF27" s="47" t="s">
-        <v>461</v>
-      </c>
-      <c r="BG27" s="47" t="s">
-        <v>462</v>
-      </c>
-      <c r="BH27" s="47" t="s">
-        <v>463</v>
-      </c>
+      <c r="BC27" s="47"/>
+      <c r="BD27" s="47"/>
+      <c r="BE27" s="47"/>
+      <c r="BF27" s="47"/>
+      <c r="BG27" s="47"/>
+      <c r="BH27" s="47"/>
       <c r="BI27" s="47"/>
       <c r="BJ27" s="47" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" ref="BJ27:BW27" si="140">MID($BI27,BJ$6,1)</f>
         <v/>
       </c>
       <c r="BK27" s="47" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="140"/>
         <v/>
       </c>
       <c r="BL27" s="47" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="140"/>
         <v/>
       </c>
       <c r="BM27" s="47" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="140"/>
         <v/>
       </c>
       <c r="BN27" s="47" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="140"/>
         <v/>
       </c>
       <c r="BO27" s="47" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="140"/>
         <v/>
       </c>
       <c r="BP27" s="47" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="140"/>
         <v/>
       </c>
       <c r="BQ27" s="47" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="140"/>
         <v/>
       </c>
       <c r="BR27" s="47" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="140"/>
         <v/>
       </c>
       <c r="BS27" s="47" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="140"/>
         <v/>
       </c>
       <c r="BT27" s="47" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="140"/>
         <v/>
       </c>
       <c r="BU27" s="47" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="140"/>
         <v/>
       </c>
       <c r="BV27" s="47" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="140"/>
         <v/>
       </c>
       <c r="BW27" s="47" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="140"/>
         <v/>
       </c>
       <c r="BX27" s="47" t="e">
@@ -18892,20 +18723,12 @@
         <f t="shared" si="139"/>
         <v>#VALUE!</v>
       </c>
-      <c r="CL27" s="47" t="s">
-        <v>553</v>
-      </c>
-      <c r="CM27" s="58" t="s">
-        <v>513</v>
-      </c>
-      <c r="CN27" s="47" t="s">
-        <v>470</v>
-      </c>
+      <c r="CL27" s="47"/>
+      <c r="CM27" s="58"/>
+      <c r="CN27" s="47"/>
       <c r="CO27" s="47"/>
       <c r="CP27" s="47"/>
-      <c r="CQ27" s="47" t="s">
-        <v>492</v>
-      </c>
+      <c r="CQ27" s="47"/>
       <c r="CR27" s="47"/>
       <c r="CS27" s="47" t="str">
         <f>SUBSTITUTE(J27," ","")</f>
@@ -18921,9 +18744,9 @@
     </row>
     <row r="28" spans="1:104" s="43" customFormat="1" ht="39.950000000000003" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A28" s="45"/>
-      <c r="B28" s="46">
+      <c r="B28" s="46" t="e">
         <f t="shared" si="56"/>
-        <v>6</v>
+        <v>#REF!</v>
       </c>
       <c r="C28" s="47" t="s">
         <v>264</v>
@@ -18970,134 +18793,134 @@
       <c r="S28" s="47"/>
       <c r="T28" s="47" t="b">
         <f>T26=T27</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U28" s="47" t="b">
-        <f t="shared" ref="U28:AZ28" si="140">U26=U27</f>
-        <v>1</v>
+        <f t="shared" ref="U28:AZ28" si="141">U26=U27</f>
+        <v>0</v>
       </c>
       <c r="V28" s="47" t="b">
-        <f t="shared" si="140"/>
-        <v>1</v>
+        <f t="shared" si="141"/>
+        <v>0</v>
       </c>
       <c r="W28" s="47" t="b">
-        <f t="shared" si="140"/>
-        <v>1</v>
+        <f t="shared" si="141"/>
+        <v>0</v>
       </c>
       <c r="X28" s="47" t="b">
-        <f t="shared" si="140"/>
-        <v>1</v>
+        <f t="shared" si="141"/>
+        <v>0</v>
       </c>
       <c r="Y28" s="47" t="b">
-        <f t="shared" si="140"/>
-        <v>1</v>
+        <f t="shared" si="141"/>
+        <v>0</v>
       </c>
       <c r="Z28" s="47" t="b">
-        <f t="shared" si="140"/>
-        <v>1</v>
+        <f t="shared" si="141"/>
+        <v>0</v>
       </c>
       <c r="AA28" s="47" t="b">
-        <f t="shared" si="140"/>
-        <v>1</v>
+        <f t="shared" si="141"/>
+        <v>0</v>
       </c>
       <c r="AB28" s="47" t="b">
-        <f t="shared" si="140"/>
-        <v>1</v>
+        <f t="shared" si="141"/>
+        <v>0</v>
       </c>
       <c r="AC28" s="47" t="b">
-        <f t="shared" si="140"/>
-        <v>1</v>
+        <f t="shared" si="141"/>
+        <v>0</v>
       </c>
       <c r="AD28" s="47" t="b">
-        <f t="shared" si="140"/>
-        <v>1</v>
+        <f t="shared" si="141"/>
+        <v>0</v>
       </c>
       <c r="AE28" s="47" t="b">
-        <f t="shared" si="140"/>
-        <v>1</v>
+        <f t="shared" si="141"/>
+        <v>0</v>
       </c>
       <c r="AF28" s="47" t="b">
-        <f t="shared" si="140"/>
-        <v>1</v>
+        <f t="shared" si="141"/>
+        <v>0</v>
       </c>
       <c r="AG28" s="47" t="b">
-        <f t="shared" si="140"/>
-        <v>1</v>
+        <f t="shared" si="141"/>
+        <v>0</v>
       </c>
       <c r="AH28" s="47" t="b">
-        <f t="shared" si="140"/>
-        <v>1</v>
+        <f t="shared" si="141"/>
+        <v>0</v>
       </c>
       <c r="AI28" s="47" t="b">
-        <f t="shared" si="140"/>
-        <v>1</v>
+        <f t="shared" si="141"/>
+        <v>0</v>
       </c>
       <c r="AJ28" s="47" t="b">
-        <f t="shared" si="140"/>
-        <v>1</v>
+        <f t="shared" si="141"/>
+        <v>0</v>
       </c>
       <c r="AK28" s="47" t="b">
-        <f t="shared" si="140"/>
-        <v>1</v>
+        <f t="shared" si="141"/>
+        <v>0</v>
       </c>
       <c r="AL28" s="47" t="b">
-        <f t="shared" si="140"/>
-        <v>1</v>
+        <f t="shared" si="141"/>
+        <v>0</v>
       </c>
       <c r="AM28" s="47" t="b">
-        <f t="shared" si="140"/>
-        <v>1</v>
+        <f t="shared" si="141"/>
+        <v>0</v>
       </c>
       <c r="AN28" s="47" t="b">
-        <f t="shared" si="140"/>
-        <v>1</v>
+        <f t="shared" si="141"/>
+        <v>0</v>
       </c>
       <c r="AO28" s="47" t="b">
-        <f t="shared" si="140"/>
-        <v>1</v>
+        <f t="shared" si="141"/>
+        <v>0</v>
       </c>
       <c r="AP28" s="47" t="b">
-        <f t="shared" si="140"/>
-        <v>1</v>
+        <f t="shared" si="141"/>
+        <v>0</v>
       </c>
       <c r="AQ28" s="47" t="b">
-        <f t="shared" si="140"/>
-        <v>1</v>
+        <f t="shared" si="141"/>
+        <v>0</v>
       </c>
       <c r="AR28" s="47" t="b">
-        <f t="shared" si="140"/>
-        <v>1</v>
+        <f t="shared" si="141"/>
+        <v>0</v>
       </c>
       <c r="AS28" s="47" t="b">
-        <f t="shared" si="140"/>
+        <f t="shared" si="141"/>
         <v>1</v>
       </c>
       <c r="AT28" s="47" t="b">
-        <f t="shared" si="140"/>
+        <f t="shared" si="141"/>
         <v>1</v>
       </c>
       <c r="AU28" s="47" t="b">
-        <f t="shared" si="140"/>
-        <v>1</v>
+        <f t="shared" si="141"/>
+        <v>0</v>
       </c>
       <c r="AV28" s="47" t="b">
-        <f t="shared" si="140"/>
-        <v>1</v>
+        <f t="shared" si="141"/>
+        <v>0</v>
       </c>
       <c r="AW28" s="47" t="b">
-        <f t="shared" si="140"/>
+        <f t="shared" si="141"/>
         <v>1</v>
       </c>
       <c r="AX28" s="47" t="b">
-        <f t="shared" si="140"/>
+        <f t="shared" si="141"/>
         <v>1</v>
       </c>
       <c r="AY28" s="47" t="b">
-        <f t="shared" si="140"/>
+        <f t="shared" si="141"/>
         <v>1</v>
       </c>
       <c r="AZ28" s="47" t="b">
-        <f t="shared" si="140"/>
+        <f t="shared" si="141"/>
         <v>1</v>
       </c>
       <c r="BA28" s="47" t="s">
@@ -19107,28 +18930,28 @@
         <v>264</v>
       </c>
       <c r="BC28" s="47" t="b">
-        <f t="shared" ref="BC28:BH28" si="141">BC26=BC27</f>
-        <v>1</v>
+        <f t="shared" ref="BC28:BH28" si="142">BC26=BC27</f>
+        <v>0</v>
       </c>
       <c r="BD28" s="47" t="b">
-        <f t="shared" si="141"/>
-        <v>1</v>
+        <f t="shared" si="142"/>
+        <v>0</v>
       </c>
       <c r="BE28" s="47" t="b">
-        <f t="shared" si="141"/>
-        <v>1</v>
+        <f t="shared" si="142"/>
+        <v>0</v>
       </c>
       <c r="BF28" s="47" t="b">
-        <f t="shared" si="141"/>
-        <v>1</v>
+        <f t="shared" si="142"/>
+        <v>0</v>
       </c>
       <c r="BG28" s="47" t="b">
-        <f t="shared" si="141"/>
-        <v>1</v>
+        <f t="shared" si="142"/>
+        <v>0</v>
       </c>
       <c r="BH28" s="47" t="b">
-        <f t="shared" si="141"/>
-        <v>1</v>
+        <f t="shared" si="142"/>
+        <v>0</v>
       </c>
       <c r="BI28" s="47" t="s">
         <v>264</v>
@@ -19219,15 +19042,15 @@
       </c>
       <c r="CL28" s="47" t="b">
         <f>CL26=CL27</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CM28" s="47" t="b">
-        <f t="shared" ref="CM28:CN28" si="142">CM26=CM27</f>
-        <v>1</v>
+        <f t="shared" ref="CM28:CN28" si="143">CM26=CM27</f>
+        <v>0</v>
       </c>
       <c r="CN28" s="47" t="b">
-        <f t="shared" si="142"/>
-        <v>1</v>
+        <f t="shared" si="143"/>
+        <v>0</v>
       </c>
       <c r="CO28" s="47" t="s">
         <v>264</v>
@@ -19236,7 +19059,7 @@
         <v>264</v>
       </c>
       <c r="CQ28" s="47" t="b">
-        <f t="shared" ref="CQ28" si="143">CQ26=CQ27</f>
+        <f t="shared" ref="CQ28" si="144">CQ26=CQ27</f>
         <v>0</v>
       </c>
       <c r="CR28" s="47" t="s">
@@ -19264,1737 +19087,17 @@
         <v>264</v>
       </c>
       <c r="CZ28" s="47" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="29" spans="1:104" s="42" customFormat="1" ht="44.25" customHeight="1" collapsed="1">
-      <c r="A29" s="45"/>
-      <c r="B29" s="51">
-        <f t="shared" si="56"/>
-        <v>7</v>
-      </c>
-      <c r="C29" s="52">
-        <v>46324.656747685185</v>
-      </c>
-      <c r="D29" s="51" t="s">
-        <v>254</v>
-      </c>
-      <c r="E29" s="51"/>
-      <c r="F29" s="51"/>
-      <c r="G29" s="104"/>
-      <c r="H29" s="51" t="s">
-        <v>557</v>
-      </c>
-      <c r="I29" s="105"/>
-      <c r="J29" s="53" t="s">
-        <v>556</v>
-      </c>
-      <c r="K29" s="53"/>
-      <c r="L29" s="51"/>
-      <c r="M29" s="51"/>
-      <c r="N29" s="51"/>
-      <c r="O29" s="51" t="str">
-        <f>IF(COUNTIF(C31:CZ31,"FALSE")&gt;0,"NG","OK")</f>
-        <v>NG</v>
-      </c>
-      <c r="P29" s="51"/>
-      <c r="Q29" s="51" t="s">
-        <v>441</v>
-      </c>
-      <c r="R29" s="51" t="s">
-        <v>442</v>
-      </c>
-      <c r="S29" s="51" t="s">
-        <v>558</v>
-      </c>
-      <c r="T29" s="51" t="s">
-        <v>39</v>
-      </c>
-      <c r="U29" s="51" t="s">
-        <v>28</v>
-      </c>
-      <c r="V29" s="51" t="s">
-        <v>38</v>
-      </c>
-      <c r="W29" s="51" t="s">
-        <v>79</v>
-      </c>
-      <c r="X29" s="51" t="s">
-        <v>444</v>
-      </c>
-      <c r="Y29" s="51" t="s">
-        <v>444</v>
-      </c>
-      <c r="Z29" s="51" t="s">
-        <v>444</v>
-      </c>
-      <c r="AA29" s="51" t="s">
-        <v>444</v>
-      </c>
-      <c r="AB29" s="51" t="s">
-        <v>559</v>
-      </c>
-      <c r="AC29" s="51">
-        <v>93</v>
-      </c>
-      <c r="AD29" s="51" t="s">
-        <v>446</v>
-      </c>
-      <c r="AE29" s="51">
-        <v>1.5</v>
-      </c>
-      <c r="AF29" s="51">
-        <v>2028</v>
-      </c>
-      <c r="AG29" s="51" t="s">
-        <v>560</v>
-      </c>
-      <c r="AH29" s="51" t="s">
-        <v>37</v>
-      </c>
-      <c r="AI29" s="51" t="s">
-        <v>449</v>
-      </c>
-      <c r="AJ29" s="51" t="s">
-        <v>561</v>
-      </c>
-      <c r="AK29" s="51">
-        <v>4</v>
-      </c>
-      <c r="AL29" s="51">
-        <v>159</v>
-      </c>
-      <c r="AM29" s="54" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(J29," ",""),"-","")</f>
-        <v>378206WZM610M6</v>
-      </c>
-      <c r="AN29" s="107" t="s">
-        <v>562</v>
-      </c>
-      <c r="AO29" s="107" t="s">
-        <v>563</v>
-      </c>
-      <c r="AP29" s="51" t="s">
-        <v>558</v>
-      </c>
-      <c r="AQ29" s="54" t="str">
-        <f>SUBSTITUTE(J29," ","")</f>
-        <v>37820-6WZ-M610-M6</v>
-      </c>
-      <c r="AR29" s="54" t="str">
-        <f>IF(RIGHT(SUBSTITUTE(J29," ",""),4)="0-M6",LEFT(SUBSTITUTE(J29," ",""),LEN(SUBSTITUTE(J29," ",""))-4),SUBSTITUTE(J29," ",""))</f>
-        <v>37820-6WZ-M61</v>
-      </c>
-      <c r="AS29" s="54">
-        <f>K29</f>
-        <v>0</v>
-      </c>
-      <c r="AT29" s="51"/>
-      <c r="AU29" s="51" t="s">
-        <v>452</v>
-      </c>
-      <c r="AV29" s="51" t="s">
-        <v>453</v>
-      </c>
-      <c r="AW29" s="107"/>
-      <c r="AX29" s="54">
-        <f>K29</f>
-        <v>0</v>
-      </c>
-      <c r="AY29" s="51"/>
-      <c r="AZ29" s="51"/>
-      <c r="BA29" s="51"/>
-      <c r="BB29" s="51"/>
-      <c r="BC29" s="51" t="s">
-        <v>564</v>
-      </c>
-      <c r="BD29" s="54" t="str">
-        <f>AP29</f>
-        <v>MG1CS022</v>
-      </c>
-      <c r="BE29" s="51" t="s">
-        <v>559</v>
-      </c>
-      <c r="BF29" s="51" t="s">
-        <v>565</v>
-      </c>
-      <c r="BG29" s="51" t="s">
-        <v>566</v>
-      </c>
-      <c r="BH29" s="51" t="s">
-        <v>567</v>
-      </c>
-      <c r="BI29" s="51" t="s">
-        <v>568</v>
-      </c>
-      <c r="BJ29" s="54" t="str">
-        <f t="shared" si="57"/>
-        <v>3</v>
-      </c>
-      <c r="BK29" s="54" t="str">
-        <f t="shared" si="57"/>
-        <v>7</v>
-      </c>
-      <c r="BL29" s="54" t="str">
-        <f t="shared" si="57"/>
-        <v>8</v>
-      </c>
-      <c r="BM29" s="54" t="str">
-        <f t="shared" si="57"/>
-        <v>0</v>
-      </c>
-      <c r="BN29" s="54" t="str">
-        <f t="shared" si="57"/>
-        <v>5</v>
-      </c>
-      <c r="BO29" s="54" t="str">
-        <f t="shared" si="57"/>
-        <v>-</v>
-      </c>
-      <c r="BP29" s="54" t="str">
-        <f t="shared" si="57"/>
-        <v>6</v>
-      </c>
-      <c r="BQ29" s="54" t="str">
-        <f t="shared" si="57"/>
-        <v>W</v>
-      </c>
-      <c r="BR29" s="54" t="str">
-        <f t="shared" si="57"/>
-        <v>Z</v>
-      </c>
-      <c r="BS29" s="54" t="str">
-        <f t="shared" si="57"/>
-        <v>-</v>
-      </c>
-      <c r="BT29" s="54" t="str">
-        <f t="shared" si="57"/>
-        <v>M</v>
-      </c>
-      <c r="BU29" s="54" t="str">
-        <f t="shared" si="57"/>
-        <v>6</v>
-      </c>
-      <c r="BV29" s="54" t="str">
-        <f t="shared" si="57"/>
-        <v>1</v>
-      </c>
-      <c r="BW29" s="54" t="str">
-        <f t="shared" si="57"/>
-        <v>0</v>
-      </c>
-      <c r="BX29" s="55" t="str">
-        <f>DEC2HEX(CODE(BJ29),2)</f>
-        <v>33</v>
-      </c>
-      <c r="BY29" s="55" t="str">
-        <f t="shared" ref="BY29:BY30" si="144">DEC2HEX(CODE(BK29),2)</f>
-        <v>37</v>
-      </c>
-      <c r="BZ29" s="55" t="str">
-        <f t="shared" ref="BZ29:BZ30" si="145">DEC2HEX(CODE(BL29),2)</f>
-        <v>38</v>
-      </c>
-      <c r="CA29" s="55" t="str">
-        <f t="shared" ref="CA29:CA30" si="146">DEC2HEX(CODE(BM29),2)</f>
-        <v>30</v>
-      </c>
-      <c r="CB29" s="55" t="str">
-        <f t="shared" ref="CB29:CB30" si="147">DEC2HEX(CODE(BN29),2)</f>
-        <v>35</v>
-      </c>
-      <c r="CC29" s="55" t="str">
-        <f t="shared" ref="CC29:CC30" si="148">DEC2HEX(CODE(BO29),2)</f>
-        <v>2D</v>
-      </c>
-      <c r="CD29" s="55" t="str">
-        <f t="shared" ref="CD29:CD30" si="149">DEC2HEX(CODE(BP29),2)</f>
-        <v>36</v>
-      </c>
-      <c r="CE29" s="55" t="str">
-        <f t="shared" ref="CE29:CE30" si="150">DEC2HEX(CODE(BQ29),2)</f>
-        <v>57</v>
-      </c>
-      <c r="CF29" s="55" t="str">
-        <f t="shared" ref="CF29:CF30" si="151">DEC2HEX(CODE(BR29),2)</f>
-        <v>5A</v>
-      </c>
-      <c r="CG29" s="55" t="str">
-        <f t="shared" ref="CG29:CG30" si="152">DEC2HEX(CODE(BS29),2)</f>
-        <v>2D</v>
-      </c>
-      <c r="CH29" s="55" t="str">
-        <f t="shared" ref="CH29:CH30" si="153">DEC2HEX(CODE(BT29),2)</f>
-        <v>4D</v>
-      </c>
-      <c r="CI29" s="55" t="str">
-        <f t="shared" ref="CI29:CI30" si="154">DEC2HEX(CODE(BU29),2)</f>
-        <v>36</v>
-      </c>
-      <c r="CJ29" s="55" t="str">
-        <f t="shared" ref="CJ29:CJ30" si="155">DEC2HEX(CODE(BV29),2)</f>
-        <v>31</v>
-      </c>
-      <c r="CK29" s="55" t="str">
-        <f t="shared" ref="CK29:CK30" si="156">DEC2HEX(CODE(BW29),2)</f>
-        <v>30</v>
-      </c>
-      <c r="CL29" s="54" t="str">
-        <f>BX29&amp;BY29&amp;BZ29&amp;CA29&amp;CB29&amp;CC29&amp;CD29&amp;CE29&amp;CF29&amp;CG29&amp;CH29&amp;CI29&amp;CJ29&amp;CK29</f>
-        <v>33373830352D36575A2D4D363130</v>
-      </c>
-      <c r="CM29" s="104" t="s">
-        <v>513</v>
-      </c>
-      <c r="CN29" s="51" t="s">
-        <v>569</v>
-      </c>
-      <c r="CO29" s="51" t="s">
-        <v>308</v>
-      </c>
-      <c r="CP29" s="51" t="s">
-        <v>308</v>
-      </c>
-      <c r="CQ29" s="107" t="s">
-        <v>570</v>
-      </c>
-      <c r="CR29" s="56"/>
-      <c r="CS29" s="54" t="str">
-        <f>SUBSTITUTE(J29," ","")</f>
-        <v>37820-6WZ-M610-M6</v>
-      </c>
-      <c r="CT29" s="107" t="s">
-        <v>571</v>
-      </c>
-      <c r="CU29" s="51" t="s">
-        <v>568</v>
-      </c>
-      <c r="CV29" s="51" t="s">
-        <v>568</v>
-      </c>
-      <c r="CW29" s="56"/>
-      <c r="CX29" s="51" t="str">
-        <f>AR29</f>
-        <v>37820-6WZ-M61</v>
-      </c>
-      <c r="CY29" s="51" t="s">
-        <v>572</v>
-      </c>
-      <c r="CZ29" s="51" t="s">
-        <v>572</v>
-      </c>
-    </row>
-    <row r="30" spans="1:104" s="42" customFormat="1" ht="44.25" hidden="1" customHeight="1" outlineLevel="1" collapsed="1">
-      <c r="A30" s="45"/>
-      <c r="B30" s="47">
-        <f t="shared" si="56"/>
-        <v>7</v>
-      </c>
-      <c r="C30" s="57"/>
-      <c r="D30" s="47" t="s">
-        <v>245</v>
-      </c>
-      <c r="E30" s="47"/>
-      <c r="F30" s="47"/>
-      <c r="G30" s="57"/>
-      <c r="H30" s="47"/>
-      <c r="I30" s="47"/>
-      <c r="J30" s="47"/>
-      <c r="K30" s="47"/>
-      <c r="L30" s="47"/>
-      <c r="M30" s="47"/>
-      <c r="N30" s="47"/>
-      <c r="O30" s="47"/>
-      <c r="P30" s="47"/>
-      <c r="Q30" s="47"/>
-      <c r="R30" s="47"/>
-      <c r="S30" s="47"/>
-      <c r="T30" s="47"/>
-      <c r="U30" s="47"/>
-      <c r="V30" s="47"/>
-      <c r="W30" s="47"/>
-      <c r="X30" s="47"/>
-      <c r="Y30" s="47"/>
-      <c r="Z30" s="47"/>
-      <c r="AA30" s="47"/>
-      <c r="AB30" s="47"/>
-      <c r="AC30" s="47"/>
-      <c r="AD30" s="47"/>
-      <c r="AE30" s="47"/>
-      <c r="AF30" s="47"/>
-      <c r="AG30" s="47"/>
-      <c r="AH30" s="47"/>
-      <c r="AI30" s="47"/>
-      <c r="AJ30" s="47"/>
-      <c r="AK30" s="47"/>
-      <c r="AL30" s="47"/>
-      <c r="AM30" s="47"/>
-      <c r="AN30" s="47"/>
-      <c r="AO30" s="47"/>
-      <c r="AP30" s="47"/>
-      <c r="AQ30" s="47"/>
-      <c r="AR30" s="47"/>
-      <c r="AS30" s="47"/>
-      <c r="AT30" s="47"/>
-      <c r="AU30" s="47"/>
-      <c r="AV30" s="47"/>
-      <c r="AW30" s="106"/>
-      <c r="AX30" s="47"/>
-      <c r="AY30" s="47"/>
-      <c r="AZ30" s="47"/>
-      <c r="BA30" s="47"/>
-      <c r="BB30" s="47"/>
-      <c r="BC30" s="47"/>
-      <c r="BD30" s="47"/>
-      <c r="BE30" s="47"/>
-      <c r="BF30" s="47"/>
-      <c r="BG30" s="47"/>
-      <c r="BH30" s="47"/>
-      <c r="BI30" s="47"/>
-      <c r="BJ30" s="47" t="str">
-        <f t="shared" ref="BJ30:BW33" si="157">MID($BI30,BJ$6,1)</f>
-        <v/>
-      </c>
-      <c r="BK30" s="47" t="str">
-        <f t="shared" si="157"/>
-        <v/>
-      </c>
-      <c r="BL30" s="47" t="str">
-        <f t="shared" si="157"/>
-        <v/>
-      </c>
-      <c r="BM30" s="47" t="str">
-        <f t="shared" si="157"/>
-        <v/>
-      </c>
-      <c r="BN30" s="47" t="str">
-        <f t="shared" si="157"/>
-        <v/>
-      </c>
-      <c r="BO30" s="47" t="str">
-        <f t="shared" si="157"/>
-        <v/>
-      </c>
-      <c r="BP30" s="47" t="str">
-        <f t="shared" si="157"/>
-        <v/>
-      </c>
-      <c r="BQ30" s="47" t="str">
-        <f t="shared" si="157"/>
-        <v/>
-      </c>
-      <c r="BR30" s="47" t="str">
-        <f t="shared" si="157"/>
-        <v/>
-      </c>
-      <c r="BS30" s="47" t="str">
-        <f t="shared" si="157"/>
-        <v/>
-      </c>
-      <c r="BT30" s="47" t="str">
-        <f t="shared" si="157"/>
-        <v/>
-      </c>
-      <c r="BU30" s="47" t="str">
-        <f t="shared" si="157"/>
-        <v/>
-      </c>
-      <c r="BV30" s="47" t="str">
-        <f t="shared" si="157"/>
-        <v/>
-      </c>
-      <c r="BW30" s="47" t="str">
-        <f t="shared" si="157"/>
-        <v/>
-      </c>
-      <c r="BX30" s="47" t="e">
-        <f>DEC2HEX(CODE(BJ30),2)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="BY30" s="47" t="e">
-        <f t="shared" si="144"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="BZ30" s="47" t="e">
-        <f t="shared" si="145"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="CA30" s="47" t="e">
-        <f t="shared" si="146"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="CB30" s="47" t="e">
-        <f t="shared" si="147"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="CC30" s="47" t="e">
-        <f t="shared" si="148"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="CD30" s="47" t="e">
-        <f t="shared" si="149"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="CE30" s="47" t="e">
-        <f t="shared" si="150"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="CF30" s="47" t="e">
-        <f t="shared" si="151"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="CG30" s="47" t="e">
-        <f t="shared" si="152"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="CH30" s="47" t="e">
-        <f t="shared" si="153"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="CI30" s="47" t="e">
-        <f t="shared" si="154"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="CJ30" s="47" t="e">
-        <f t="shared" si="155"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="CK30" s="47" t="e">
-        <f t="shared" si="156"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="CL30" s="47"/>
-      <c r="CM30" s="58"/>
-      <c r="CN30" s="47"/>
-      <c r="CO30" s="47"/>
-      <c r="CP30" s="47"/>
-      <c r="CQ30" s="47"/>
-      <c r="CR30" s="47"/>
-      <c r="CS30" s="47" t="str">
-        <f>SUBSTITUTE(J30," ","")</f>
-        <v/>
-      </c>
-      <c r="CT30" s="47"/>
-      <c r="CU30" s="47"/>
-      <c r="CV30" s="47"/>
-      <c r="CW30" s="47"/>
-      <c r="CX30" s="47"/>
-      <c r="CY30" s="47"/>
-      <c r="CZ30" s="47"/>
-    </row>
-    <row r="31" spans="1:104" s="43" customFormat="1" ht="39.950000000000003" hidden="1" customHeight="1" outlineLevel="1">
-      <c r="A31" s="45"/>
-      <c r="B31" s="46">
-        <f t="shared" si="56"/>
-        <v>7</v>
-      </c>
-      <c r="C31" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="D31" s="46" t="s">
-        <v>251</v>
-      </c>
-      <c r="E31" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="F31" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="G31" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="H31" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="I31" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="J31" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="K31" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="L31" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="M31" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="N31" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="O31" s="47"/>
-      <c r="P31" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="Q31" s="47"/>
-      <c r="R31" s="47"/>
-      <c r="S31" s="47"/>
-      <c r="T31" s="47" t="b">
-        <f>T29=T30</f>
-        <v>0</v>
-      </c>
-      <c r="U31" s="47" t="b">
-        <f t="shared" ref="U31:AZ31" si="158">U29=U30</f>
-        <v>0</v>
-      </c>
-      <c r="V31" s="47" t="b">
-        <f t="shared" si="158"/>
-        <v>0</v>
-      </c>
-      <c r="W31" s="47" t="b">
-        <f t="shared" si="158"/>
-        <v>0</v>
-      </c>
-      <c r="X31" s="47" t="b">
-        <f t="shared" si="158"/>
-        <v>0</v>
-      </c>
-      <c r="Y31" s="47" t="b">
-        <f t="shared" si="158"/>
-        <v>0</v>
-      </c>
-      <c r="Z31" s="47" t="b">
-        <f t="shared" si="158"/>
-        <v>0</v>
-      </c>
-      <c r="AA31" s="47" t="b">
-        <f t="shared" si="158"/>
-        <v>0</v>
-      </c>
-      <c r="AB31" s="47" t="b">
-        <f t="shared" si="158"/>
-        <v>0</v>
-      </c>
-      <c r="AC31" s="47" t="b">
-        <f t="shared" si="158"/>
-        <v>0</v>
-      </c>
-      <c r="AD31" s="47" t="b">
-        <f t="shared" si="158"/>
-        <v>0</v>
-      </c>
-      <c r="AE31" s="47" t="b">
-        <f t="shared" si="158"/>
-        <v>0</v>
-      </c>
-      <c r="AF31" s="47" t="b">
-        <f t="shared" si="158"/>
-        <v>0</v>
-      </c>
-      <c r="AG31" s="47" t="b">
-        <f t="shared" si="158"/>
-        <v>0</v>
-      </c>
-      <c r="AH31" s="47" t="b">
-        <f t="shared" si="158"/>
-        <v>0</v>
-      </c>
-      <c r="AI31" s="47" t="b">
-        <f t="shared" si="158"/>
-        <v>0</v>
-      </c>
-      <c r="AJ31" s="47" t="b">
-        <f t="shared" si="158"/>
-        <v>0</v>
-      </c>
-      <c r="AK31" s="47" t="b">
-        <f t="shared" si="158"/>
-        <v>0</v>
-      </c>
-      <c r="AL31" s="47" t="b">
-        <f t="shared" si="158"/>
-        <v>0</v>
-      </c>
-      <c r="AM31" s="47" t="b">
-        <f t="shared" si="158"/>
-        <v>0</v>
-      </c>
-      <c r="AN31" s="47" t="b">
-        <f t="shared" si="158"/>
-        <v>0</v>
-      </c>
-      <c r="AO31" s="47" t="b">
-        <f t="shared" si="158"/>
-        <v>0</v>
-      </c>
-      <c r="AP31" s="47" t="b">
-        <f t="shared" si="158"/>
-        <v>0</v>
-      </c>
-      <c r="AQ31" s="47" t="b">
-        <f t="shared" si="158"/>
-        <v>0</v>
-      </c>
-      <c r="AR31" s="47" t="b">
-        <f t="shared" si="158"/>
-        <v>0</v>
-      </c>
-      <c r="AS31" s="47" t="b">
-        <f t="shared" si="158"/>
-        <v>1</v>
-      </c>
-      <c r="AT31" s="47" t="b">
-        <f t="shared" si="158"/>
-        <v>1</v>
-      </c>
-      <c r="AU31" s="47" t="b">
-        <f t="shared" si="158"/>
-        <v>0</v>
-      </c>
-      <c r="AV31" s="47" t="b">
-        <f t="shared" si="158"/>
-        <v>0</v>
-      </c>
-      <c r="AW31" s="47" t="b">
-        <f t="shared" si="158"/>
-        <v>1</v>
-      </c>
-      <c r="AX31" s="47" t="b">
-        <f t="shared" si="158"/>
-        <v>1</v>
-      </c>
-      <c r="AY31" s="47" t="b">
-        <f t="shared" si="158"/>
-        <v>1</v>
-      </c>
-      <c r="AZ31" s="47" t="b">
-        <f t="shared" si="158"/>
-        <v>1</v>
-      </c>
-      <c r="BA31" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="BB31" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="BC31" s="47" t="b">
-        <f t="shared" ref="BC31:BH31" si="159">BC29=BC30</f>
-        <v>0</v>
-      </c>
-      <c r="BD31" s="47" t="b">
-        <f t="shared" si="159"/>
-        <v>0</v>
-      </c>
-      <c r="BE31" s="47" t="b">
-        <f t="shared" si="159"/>
-        <v>0</v>
-      </c>
-      <c r="BF31" s="47" t="b">
-        <f t="shared" si="159"/>
-        <v>0</v>
-      </c>
-      <c r="BG31" s="47" t="b">
-        <f t="shared" si="159"/>
-        <v>0</v>
-      </c>
-      <c r="BH31" s="47" t="b">
-        <f t="shared" si="159"/>
-        <v>0</v>
-      </c>
-      <c r="BI31" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="BJ31" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="BK31" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="BL31" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="BM31" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="BN31" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="BO31" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="BP31" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="BQ31" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="BR31" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="BS31" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="BT31" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="BU31" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="BV31" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="BW31" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="BX31" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="BY31" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="BZ31" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CA31" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CB31" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CC31" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CD31" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CE31" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CF31" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CG31" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CH31" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CI31" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CJ31" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CK31" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CL31" s="47" t="b">
-        <f>CL29=CL30</f>
-        <v>0</v>
-      </c>
-      <c r="CM31" s="47" t="b">
-        <f t="shared" ref="CM31:CN31" si="160">CM29=CM30</f>
-        <v>0</v>
-      </c>
-      <c r="CN31" s="47" t="b">
-        <f t="shared" si="160"/>
-        <v>0</v>
-      </c>
-      <c r="CO31" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CP31" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CQ31" s="47" t="b">
-        <f t="shared" ref="CQ31" si="161">CQ29=CQ30</f>
-        <v>0</v>
-      </c>
-      <c r="CR31" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CS31" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CT31" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CU31" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CV31" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CW31" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CX31" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CY31" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CZ31" s="47" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="32" spans="1:104" s="42" customFormat="1" ht="44.25" customHeight="1" collapsed="1">
-      <c r="A32" s="45"/>
-      <c r="B32" s="51">
-        <f t="shared" si="56"/>
-        <v>8</v>
-      </c>
-      <c r="C32" s="52">
-        <v>46324.656793981485</v>
-      </c>
-      <c r="D32" s="51" t="s">
-        <v>254</v>
-      </c>
-      <c r="E32" s="51"/>
-      <c r="F32" s="51"/>
-      <c r="G32" s="104"/>
-      <c r="H32" s="51" t="s">
-        <v>557</v>
-      </c>
-      <c r="I32" s="105"/>
-      <c r="J32" s="53" t="s">
-        <v>573</v>
-      </c>
-      <c r="K32" s="53"/>
-      <c r="L32" s="51"/>
-      <c r="M32" s="51"/>
-      <c r="N32" s="51"/>
-      <c r="O32" s="51" t="str">
-        <f>IF(COUNTIF(C34:CZ34,"FALSE")&gt;0,"NG","OK")</f>
-        <v>NG</v>
-      </c>
-      <c r="P32" s="51"/>
-      <c r="Q32" s="51" t="s">
-        <v>441</v>
-      </c>
-      <c r="R32" s="51" t="s">
-        <v>442</v>
-      </c>
-      <c r="S32" s="51" t="s">
-        <v>558</v>
-      </c>
-      <c r="T32" s="51" t="s">
-        <v>39</v>
-      </c>
-      <c r="U32" s="51" t="s">
-        <v>28</v>
-      </c>
-      <c r="V32" s="51" t="s">
-        <v>38</v>
-      </c>
-      <c r="W32" s="51" t="s">
-        <v>79</v>
-      </c>
-      <c r="X32" s="51" t="s">
-        <v>444</v>
-      </c>
-      <c r="Y32" s="51" t="s">
-        <v>444</v>
-      </c>
-      <c r="Z32" s="51" t="s">
-        <v>444</v>
-      </c>
-      <c r="AA32" s="51" t="s">
-        <v>444</v>
-      </c>
-      <c r="AB32" s="51" t="s">
-        <v>559</v>
-      </c>
-      <c r="AC32" s="51">
-        <v>93</v>
-      </c>
-      <c r="AD32" s="51" t="s">
-        <v>446</v>
-      </c>
-      <c r="AE32" s="51">
-        <v>1.5</v>
-      </c>
-      <c r="AF32" s="51">
-        <v>2028</v>
-      </c>
-      <c r="AG32" s="51" t="s">
-        <v>560</v>
-      </c>
-      <c r="AH32" s="51" t="s">
-        <v>37</v>
-      </c>
-      <c r="AI32" s="51" t="s">
-        <v>449</v>
-      </c>
-      <c r="AJ32" s="51" t="s">
-        <v>561</v>
-      </c>
-      <c r="AK32" s="51">
-        <v>4</v>
-      </c>
-      <c r="AL32" s="51">
-        <v>159</v>
-      </c>
-      <c r="AM32" s="54" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(J32," ",""),"-","")</f>
-        <v>378206WZM710M6</v>
-      </c>
-      <c r="AN32" s="107" t="s">
-        <v>574</v>
-      </c>
-      <c r="AO32" s="107" t="s">
-        <v>575</v>
-      </c>
-      <c r="AP32" s="51" t="s">
-        <v>558</v>
-      </c>
-      <c r="AQ32" s="54" t="str">
-        <f>SUBSTITUTE(J32," ","")</f>
-        <v>37820-6WZ-M710-M6</v>
-      </c>
-      <c r="AR32" s="54" t="str">
-        <f>IF(RIGHT(SUBSTITUTE(J32," ",""),4)="0-M6",LEFT(SUBSTITUTE(J32," ",""),LEN(SUBSTITUTE(J32," ",""))-4),SUBSTITUTE(J32," ",""))</f>
-        <v>37820-6WZ-M71</v>
-      </c>
-      <c r="AS32" s="54">
-        <f>K32</f>
-        <v>0</v>
-      </c>
-      <c r="AT32" s="51"/>
-      <c r="AU32" s="51" t="s">
-        <v>452</v>
-      </c>
-      <c r="AV32" s="51" t="s">
-        <v>453</v>
-      </c>
-      <c r="AW32" s="107"/>
-      <c r="AX32" s="54">
-        <f>K32</f>
-        <v>0</v>
-      </c>
-      <c r="AY32" s="51"/>
-      <c r="AZ32" s="51"/>
-      <c r="BA32" s="51"/>
-      <c r="BB32" s="51"/>
-      <c r="BC32" s="51" t="s">
-        <v>564</v>
-      </c>
-      <c r="BD32" s="54" t="str">
-        <f>AP32</f>
-        <v>MG1CS022</v>
-      </c>
-      <c r="BE32" s="51" t="s">
-        <v>559</v>
-      </c>
-      <c r="BF32" s="51" t="s">
-        <v>565</v>
-      </c>
-      <c r="BG32" s="51" t="s">
-        <v>566</v>
-      </c>
-      <c r="BH32" s="51" t="s">
-        <v>567</v>
-      </c>
-      <c r="BI32" s="51" t="s">
-        <v>576</v>
-      </c>
-      <c r="BJ32" s="54" t="str">
-        <f t="shared" ref="BJ32:BW34" si="162">MID($BI32,BJ$6,1)</f>
-        <v>3</v>
-      </c>
-      <c r="BK32" s="54" t="str">
-        <f t="shared" si="162"/>
-        <v>7</v>
-      </c>
-      <c r="BL32" s="54" t="str">
-        <f t="shared" si="162"/>
-        <v>8</v>
-      </c>
-      <c r="BM32" s="54" t="str">
-        <f t="shared" si="162"/>
-        <v>0</v>
-      </c>
-      <c r="BN32" s="54" t="str">
-        <f t="shared" si="162"/>
-        <v>5</v>
-      </c>
-      <c r="BO32" s="54" t="str">
-        <f t="shared" si="162"/>
-        <v>-</v>
-      </c>
-      <c r="BP32" s="54" t="str">
-        <f t="shared" si="162"/>
-        <v>6</v>
-      </c>
-      <c r="BQ32" s="54" t="str">
-        <f t="shared" si="162"/>
-        <v>W</v>
-      </c>
-      <c r="BR32" s="54" t="str">
-        <f t="shared" si="162"/>
-        <v>Z</v>
-      </c>
-      <c r="BS32" s="54" t="str">
-        <f t="shared" si="162"/>
-        <v>-</v>
-      </c>
-      <c r="BT32" s="54" t="str">
-        <f t="shared" si="162"/>
-        <v>M</v>
-      </c>
-      <c r="BU32" s="54" t="str">
-        <f t="shared" si="162"/>
-        <v>7</v>
-      </c>
-      <c r="BV32" s="54" t="str">
-        <f t="shared" si="162"/>
-        <v>1</v>
-      </c>
-      <c r="BW32" s="54" t="str">
-        <f t="shared" si="162"/>
-        <v>0</v>
-      </c>
-      <c r="BX32" s="55" t="str">
-        <f>DEC2HEX(CODE(BJ32),2)</f>
-        <v>33</v>
-      </c>
-      <c r="BY32" s="55" t="str">
-        <f t="shared" ref="BY32:BY33" si="163">DEC2HEX(CODE(BK32),2)</f>
-        <v>37</v>
-      </c>
-      <c r="BZ32" s="55" t="str">
-        <f t="shared" ref="BZ32:BZ33" si="164">DEC2HEX(CODE(BL32),2)</f>
-        <v>38</v>
-      </c>
-      <c r="CA32" s="55" t="str">
-        <f t="shared" ref="CA32:CA33" si="165">DEC2HEX(CODE(BM32),2)</f>
-        <v>30</v>
-      </c>
-      <c r="CB32" s="55" t="str">
-        <f t="shared" ref="CB32:CB33" si="166">DEC2HEX(CODE(BN32),2)</f>
-        <v>35</v>
-      </c>
-      <c r="CC32" s="55" t="str">
-        <f t="shared" ref="CC32:CC33" si="167">DEC2HEX(CODE(BO32),2)</f>
-        <v>2D</v>
-      </c>
-      <c r="CD32" s="55" t="str">
-        <f t="shared" ref="CD32:CD33" si="168">DEC2HEX(CODE(BP32),2)</f>
-        <v>36</v>
-      </c>
-      <c r="CE32" s="55" t="str">
-        <f t="shared" ref="CE32:CE33" si="169">DEC2HEX(CODE(BQ32),2)</f>
-        <v>57</v>
-      </c>
-      <c r="CF32" s="55" t="str">
-        <f t="shared" ref="CF32:CF33" si="170">DEC2HEX(CODE(BR32),2)</f>
-        <v>5A</v>
-      </c>
-      <c r="CG32" s="55" t="str">
-        <f t="shared" ref="CG32:CG33" si="171">DEC2HEX(CODE(BS32),2)</f>
-        <v>2D</v>
-      </c>
-      <c r="CH32" s="55" t="str">
-        <f t="shared" ref="CH32:CH33" si="172">DEC2HEX(CODE(BT32),2)</f>
-        <v>4D</v>
-      </c>
-      <c r="CI32" s="55" t="str">
-        <f t="shared" ref="CI32:CI33" si="173">DEC2HEX(CODE(BU32),2)</f>
-        <v>37</v>
-      </c>
-      <c r="CJ32" s="55" t="str">
-        <f t="shared" ref="CJ32:CJ33" si="174">DEC2HEX(CODE(BV32),2)</f>
-        <v>31</v>
-      </c>
-      <c r="CK32" s="55" t="str">
-        <f t="shared" ref="CK32:CK33" si="175">DEC2HEX(CODE(BW32),2)</f>
-        <v>30</v>
-      </c>
-      <c r="CL32" s="54" t="str">
-        <f>BX32&amp;BY32&amp;BZ32&amp;CA32&amp;CB32&amp;CC32&amp;CD32&amp;CE32&amp;CF32&amp;CG32&amp;CH32&amp;CI32&amp;CJ32&amp;CK32</f>
-        <v>33373830352D36575A2D4D373130</v>
-      </c>
-      <c r="CM32" s="104" t="s">
-        <v>513</v>
-      </c>
-      <c r="CN32" s="51" t="s">
-        <v>569</v>
-      </c>
-      <c r="CO32" s="51" t="s">
-        <v>308</v>
-      </c>
-      <c r="CP32" s="51" t="s">
-        <v>308</v>
-      </c>
-      <c r="CQ32" s="107" t="s">
-        <v>570</v>
-      </c>
-      <c r="CR32" s="56"/>
-      <c r="CS32" s="54" t="str">
-        <f>SUBSTITUTE(J32," ","")</f>
-        <v>37820-6WZ-M710-M6</v>
-      </c>
-      <c r="CT32" s="107" t="s">
-        <v>577</v>
-      </c>
-      <c r="CU32" s="51" t="s">
-        <v>576</v>
-      </c>
-      <c r="CV32" s="51" t="s">
-        <v>576</v>
-      </c>
-      <c r="CW32" s="56"/>
-      <c r="CX32" s="51" t="str">
-        <f>AR32</f>
-        <v>37820-6WZ-M71</v>
-      </c>
-      <c r="CY32" s="51" t="s">
-        <v>572</v>
-      </c>
-      <c r="CZ32" s="51" t="s">
-        <v>578</v>
-      </c>
-    </row>
-    <row r="33" spans="1:104" s="42" customFormat="1" ht="44.25" hidden="1" customHeight="1" outlineLevel="1" collapsed="1">
-      <c r="A33" s="45"/>
-      <c r="B33" s="47">
-        <f t="shared" si="56"/>
-        <v>8</v>
-      </c>
-      <c r="C33" s="57"/>
-      <c r="D33" s="47" t="s">
-        <v>245</v>
-      </c>
-      <c r="E33" s="47"/>
-      <c r="F33" s="47"/>
-      <c r="G33" s="57"/>
-      <c r="H33" s="47"/>
-      <c r="I33" s="47"/>
-      <c r="J33" s="47"/>
-      <c r="K33" s="47"/>
-      <c r="L33" s="47"/>
-      <c r="M33" s="47"/>
-      <c r="N33" s="47"/>
-      <c r="O33" s="47"/>
-      <c r="P33" s="47"/>
-      <c r="Q33" s="47"/>
-      <c r="R33" s="47"/>
-      <c r="S33" s="47"/>
-      <c r="T33" s="47"/>
-      <c r="U33" s="47"/>
-      <c r="V33" s="47"/>
-      <c r="W33" s="47"/>
-      <c r="X33" s="47"/>
-      <c r="Y33" s="47"/>
-      <c r="Z33" s="47"/>
-      <c r="AA33" s="47"/>
-      <c r="AB33" s="47"/>
-      <c r="AC33" s="47"/>
-      <c r="AD33" s="47"/>
-      <c r="AE33" s="47"/>
-      <c r="AF33" s="47"/>
-      <c r="AG33" s="47"/>
-      <c r="AH33" s="47"/>
-      <c r="AI33" s="47"/>
-      <c r="AJ33" s="47"/>
-      <c r="AK33" s="47"/>
-      <c r="AL33" s="47"/>
-      <c r="AM33" s="47"/>
-      <c r="AN33" s="47"/>
-      <c r="AO33" s="47"/>
-      <c r="AP33" s="47"/>
-      <c r="AQ33" s="47"/>
-      <c r="AR33" s="47"/>
-      <c r="AS33" s="47"/>
-      <c r="AT33" s="47"/>
-      <c r="AU33" s="47"/>
-      <c r="AV33" s="47"/>
-      <c r="AW33" s="106"/>
-      <c r="AX33" s="47"/>
-      <c r="AY33" s="47"/>
-      <c r="AZ33" s="47"/>
-      <c r="BA33" s="47"/>
-      <c r="BB33" s="47"/>
-      <c r="BC33" s="47"/>
-      <c r="BD33" s="47"/>
-      <c r="BE33" s="47"/>
-      <c r="BF33" s="47"/>
-      <c r="BG33" s="47"/>
-      <c r="BH33" s="47"/>
-      <c r="BI33" s="47"/>
-      <c r="BJ33" s="47" t="str">
-        <f t="shared" si="157"/>
-        <v/>
-      </c>
-      <c r="BK33" s="47" t="str">
-        <f t="shared" si="157"/>
-        <v/>
-      </c>
-      <c r="BL33" s="47" t="str">
-        <f t="shared" si="157"/>
-        <v/>
-      </c>
-      <c r="BM33" s="47" t="str">
-        <f t="shared" si="157"/>
-        <v/>
-      </c>
-      <c r="BN33" s="47" t="str">
-        <f t="shared" si="157"/>
-        <v/>
-      </c>
-      <c r="BO33" s="47" t="str">
-        <f t="shared" si="157"/>
-        <v/>
-      </c>
-      <c r="BP33" s="47" t="str">
-        <f t="shared" si="157"/>
-        <v/>
-      </c>
-      <c r="BQ33" s="47" t="str">
-        <f t="shared" si="157"/>
-        <v/>
-      </c>
-      <c r="BR33" s="47" t="str">
-        <f t="shared" si="157"/>
-        <v/>
-      </c>
-      <c r="BS33" s="47" t="str">
-        <f t="shared" si="157"/>
-        <v/>
-      </c>
-      <c r="BT33" s="47" t="str">
-        <f t="shared" si="157"/>
-        <v/>
-      </c>
-      <c r="BU33" s="47" t="str">
-        <f t="shared" si="157"/>
-        <v/>
-      </c>
-      <c r="BV33" s="47" t="str">
-        <f t="shared" si="157"/>
-        <v/>
-      </c>
-      <c r="BW33" s="47" t="str">
-        <f t="shared" si="157"/>
-        <v/>
-      </c>
-      <c r="BX33" s="47" t="e">
-        <f>DEC2HEX(CODE(BJ33),2)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="BY33" s="47" t="e">
-        <f t="shared" si="163"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="BZ33" s="47" t="e">
-        <f t="shared" si="164"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="CA33" s="47" t="e">
-        <f t="shared" si="165"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="CB33" s="47" t="e">
-        <f t="shared" si="166"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="CC33" s="47" t="e">
-        <f t="shared" si="167"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="CD33" s="47" t="e">
-        <f t="shared" si="168"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="CE33" s="47" t="e">
-        <f t="shared" si="169"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="CF33" s="47" t="e">
-        <f t="shared" si="170"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="CG33" s="47" t="e">
-        <f t="shared" si="171"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="CH33" s="47" t="e">
-        <f t="shared" si="172"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="CI33" s="47" t="e">
-        <f t="shared" si="173"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="CJ33" s="47" t="e">
-        <f t="shared" si="174"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="CK33" s="47" t="e">
-        <f t="shared" si="175"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="CL33" s="47"/>
-      <c r="CM33" s="58"/>
-      <c r="CN33" s="47"/>
-      <c r="CO33" s="47"/>
-      <c r="CP33" s="47"/>
-      <c r="CQ33" s="47"/>
-      <c r="CR33" s="47"/>
-      <c r="CS33" s="47" t="str">
-        <f>SUBSTITUTE(J33," ","")</f>
-        <v/>
-      </c>
-      <c r="CT33" s="47"/>
-      <c r="CU33" s="47"/>
-      <c r="CV33" s="47"/>
-      <c r="CW33" s="47"/>
-      <c r="CX33" s="47"/>
-      <c r="CY33" s="47"/>
-      <c r="CZ33" s="47"/>
-    </row>
-    <row r="34" spans="1:104" s="43" customFormat="1" ht="39.950000000000003" hidden="1" customHeight="1" outlineLevel="1">
-      <c r="A34" s="45"/>
-      <c r="B34" s="46">
-        <f t="shared" si="56"/>
-        <v>8</v>
-      </c>
-      <c r="C34" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="D34" s="46" t="s">
-        <v>251</v>
-      </c>
-      <c r="E34" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="F34" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="G34" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="H34" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="I34" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="J34" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="K34" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="L34" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="M34" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="N34" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="O34" s="47"/>
-      <c r="P34" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="Q34" s="47"/>
-      <c r="R34" s="47"/>
-      <c r="S34" s="47"/>
-      <c r="T34" s="47" t="b">
-        <f>T32=T33</f>
-        <v>0</v>
-      </c>
-      <c r="U34" s="47" t="b">
-        <f t="shared" ref="U34:AZ34" si="176">U32=U33</f>
-        <v>0</v>
-      </c>
-      <c r="V34" s="47" t="b">
-        <f t="shared" si="176"/>
-        <v>0</v>
-      </c>
-      <c r="W34" s="47" t="b">
-        <f t="shared" si="176"/>
-        <v>0</v>
-      </c>
-      <c r="X34" s="47" t="b">
-        <f t="shared" si="176"/>
-        <v>0</v>
-      </c>
-      <c r="Y34" s="47" t="b">
-        <f t="shared" si="176"/>
-        <v>0</v>
-      </c>
-      <c r="Z34" s="47" t="b">
-        <f t="shared" si="176"/>
-        <v>0</v>
-      </c>
-      <c r="AA34" s="47" t="b">
-        <f t="shared" si="176"/>
-        <v>0</v>
-      </c>
-      <c r="AB34" s="47" t="b">
-        <f t="shared" si="176"/>
-        <v>0</v>
-      </c>
-      <c r="AC34" s="47" t="b">
-        <f t="shared" si="176"/>
-        <v>0</v>
-      </c>
-      <c r="AD34" s="47" t="b">
-        <f t="shared" si="176"/>
-        <v>0</v>
-      </c>
-      <c r="AE34" s="47" t="b">
-        <f t="shared" si="176"/>
-        <v>0</v>
-      </c>
-      <c r="AF34" s="47" t="b">
-        <f t="shared" si="176"/>
-        <v>0</v>
-      </c>
-      <c r="AG34" s="47" t="b">
-        <f t="shared" si="176"/>
-        <v>0</v>
-      </c>
-      <c r="AH34" s="47" t="b">
-        <f t="shared" si="176"/>
-        <v>0</v>
-      </c>
-      <c r="AI34" s="47" t="b">
-        <f t="shared" si="176"/>
-        <v>0</v>
-      </c>
-      <c r="AJ34" s="47" t="b">
-        <f t="shared" si="176"/>
-        <v>0</v>
-      </c>
-      <c r="AK34" s="47" t="b">
-        <f t="shared" si="176"/>
-        <v>0</v>
-      </c>
-      <c r="AL34" s="47" t="b">
-        <f t="shared" si="176"/>
-        <v>0</v>
-      </c>
-      <c r="AM34" s="47" t="b">
-        <f t="shared" si="176"/>
-        <v>0</v>
-      </c>
-      <c r="AN34" s="47" t="b">
-        <f t="shared" si="176"/>
-        <v>0</v>
-      </c>
-      <c r="AO34" s="47" t="b">
-        <f t="shared" si="176"/>
-        <v>0</v>
-      </c>
-      <c r="AP34" s="47" t="b">
-        <f t="shared" si="176"/>
-        <v>0</v>
-      </c>
-      <c r="AQ34" s="47" t="b">
-        <f t="shared" si="176"/>
-        <v>0</v>
-      </c>
-      <c r="AR34" s="47" t="b">
-        <f t="shared" si="176"/>
-        <v>0</v>
-      </c>
-      <c r="AS34" s="47" t="b">
-        <f t="shared" si="176"/>
-        <v>1</v>
-      </c>
-      <c r="AT34" s="47" t="b">
-        <f t="shared" si="176"/>
-        <v>1</v>
-      </c>
-      <c r="AU34" s="47" t="b">
-        <f t="shared" si="176"/>
-        <v>0</v>
-      </c>
-      <c r="AV34" s="47" t="b">
-        <f t="shared" si="176"/>
-        <v>0</v>
-      </c>
-      <c r="AW34" s="47" t="b">
-        <f t="shared" si="176"/>
-        <v>1</v>
-      </c>
-      <c r="AX34" s="47" t="b">
-        <f t="shared" si="176"/>
-        <v>1</v>
-      </c>
-      <c r="AY34" s="47" t="b">
-        <f t="shared" si="176"/>
-        <v>1</v>
-      </c>
-      <c r="AZ34" s="47" t="b">
-        <f t="shared" si="176"/>
-        <v>1</v>
-      </c>
-      <c r="BA34" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="BB34" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="BC34" s="47" t="b">
-        <f t="shared" ref="BC34:BH34" si="177">BC32=BC33</f>
-        <v>0</v>
-      </c>
-      <c r="BD34" s="47" t="b">
-        <f t="shared" si="177"/>
-        <v>0</v>
-      </c>
-      <c r="BE34" s="47" t="b">
-        <f t="shared" si="177"/>
-        <v>0</v>
-      </c>
-      <c r="BF34" s="47" t="b">
-        <f t="shared" si="177"/>
-        <v>0</v>
-      </c>
-      <c r="BG34" s="47" t="b">
-        <f t="shared" si="177"/>
-        <v>0</v>
-      </c>
-      <c r="BH34" s="47" t="b">
-        <f t="shared" si="177"/>
-        <v>0</v>
-      </c>
-      <c r="BI34" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="BJ34" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="BK34" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="BL34" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="BM34" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="BN34" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="BO34" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="BP34" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="BQ34" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="BR34" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="BS34" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="BT34" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="BU34" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="BV34" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="BW34" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="BX34" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="BY34" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="BZ34" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CA34" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CB34" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CC34" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CD34" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CE34" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CF34" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CG34" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CH34" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CI34" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CJ34" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CK34" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CL34" s="47" t="b">
-        <f>CL32=CL33</f>
-        <v>0</v>
-      </c>
-      <c r="CM34" s="47" t="b">
-        <f t="shared" ref="CM34:CN34" si="178">CM32=CM33</f>
-        <v>0</v>
-      </c>
-      <c r="CN34" s="47" t="b">
-        <f t="shared" si="178"/>
-        <v>0</v>
-      </c>
-      <c r="CO34" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CP34" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CQ34" s="47" t="b">
-        <f t="shared" ref="CQ34" si="179">CQ32=CQ33</f>
-        <v>0</v>
-      </c>
-      <c r="CR34" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CS34" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CT34" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CU34" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CV34" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CW34" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CX34" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CY34" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="CZ34" s="47" t="s">
         <v>264</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="CS6:CZ6"/>
+    <mergeCell ref="CL6:CR6"/>
+    <mergeCell ref="AQ6:AU6"/>
+    <mergeCell ref="AV6:AZ6"/>
+    <mergeCell ref="BJ7:BW7"/>
+    <mergeCell ref="BX7:CK7"/>
     <mergeCell ref="B2:H4"/>
     <mergeCell ref="T6:AA6"/>
     <mergeCell ref="AB6:AK6"/>
@@ -21002,12 +19105,6 @@
     <mergeCell ref="M6:N6"/>
     <mergeCell ref="B6:L6"/>
     <mergeCell ref="O6:P6"/>
-    <mergeCell ref="CS6:CZ6"/>
-    <mergeCell ref="CL6:CR6"/>
-    <mergeCell ref="AQ6:AU6"/>
-    <mergeCell ref="AV6:AZ6"/>
-    <mergeCell ref="BJ7:BW7"/>
-    <mergeCell ref="BX7:CK7"/>
   </mergeCells>
   <phoneticPr fontId="18"/>
   <conditionalFormatting sqref="T13:AZ13 BC13:CR13 BC16:CR16">
@@ -21021,63 +19118,52 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T19:AZ19">
-    <cfRule type="cellIs" dxfId="12" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="11" priority="5" operator="equal">
       <formula>2370014827</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T22:AZ22">
-    <cfRule type="cellIs" dxfId="11" priority="5" operator="equal">
-      <formula>2370014827</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="T25:AZ25">
     <cfRule type="cellIs" dxfId="10" priority="3" operator="equal">
       <formula>2370014827</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T28:AZ28 T31:AZ31 T34:AZ34">
+  <conditionalFormatting sqref="T25:AZ25 T28:AZ28">
     <cfRule type="cellIs" dxfId="9" priority="1" operator="equal">
       <formula>2370014827</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BC19:CR19">
-    <cfRule type="cellIs" dxfId="8" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="6" operator="equal">
       <formula>2370014827</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BC22:CR22">
-    <cfRule type="cellIs" dxfId="7" priority="6" operator="equal">
-      <formula>2370014827</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="BC25:CR25">
     <cfRule type="cellIs" dxfId="6" priority="4" operator="equal">
       <formula>2370014827</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BC28:CR28 BC31:CR31 BC34:CR34">
+  <conditionalFormatting sqref="BC25:CR25 BC28:CR28">
     <cfRule type="cellIs" dxfId="5" priority="2" operator="equal">
       <formula>2370014827</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations xWindow="1254" yWindow="852" count="3">
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="to be imported from pool and filled later" sqref="AW8:AW12 AW14:AW15 AW17:AW18 AW20:AW21 AW23:AW24 AW26:AW27 AW29:AW30 AW32:AW33" xr:uid="{7E3410B7-94B3-4447-9E49-760CE60EEE4F}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="to be pick from PST_Lib, requried D2C" sqref="BD8:BF12 BH17:CZ18 BD26:BF27 BH20:CZ21 BD14:BF15 BH8:CZ12 BD17:BF18 BH23:CZ24 BD20:BF21 BH14:CZ15 BD23:BF24 BH26:CZ27 BD29:BF30 BH29:CZ30 BD32:BF33 BH32:CZ33" xr:uid="{F4497FCE-6BFF-4813-BA4D-924E8853B93C}"/>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X8:AA8 X23:AA24 X10:AA12 X14:AA15 X17:AA18 X20:AA21 X26:AA27 X29:AA30 X32:AA33" xr:uid="{B1F30C27-2B87-435B-A957-C50D2371C83F}">
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="to be imported from pool and filled later" sqref="AW8:AW12 AW14:AW15 AW17:AW18 AW20:AW21 AW23:AW24 AW26:AW27" xr:uid="{7E3410B7-94B3-4447-9E49-760CE60EEE4F}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="to be pick from PST_Lib, requried D2C" sqref="BD8:BF12 BD23:BF24 BH17:CZ18 BD14:BF15 BH8:CZ12 BH20:CZ21 BD17:BF18 BH14:CZ15 BD20:BF21 BH23:CZ24 BD26:BF27 BH26:CZ27" xr:uid="{F4497FCE-6BFF-4813-BA4D-924E8853B93C}"/>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X8:AA8 X20:AA21 X10:AA12 X14:AA15 X17:AA18 X23:AA24 X26:AA27" xr:uid="{B1F30C27-2B87-435B-A957-C50D2371C83F}">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
     <hyperlink ref="I11" r:id="rId1" xr:uid="{FD80D307-1420-4961-8186-7D132D8AA117}"/>
     <hyperlink ref="I14" r:id="rId2" xr:uid="{754F8193-4398-4D18-867D-BB333B86F2BE}"/>
-    <hyperlink ref="I17" r:id="rId3" xr:uid="{81ED5211-E8B3-413C-88C3-CA1F1D222DE8}"/>
-    <hyperlink ref="I20" r:id="rId4" xr:uid="{332A67C1-913A-4CB5-8AF6-4205F58CA79A}"/>
-    <hyperlink ref="I23" r:id="rId5" xr:uid="{9F8ADA39-5034-4428-84D4-E3806882DCB2}"/>
-    <hyperlink ref="I26" r:id="rId6" xr:uid="{22DF0105-0871-47FD-91DE-E18A226DB0F6}"/>
+    <hyperlink ref="I17" r:id="rId3" xr:uid="{332A67C1-913A-4CB5-8AF6-4205F58CA79A}"/>
+    <hyperlink ref="I20" r:id="rId4" xr:uid="{9F8ADA39-5034-4428-84D4-E3806882DCB2}"/>
+    <hyperlink ref="I23" r:id="rId5" xr:uid="{22DF0105-0871-47FD-91DE-E18A226DB0F6}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId7"/>
-  <legacyDrawing r:id="rId8"/>
+  <drawing r:id="rId6"/>
+  <legacyDrawing r:id="rId7"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xWindow="1254" yWindow="852" count="4">
@@ -21085,25 +19171,25 @@
           <x14:formula1>
             <xm:f>Term!$B$6:$B$8</xm:f>
           </x14:formula1>
-          <xm:sqref>T8:T12 T23:T24 T14:T15 T17:T18 T20:T21 T26:T27 T29:T30 T32:T33</xm:sqref>
+          <xm:sqref>T8:T12 T20:T21 T14:T15 T17:T18 T23:T24 T26:T27</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{8393420D-CF47-4DAC-823D-054E6C500F4E}">
           <x14:formula1>
             <xm:f>Term!$B$13:$B$20</xm:f>
           </x14:formula1>
-          <xm:sqref>U8 U10:U12 U23:U24 U14:U15 U17:U18 U20:U21 U26:U27 U29:U30 U32:U33</xm:sqref>
+          <xm:sqref>U8 U10:U12 U20:U21 U14:U15 U17:U18 U23:U24 U26:U27</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{D6F878B0-BC66-4D73-B333-AC478B6ECF75}">
           <x14:formula1>
             <xm:f>Term!$B$25:$B$29</xm:f>
           </x14:formula1>
-          <xm:sqref>V8 V10:V12 V23:V24 V14:V15 V17:V18 V20:V21 V26:V27 V29:V30 V32:V33</xm:sqref>
+          <xm:sqref>V8 V10:V12 V20:V21 V14:V15 V17:V18 V23:V24 V26:V27</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{66CAFB4E-FD6E-45D7-B5CC-5BEEE77F060C}">
           <x14:formula1>
             <xm:f>Term!$B$34:$B$36</xm:f>
           </x14:formula1>
-          <xm:sqref>W8 W10:W12 W23:W24 W14:W15 W17:W18 W20:W21 W26:W27 W29:W30 W32:W33</xm:sqref>
+          <xm:sqref>W8 W10:W12 W20:W21 W14:W15 W17:W18 W23:W24 W26:W27</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -21367,13 +19453,13 @@
       </c>
       <c r="E7" s="93"/>
       <c r="F7" s="97" t="s">
-        <v>535</v>
+        <v>523</v>
       </c>
       <c r="G7" s="98" t="s">
-        <v>534</v>
+        <v>522</v>
       </c>
       <c r="H7" s="91" t="s">
-        <v>533</v>
+        <v>521</v>
       </c>
       <c r="I7" s="91" t="s">
         <v>427</v>
